--- a/btp_dati.xlsx
+++ b/btp_dati.xlsx
@@ -551,10 +551,10 @@
         <v>3.994</v>
       </c>
       <c r="L2" t="n">
-        <v>3.71</v>
+        <v>3.719</v>
       </c>
       <c r="M2" t="n">
-        <v>3.246</v>
+        <v>3.254</v>
       </c>
     </row>
     <row r="3">
@@ -598,10 +598,10 @@
         <v>6.019</v>
       </c>
       <c r="L3" t="n">
-        <v>3.085</v>
+        <v>3.088</v>
       </c>
       <c r="M3" t="n">
-        <v>2.699</v>
+        <v>2.702</v>
       </c>
     </row>
     <row r="4">
@@ -645,10 +645,10 @@
         <v>10.924</v>
       </c>
       <c r="L4" t="n">
-        <v>2.949</v>
+        <v>2.951</v>
       </c>
       <c r="M4" t="n">
-        <v>2.58</v>
+        <v>2.582</v>
       </c>
     </row>
     <row r="5">
@@ -692,10 +692,10 @@
         <v>16.581</v>
       </c>
       <c r="L5" t="n">
-        <v>3.307</v>
+        <v>3.309</v>
       </c>
       <c r="M5" t="n">
-        <v>2.893</v>
+        <v>2.895</v>
       </c>
     </row>
     <row r="6">
@@ -739,10 +739,10 @@
         <v>22.474</v>
       </c>
       <c r="L6" t="n">
-        <v>3.43</v>
+        <v>3.431</v>
       </c>
       <c r="M6" t="n">
-        <v>3.001</v>
+        <v>3.002</v>
       </c>
     </row>
     <row r="7">
@@ -786,10 +786,10 @@
         <v>27.824</v>
       </c>
       <c r="L7" t="n">
-        <v>3.539</v>
+        <v>3.54</v>
       </c>
       <c r="M7" t="n">
-        <v>3.096</v>
+        <v>3.097</v>
       </c>
     </row>
     <row r="8">
@@ -880,10 +880,10 @@
         <v>36.452</v>
       </c>
       <c r="L9" t="n">
-        <v>3.625</v>
+        <v>3.626</v>
       </c>
       <c r="M9" t="n">
-        <v>3.171</v>
+        <v>3.172</v>
       </c>
     </row>
     <row r="10">
@@ -927,10 +927,10 @@
         <v>49.437</v>
       </c>
       <c r="L10" t="n">
-        <v>4.039</v>
+        <v>4.04</v>
       </c>
       <c r="M10" t="n">
-        <v>3.534</v>
+        <v>3.535</v>
       </c>
     </row>
     <row r="11">
@@ -974,10 +974,10 @@
         <v>56.209</v>
       </c>
       <c r="L11" t="n">
-        <v>4.261</v>
+        <v>4.262</v>
       </c>
       <c r="M11" t="n">
-        <v>3.728</v>
+        <v>3.729</v>
       </c>
     </row>
     <row r="12">
@@ -1068,10 +1068,10 @@
         <v>2.74</v>
       </c>
       <c r="L13" t="n">
-        <v>5.603</v>
+        <v>5.631</v>
       </c>
       <c r="M13" t="n">
-        <v>4.902</v>
+        <v>4.927</v>
       </c>
     </row>
     <row r="14">
@@ -1115,10 +1115,10 @@
         <v>1.443</v>
       </c>
       <c r="L14" t="n">
-        <v>1.498</v>
+        <v>1.501</v>
       </c>
       <c r="M14" t="n">
-        <v>1.31</v>
+        <v>1.313</v>
       </c>
     </row>
     <row r="15">
@@ -1317,10 +1317,10 @@
         <v>8.273</v>
       </c>
       <c r="L22" t="n">
-        <v>3.084</v>
+        <v>3.086</v>
       </c>
       <c r="M22" t="n">
-        <v>2.698</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="23">
@@ -1364,10 +1364,10 @@
         <v>72.489</v>
       </c>
       <c r="L23" t="n">
-        <v>4.342</v>
+        <v>4.343</v>
       </c>
       <c r="M23" t="n">
-        <v>3.799</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="24">
@@ -1563,10 +1563,10 @@
         <v>11.786</v>
       </c>
       <c r="L31" t="n">
-        <v>2.952</v>
+        <v>2.954</v>
       </c>
       <c r="M31" t="n">
-        <v>2.583</v>
+        <v>2.584</v>
       </c>
     </row>
     <row r="32">
@@ -1657,10 +1657,10 @@
         <v>16.773</v>
       </c>
       <c r="L33" t="n">
-        <v>2.92</v>
+        <v>2.921</v>
       </c>
       <c r="M33" t="n">
-        <v>2.554</v>
+        <v>2.555</v>
       </c>
     </row>
     <row r="34">
@@ -1704,10 +1704,10 @@
         <v>0.868</v>
       </c>
       <c r="L34" t="n">
-        <v>3.179</v>
+        <v>3.207</v>
       </c>
       <c r="M34" t="n">
-        <v>2.781</v>
+        <v>2.806</v>
       </c>
     </row>
     <row r="35">
@@ -1751,10 +1751,10 @@
         <v>7.958</v>
       </c>
       <c r="L35" t="n">
-        <v>1.279</v>
+        <v>1.28</v>
       </c>
       <c r="M35" t="n">
-        <v>1.119</v>
+        <v>1.12</v>
       </c>
     </row>
     <row r="36">
@@ -1845,10 +1845,10 @@
         <v>1.638</v>
       </c>
       <c r="L37" t="n">
-        <v>2.309</v>
+        <v>2.317</v>
       </c>
       <c r="M37" t="n">
-        <v>2.02</v>
+        <v>2.027</v>
       </c>
     </row>
     <row r="38">
@@ -1892,10 +1892,10 @@
         <v>32.764</v>
       </c>
       <c r="L38" t="n">
-        <v>3.382</v>
+        <v>3.383</v>
       </c>
       <c r="M38" t="n">
-        <v>2.959</v>
+        <v>2.96</v>
       </c>
     </row>
     <row r="39">
@@ -1939,10 +1939,10 @@
         <v>2.393</v>
       </c>
       <c r="L39" t="n">
-        <v>2.084</v>
+        <v>2.088</v>
       </c>
       <c r="M39" t="n">
-        <v>1.823</v>
+        <v>1.827</v>
       </c>
     </row>
     <row r="40">
@@ -2033,10 +2033,10 @@
         <v>22.561</v>
       </c>
       <c r="L41" t="n">
-        <v>3.195</v>
+        <v>3.196</v>
       </c>
       <c r="M41" t="n">
-        <v>2.795</v>
+        <v>2.796</v>
       </c>
     </row>
     <row r="42">
@@ -2080,10 +2080,10 @@
         <v>3.596</v>
       </c>
       <c r="L42" t="n">
-        <v>2.269</v>
+        <v>2.272</v>
       </c>
       <c r="M42" t="n">
-        <v>1.985</v>
+        <v>1.987</v>
       </c>
     </row>
     <row r="43">
@@ -2156,10 +2156,10 @@
         <v>77.901</v>
       </c>
       <c r="L44" t="n">
-        <v>3.943</v>
+        <v>3.944</v>
       </c>
       <c r="M44" t="n">
-        <v>3.45</v>
+        <v>3.451</v>
       </c>
     </row>
     <row r="45">
@@ -2203,10 +2203,10 @@
         <v>3.631</v>
       </c>
       <c r="L45" t="n">
-        <v>2.097</v>
+        <v>2.1</v>
       </c>
       <c r="M45" t="n">
-        <v>1.834</v>
+        <v>1.837</v>
       </c>
     </row>
     <row r="46">
@@ -2250,10 +2250,10 @@
         <v>41.566</v>
       </c>
       <c r="L46" t="n">
-        <v>3.634</v>
+        <v>3.635</v>
       </c>
       <c r="M46" t="n">
-        <v>3.179</v>
+        <v>3.18</v>
       </c>
     </row>
     <row r="47">
@@ -2297,10 +2297,10 @@
         <v>4.698</v>
       </c>
       <c r="L47" t="n">
-        <v>2.163</v>
+        <v>2.165</v>
       </c>
       <c r="M47" t="n">
-        <v>1.892</v>
+        <v>1.894</v>
       </c>
     </row>
     <row r="48">
@@ -2344,10 +2344,10 @@
         <v>0.5679999999999999</v>
       </c>
       <c r="L48" t="n">
-        <v>0.832</v>
+        <v>0.835</v>
       </c>
       <c r="M48" t="n">
-        <v>0.728</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="49">
@@ -2391,10 +2391,10 @@
         <v>7.218</v>
       </c>
       <c r="L49" t="n">
-        <v>2.488</v>
+        <v>2.49</v>
       </c>
       <c r="M49" t="n">
-        <v>2.177</v>
+        <v>2.178</v>
       </c>
     </row>
     <row r="50">
@@ -2438,10 +2438,10 @@
         <v>0.992</v>
       </c>
       <c r="L50" t="n">
-        <v>4.223</v>
+        <v>4.267</v>
       </c>
       <c r="M50" t="n">
-        <v>3.695</v>
+        <v>3.733</v>
       </c>
     </row>
     <row r="51">
@@ -2485,7 +2485,7 @@
         <v>29.259</v>
       </c>
       <c r="L51" t="n">
-        <v>3.496</v>
+        <v>3.497</v>
       </c>
       <c r="M51" t="n">
         <v>3.059</v>
@@ -2579,10 +2579,10 @@
         <v>8.662000000000001</v>
       </c>
       <c r="L53" t="n">
-        <v>2.486</v>
+        <v>2.488</v>
       </c>
       <c r="M53" t="n">
-        <v>2.175</v>
+        <v>2.177</v>
       </c>
     </row>
     <row r="54">
@@ -2626,10 +2626,10 @@
         <v>1.744</v>
       </c>
       <c r="L54" t="n">
-        <v>2.14</v>
+        <v>2.146</v>
       </c>
       <c r="M54" t="n">
-        <v>1.872</v>
+        <v>1.877</v>
       </c>
     </row>
     <row r="55">
@@ -2673,10 +2673,10 @@
         <v>47.608</v>
       </c>
       <c r="L55" t="n">
-        <v>3.734</v>
+        <v>3.735</v>
       </c>
       <c r="M55" t="n">
-        <v>3.267</v>
+        <v>3.268</v>
       </c>
     </row>
     <row r="56">
@@ -2720,10 +2720,10 @@
         <v>10.561</v>
       </c>
       <c r="L56" t="n">
-        <v>2.597</v>
+        <v>2.599</v>
       </c>
       <c r="M56" t="n">
-        <v>2.272</v>
+        <v>2.274</v>
       </c>
     </row>
     <row r="57">
@@ -2814,10 +2814,10 @@
         <v>1.526</v>
       </c>
       <c r="L58" t="n">
-        <v>0.786</v>
+        <v>0.787</v>
       </c>
       <c r="M58" t="n">
-        <v>0.6870000000000001</v>
+        <v>0.6879999999999999</v>
       </c>
     </row>
     <row r="59">
@@ -2861,10 +2861,10 @@
         <v>2.489</v>
       </c>
       <c r="L59" t="n">
-        <v>1.981</v>
+        <v>1.985</v>
       </c>
       <c r="M59" t="n">
-        <v>1.733</v>
+        <v>1.736</v>
       </c>
     </row>
     <row r="60">
@@ -3002,10 +3002,10 @@
         <v>11.06</v>
       </c>
       <c r="L62" t="n">
-        <v>2.537</v>
+        <v>2.539</v>
       </c>
       <c r="M62" t="n">
-        <v>2.219</v>
+        <v>2.221</v>
       </c>
     </row>
     <row r="63">
@@ -3049,10 +3049,10 @@
         <v>12.586</v>
       </c>
       <c r="L63" t="n">
-        <v>2.706</v>
+        <v>2.707</v>
       </c>
       <c r="M63" t="n">
-        <v>2.367</v>
+        <v>2.368</v>
       </c>
     </row>
     <row r="64">
@@ -3096,10 +3096,10 @@
         <v>10.928</v>
       </c>
       <c r="L64" t="n">
-        <v>2.532</v>
+        <v>2.534</v>
       </c>
       <c r="M64" t="n">
-        <v>2.215</v>
+        <v>2.217</v>
       </c>
     </row>
     <row r="65">
@@ -3172,10 +3172,10 @@
         <v>4.108</v>
       </c>
       <c r="L66" t="n">
-        <v>2.234</v>
+        <v>2.237</v>
       </c>
       <c r="M66" t="n">
-        <v>1.954</v>
+        <v>1.957</v>
       </c>
     </row>
     <row r="67">
@@ -3219,10 +3219,10 @@
         <v>0.822</v>
       </c>
       <c r="L67" t="n">
-        <v>1.949</v>
+        <v>1.96</v>
       </c>
       <c r="M67" t="n">
-        <v>1.705</v>
+        <v>1.714</v>
       </c>
     </row>
     <row r="68">
@@ -3266,10 +3266,10 @@
         <v>46.41</v>
       </c>
       <c r="L68" t="n">
-        <v>3.406</v>
+        <v>3.407</v>
       </c>
       <c r="M68" t="n">
-        <v>2.98</v>
+        <v>2.981</v>
       </c>
     </row>
     <row r="69">
@@ -3313,10 +3313,10 @@
         <v>13.317</v>
       </c>
       <c r="L69" t="n">
-        <v>2.695</v>
+        <v>2.696</v>
       </c>
       <c r="M69" t="n">
-        <v>2.358</v>
+        <v>2.359</v>
       </c>
     </row>
     <row r="70">
@@ -3407,10 +3407,10 @@
         <v>5.853</v>
       </c>
       <c r="L71" t="n">
-        <v>2.041</v>
+        <v>2.043</v>
       </c>
       <c r="M71" t="n">
-        <v>1.785</v>
+        <v>1.787</v>
       </c>
     </row>
     <row r="72">
@@ -3501,10 +3501,10 @@
         <v>4.908</v>
       </c>
       <c r="L73" t="n">
-        <v>2.157</v>
+        <v>2.159</v>
       </c>
       <c r="M73" t="n">
-        <v>1.887</v>
+        <v>1.889</v>
       </c>
     </row>
     <row r="74">
@@ -3548,10 +3548,10 @@
         <v>13.868</v>
       </c>
       <c r="L74" t="n">
-        <v>2.65</v>
+        <v>2.651</v>
       </c>
       <c r="M74" t="n">
-        <v>2.318</v>
+        <v>2.319</v>
       </c>
     </row>
     <row r="75">
@@ -3665,10 +3665,10 @@
         <v>55.798</v>
       </c>
       <c r="L77" t="n">
-        <v>3.23</v>
+        <v>3.231</v>
       </c>
       <c r="M77" t="n">
-        <v>2.826</v>
+        <v>2.827</v>
       </c>
     </row>
     <row r="78">
@@ -3806,10 +3806,10 @@
         <v>5.643</v>
       </c>
       <c r="L80" t="n">
-        <v>2.198</v>
+        <v>2.2</v>
       </c>
       <c r="M80" t="n">
-        <v>1.923</v>
+        <v>1.925</v>
       </c>
     </row>
     <row r="81">
@@ -3853,10 +3853,10 @@
         <v>15.159</v>
       </c>
       <c r="L81" t="n">
-        <v>2.743</v>
+        <v>2.744</v>
       </c>
       <c r="M81" t="n">
-        <v>2.4</v>
+        <v>2.401</v>
       </c>
     </row>
     <row r="82">
@@ -3923,10 +3923,10 @@
         <v>16.66</v>
       </c>
       <c r="L83" t="n">
-        <v>2.793</v>
+        <v>2.794</v>
       </c>
       <c r="M83" t="n">
-        <v>2.443</v>
+        <v>2.444</v>
       </c>
     </row>
     <row r="84">
@@ -3970,10 +3970,10 @@
         <v>16.489</v>
       </c>
       <c r="L84" t="n">
-        <v>2.276</v>
+        <v>2.277</v>
       </c>
       <c r="M84" t="n">
-        <v>1.991</v>
+        <v>1.992</v>
       </c>
     </row>
     <row r="85">
@@ -4017,10 +4017,10 @@
         <v>7.253</v>
       </c>
       <c r="L85" t="n">
-        <v>2.352</v>
+        <v>2.354</v>
       </c>
       <c r="M85" t="n">
-        <v>2.058</v>
+        <v>2.059</v>
       </c>
     </row>
     <row r="86">
@@ -4111,10 +4111,10 @@
         <v>9.082000000000001</v>
       </c>
       <c r="L87" t="n">
-        <v>1.335</v>
+        <v>1.336</v>
       </c>
       <c r="M87" t="n">
-        <v>1.168</v>
+        <v>1.169</v>
       </c>
     </row>
     <row r="88">
@@ -4158,10 +4158,10 @@
         <v>3.281</v>
       </c>
       <c r="L88" t="n">
-        <v>2.281</v>
+        <v>2.285</v>
       </c>
       <c r="M88" t="n">
-        <v>1.995</v>
+        <v>1.999</v>
       </c>
     </row>
     <row r="89">
@@ -4205,10 +4205,10 @@
         <v>0.534</v>
       </c>
       <c r="L89" t="n">
-        <v>37.169</v>
+        <v>44.602</v>
       </c>
       <c r="M89" t="n">
-        <v>32.522</v>
+        <v>39.026</v>
       </c>
     </row>
     <row r="90">
@@ -4252,10 +4252,10 @@
         <v>19.582</v>
       </c>
       <c r="L90" t="n">
-        <v>3.058</v>
+        <v>3.059</v>
       </c>
       <c r="M90" t="n">
-        <v>2.675</v>
+        <v>2.676</v>
       </c>
     </row>
     <row r="91">
@@ -4299,10 +4299,10 @@
         <v>8.75</v>
       </c>
       <c r="L91" t="n">
-        <v>2.596</v>
+        <v>2.597</v>
       </c>
       <c r="M91" t="n">
-        <v>2.271</v>
+        <v>2.272</v>
       </c>
     </row>
     <row r="92">
@@ -4346,10 +4346,10 @@
         <v>40.713</v>
       </c>
       <c r="L92" t="n">
-        <v>3.702</v>
+        <v>3.703</v>
       </c>
       <c r="M92" t="n">
-        <v>3.239</v>
+        <v>3.24</v>
       </c>
     </row>
     <row r="93">
@@ -4393,10 +4393,10 @@
         <v>6.037</v>
       </c>
       <c r="L93" t="n">
-        <v>1.411</v>
+        <v>1.412</v>
       </c>
       <c r="M93" t="n">
-        <v>1.234</v>
+        <v>1.235</v>
       </c>
     </row>
     <row r="94">
@@ -4600,10 +4600,10 @@
         <v>4.886</v>
       </c>
       <c r="L102" t="n">
-        <v>2.415</v>
+        <v>2.418</v>
       </c>
       <c r="M102" t="n">
-        <v>2.113</v>
+        <v>2.115</v>
       </c>
     </row>
     <row r="103">
@@ -4647,7 +4647,7 @@
         <v>30.038</v>
       </c>
       <c r="L103" t="n">
-        <v>3.528</v>
+        <v>3.529</v>
       </c>
       <c r="M103" t="n">
         <v>3.087</v>
@@ -4694,10 +4694,10 @@
         <v>0.982</v>
       </c>
       <c r="L104" t="n">
-        <v>2.577</v>
+        <v>2.594</v>
       </c>
       <c r="M104" t="n">
-        <v>2.254</v>
+        <v>2.269</v>
       </c>
     </row>
     <row r="105">
@@ -4741,10 +4741,10 @@
         <v>3.5</v>
       </c>
       <c r="L105" t="n">
-        <v>1.215</v>
+        <v>1.216</v>
       </c>
       <c r="M105" t="n">
-        <v>1.063</v>
+        <v>1.064</v>
       </c>
     </row>
     <row r="106">
@@ -4788,10 +4788,10 @@
         <v>23.248</v>
       </c>
       <c r="L106" t="n">
-        <v>3.436</v>
+        <v>3.437</v>
       </c>
       <c r="M106" t="n">
-        <v>3.006</v>
+        <v>3.007</v>
       </c>
     </row>
     <row r="107">
@@ -4835,10 +4835,10 @@
         <v>10.626</v>
       </c>
       <c r="L107" t="n">
-        <v>2.789</v>
+        <v>2.791</v>
       </c>
       <c r="M107" t="n">
-        <v>2.44</v>
+        <v>2.442</v>
       </c>
     </row>
     <row r="108">
@@ -4882,10 +4882,10 @@
         <v>6.378</v>
       </c>
       <c r="L108" t="n">
-        <v>2.754</v>
+        <v>2.757</v>
       </c>
       <c r="M108" t="n">
-        <v>2.409</v>
+        <v>2.412</v>
       </c>
     </row>
     <row r="109">
@@ -4996,10 +4996,10 @@
         <v>3.132</v>
       </c>
       <c r="L111" t="n">
-        <v>1.378</v>
+        <v>1.379</v>
       </c>
       <c r="M111" t="n">
-        <v>1.205</v>
+        <v>1.206</v>
       </c>
     </row>
     <row r="112">
@@ -5043,10 +5043,10 @@
         <v>109.488</v>
       </c>
       <c r="L112" t="n">
-        <v>4.442</v>
+        <v>4.443</v>
       </c>
       <c r="M112" t="n">
-        <v>3.886</v>
+        <v>3.887</v>
       </c>
     </row>
     <row r="113">
@@ -5090,10 +5090,10 @@
         <v>2.283</v>
       </c>
       <c r="L113" t="n">
-        <v>3.825</v>
+        <v>3.841</v>
       </c>
       <c r="M113" t="n">
-        <v>3.346</v>
+        <v>3.36</v>
       </c>
     </row>
     <row r="114">
@@ -5137,10 +5137,10 @@
         <v>17.071</v>
       </c>
       <c r="L114" t="n">
-        <v>3.132</v>
+        <v>3.134</v>
       </c>
       <c r="M114" t="n">
-        <v>2.74</v>
+        <v>2.742</v>
       </c>
     </row>
     <row r="115">
@@ -5184,10 +5184,10 @@
         <v>12.153</v>
       </c>
       <c r="L115" t="n">
-        <v>2.862</v>
+        <v>2.864</v>
       </c>
       <c r="M115" t="n">
-        <v>2.504</v>
+        <v>2.506</v>
       </c>
     </row>
     <row r="116">
@@ -5231,7 +5231,7 @@
         <v>3.535</v>
       </c>
       <c r="L116" t="n">
-        <v>1.072</v>
+        <v>1.073</v>
       </c>
       <c r="M116" t="n">
         <v>0.9379999999999999</v>
@@ -5278,10 +5278,10 @@
         <v>25.213</v>
       </c>
       <c r="L117" t="n">
-        <v>3.498</v>
+        <v>3.499</v>
       </c>
       <c r="M117" t="n">
-        <v>3.06</v>
+        <v>3.061</v>
       </c>
     </row>
     <row r="118">
@@ -5325,10 +5325,10 @@
         <v>4.488</v>
       </c>
       <c r="L118" t="n">
-        <v>2.782</v>
+        <v>2.786</v>
       </c>
       <c r="M118" t="n">
-        <v>2.434</v>
+        <v>2.437</v>
       </c>
     </row>
     <row r="119">
@@ -5419,10 +5419,10 @@
         <v>6.265</v>
       </c>
       <c r="L120" t="n">
-        <v>2.402</v>
+        <v>2.404</v>
       </c>
       <c r="M120" t="n">
-        <v>2.101</v>
+        <v>2.103</v>
       </c>
     </row>
     <row r="121">
@@ -5489,10 +5489,10 @@
         <v>3.399</v>
       </c>
       <c r="L122" t="n">
-        <v>3.527</v>
+        <v>3.536</v>
       </c>
       <c r="M122" t="n">
-        <v>3.086</v>
+        <v>3.094</v>
       </c>
     </row>
     <row r="123">
@@ -5536,10 +5536,10 @@
         <v>1.398</v>
       </c>
       <c r="L123" t="n">
-        <v>11.436</v>
+        <v>11.665</v>
       </c>
       <c r="M123" t="n">
-        <v>10.006</v>
+        <v>10.206</v>
       </c>
     </row>
     <row r="124">
@@ -5583,10 +5583,10 @@
         <v>26.95</v>
       </c>
       <c r="L124" t="n">
-        <v>3.596</v>
+        <v>3.597</v>
       </c>
       <c r="M124" t="n">
-        <v>3.146</v>
+        <v>3.147</v>
       </c>
     </row>
     <row r="125">
@@ -5630,10 +5630,10 @@
         <v>13.982</v>
       </c>
       <c r="L125" t="n">
-        <v>3.031</v>
+        <v>3.033</v>
       </c>
       <c r="M125" t="n">
-        <v>2.652</v>
+        <v>2.653</v>
       </c>
     </row>
     <row r="126">
@@ -5747,10 +5747,10 @@
         <v>4.103</v>
       </c>
       <c r="L128" t="n">
-        <v>3.084</v>
+        <v>3.089</v>
       </c>
       <c r="M128" t="n">
-        <v>2.698</v>
+        <v>2.702</v>
       </c>
     </row>
     <row r="129">
@@ -5794,10 +5794,10 @@
         <v>15.338</v>
       </c>
       <c r="L129" t="n">
-        <v>3.173</v>
+        <v>3.175</v>
       </c>
       <c r="M129" t="n">
-        <v>2.776</v>
+        <v>2.778</v>
       </c>
     </row>
     <row r="130">
@@ -5864,10 +5864,10 @@
         <v>3.836</v>
       </c>
       <c r="L131" t="n">
-        <v>0.958</v>
+        <v>0.959</v>
       </c>
       <c r="M131" t="n">
-        <v>0.838</v>
+        <v>0.839</v>
       </c>
     </row>
     <row r="132">
@@ -5911,10 +5911,10 @@
         <v>0.948</v>
       </c>
       <c r="L132" t="n">
-        <v>2.3</v>
+        <v>2.313</v>
       </c>
       <c r="M132" t="n">
-        <v>2.012</v>
+        <v>2.023</v>
       </c>
     </row>
     <row r="133">
@@ -5958,10 +5958,10 @@
         <v>9.029999999999999</v>
       </c>
       <c r="L133" t="n">
-        <v>2.648</v>
+        <v>2.65</v>
       </c>
       <c r="M133" t="n">
-        <v>2.317</v>
+        <v>2.318</v>
       </c>
     </row>
     <row r="134">
@@ -6005,10 +6005,10 @@
         <v>26.652</v>
       </c>
       <c r="L134" t="n">
-        <v>3.422</v>
+        <v>3.424</v>
       </c>
       <c r="M134" t="n">
-        <v>2.994</v>
+        <v>2.996</v>
       </c>
     </row>
     <row r="135">
@@ -6099,10 +6099,10 @@
         <v>4.116</v>
       </c>
       <c r="L136" t="n">
-        <v>0.987</v>
+        <v>0.988</v>
       </c>
       <c r="M136" t="n">
-        <v>0.863</v>
+        <v>0.864</v>
       </c>
     </row>
     <row r="137">
@@ -6146,10 +6146,10 @@
         <v>15.47</v>
       </c>
       <c r="L137" t="n">
-        <v>2.979</v>
+        <v>2.98</v>
       </c>
       <c r="M137" t="n">
-        <v>2.606</v>
+        <v>2.607</v>
       </c>
     </row>
     <row r="138">
@@ -6193,10 +6193,10 @@
         <v>40.691</v>
       </c>
       <c r="L138" t="n">
-        <v>3.801</v>
+        <v>3.802</v>
       </c>
       <c r="M138" t="n">
-        <v>3.325</v>
+        <v>3.326</v>
       </c>
     </row>
     <row r="139">
@@ -6240,10 +6240,10 @@
         <v>3.893</v>
       </c>
       <c r="L139" t="n">
-        <v>2.303</v>
+        <v>2.307</v>
       </c>
       <c r="M139" t="n">
-        <v>2.015</v>
+        <v>2.018</v>
       </c>
     </row>
     <row r="140">
@@ -6287,10 +6287,10 @@
         <v>3.141</v>
       </c>
       <c r="L140" t="n">
-        <v>3.412</v>
+        <v>3.421</v>
       </c>
       <c r="M140" t="n">
-        <v>2.985</v>
+        <v>2.993</v>
       </c>
     </row>
     <row r="141">
@@ -6334,7 +6334,7 @@
         <v>28.695</v>
       </c>
       <c r="L141" t="n">
-        <v>3.456</v>
+        <v>3.457</v>
       </c>
       <c r="M141" t="n">
         <v>3.024</v>
@@ -6381,10 +6381,10 @@
         <v>9.887</v>
       </c>
       <c r="L142" t="n">
-        <v>2.724</v>
+        <v>2.726</v>
       </c>
       <c r="M142" t="n">
-        <v>2.383</v>
+        <v>2.385</v>
       </c>
     </row>
     <row r="143">
@@ -6428,10 +6428,10 @@
         <v>111.667</v>
       </c>
       <c r="L143" t="n">
-        <v>4.375</v>
+        <v>4.376</v>
       </c>
       <c r="M143" t="n">
-        <v>3.828</v>
+        <v>3.829</v>
       </c>
     </row>
     <row r="144">
@@ -6475,10 +6475,10 @@
         <v>16.891</v>
       </c>
       <c r="L144" t="n">
-        <v>3.078</v>
+        <v>3.079</v>
       </c>
       <c r="M144" t="n">
-        <v>2.693</v>
+        <v>2.694</v>
       </c>
     </row>
     <row r="145">
@@ -6522,10 +6522,10 @@
         <v>4.97</v>
       </c>
       <c r="L145" t="n">
-        <v>2.601</v>
+        <v>2.604</v>
       </c>
       <c r="M145" t="n">
-        <v>2.275</v>
+        <v>2.278</v>
       </c>
     </row>
     <row r="146">
@@ -6569,10 +6569,10 @@
         <v>30.458</v>
       </c>
       <c r="L146" t="n">
-        <v>3.486</v>
+        <v>3.487</v>
       </c>
       <c r="M146" t="n">
-        <v>3.05</v>
+        <v>3.051</v>
       </c>
     </row>
     <row r="147">
@@ -6663,10 +6663,10 @@
         <v>3.867</v>
       </c>
       <c r="L148" t="n">
-        <v>2.855</v>
+        <v>2.86</v>
       </c>
       <c r="M148" t="n">
-        <v>2.498</v>
+        <v>2.502</v>
       </c>
     </row>
     <row r="149">
@@ -6757,10 +6757,10 @@
         <v>52.653</v>
       </c>
       <c r="L150" t="n">
-        <v>3.97</v>
+        <v>3.971</v>
       </c>
       <c r="M150" t="n">
-        <v>3.473</v>
+        <v>3.474</v>
       </c>
     </row>
     <row r="151">
@@ -6804,10 +6804,10 @@
         <v>11.908</v>
       </c>
       <c r="L151" t="n">
-        <v>2.779</v>
+        <v>2.781</v>
       </c>
       <c r="M151" t="n">
-        <v>2.431</v>
+        <v>2.433</v>
       </c>
     </row>
     <row r="152">
@@ -6851,10 +6851,10 @@
         <v>6.142</v>
       </c>
       <c r="L152" t="n">
-        <v>2.461</v>
+        <v>2.463</v>
       </c>
       <c r="M152" t="n">
-        <v>2.153</v>
+        <v>2.155</v>
       </c>
     </row>
     <row r="153">
@@ -6898,10 +6898,10 @@
         <v>18.83</v>
       </c>
       <c r="L153" t="n">
-        <v>3.102</v>
+        <v>3.103</v>
       </c>
       <c r="M153" t="n">
-        <v>2.714</v>
+        <v>2.715</v>
       </c>
     </row>
     <row r="154">
@@ -6945,10 +6945,10 @@
         <v>67.961</v>
       </c>
       <c r="L154" t="n">
-        <v>2.522</v>
+        <v>2.523</v>
       </c>
       <c r="M154" t="n">
-        <v>2.206</v>
+        <v>2.207</v>
       </c>
     </row>
     <row r="155">
@@ -6992,10 +6992,10 @@
         <v>26.509</v>
       </c>
       <c r="L155" t="n">
-        <v>2.984</v>
+        <v>2.985</v>
       </c>
       <c r="M155" t="n">
-        <v>2.61</v>
+        <v>2.611</v>
       </c>
     </row>
     <row r="156">
@@ -7039,10 +7039,10 @@
         <v>10.692</v>
       </c>
       <c r="L156" t="n">
-        <v>1.79</v>
+        <v>1.791</v>
       </c>
       <c r="M156" t="n">
-        <v>1.566</v>
+        <v>1.567</v>
       </c>
     </row>
     <row r="157">
@@ -7086,10 +7086,10 @@
         <v>8.206</v>
       </c>
       <c r="L157" t="n">
-        <v>1.821</v>
+        <v>1.822</v>
       </c>
       <c r="M157" t="n">
-        <v>1.593</v>
+        <v>1.594</v>
       </c>
     </row>
     <row r="158">
@@ -7133,10 +7133,10 @@
         <v>1.654</v>
       </c>
       <c r="L158" t="n">
-        <v>0.923</v>
+        <v>0.924</v>
       </c>
       <c r="M158" t="n">
-        <v>0.8070000000000001</v>
+        <v>0.8080000000000001</v>
       </c>
     </row>
     <row r="159">
@@ -7227,10 +7227,10 @@
         <v>7.459</v>
       </c>
       <c r="L160" t="n">
-        <v>2.479</v>
+        <v>2.481</v>
       </c>
       <c r="M160" t="n">
-        <v>2.169</v>
+        <v>2.17</v>
       </c>
     </row>
   </sheetData>

--- a/btp_dati.xlsx
+++ b/btp_dati.xlsx
@@ -428,17 +428,17 @@
   <dimension ref="A1:M160"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14.4" customWidth="1" min="1" max="1"/>
-    <col width="33.6" customWidth="1" min="2" max="2"/>
-    <col width="8.4" customWidth="1" min="3" max="3"/>
-    <col width="9.6" customWidth="1" min="4" max="4"/>
-    <col width="9.6" customWidth="1" min="5" max="5"/>
-    <col width="19.2" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="33" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="19" customWidth="1" min="6" max="6"/>
     <col width="24" customWidth="1" min="7" max="7"/>
-    <col width="15.6" customWidth="1" min="8" max="8"/>
-    <col width="15.6" customWidth="1" min="9" max="9"/>
-    <col width="25.2" customWidth="1" min="10" max="10"/>
-    <col width="25.2" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="25" customWidth="1" min="10" max="10"/>
+    <col width="25" customWidth="1" min="11" max="11"/>
     <col width="24" customWidth="1" min="12" max="12"/>
     <col width="24" customWidth="1" min="13" max="13"/>
   </cols>

--- a/btp_dati.xlsx
+++ b/btp_dati.xlsx
@@ -428,7 +428,7 @@
   <dimension ref="A1:M160"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="121" customWidth="1" min="1" max="1"/>
     <col width="33" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
@@ -513,12 +513,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>IT0001086567</t>
+          <t>IT0001086567 -Btp-1nv26      7,25%Ultimo: 106,31Cedola: 3,625Scadenza: 01/11/2026IT0001086567</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Btp-1nv26 7,25%</t>
+          <t>Btp-1nv26      7,25%</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -560,12 +560,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>IT0001174611</t>
+          <t>IT0001174611 -Btp-1nv27       6,5%Ultimo: 109,37Cedola: 3,25Scadenza: 01/11/2027IT0001174611</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Btp-1nv27 6,5%</t>
+          <t>Btp-1nv27       6,5%</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -607,12 +607,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>IT0001278511</t>
+          <t>IT0001278511 -Btp-1nv29      5,25%Ultimo: 111,14Cedola: 2,625Scadenza: 01/11/2029IT0001278511</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Btp-1nv29 5,25%</t>
+          <t>Btp-1nv29      5,25%</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -654,12 +654,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>IT0001444378</t>
+          <t>IT0001444378 -Btp-1mg31         6%Ultimo: 117,05Cedola: 3,00Scadenza: 01/05/2031IT0001444378</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Btp-1mg31 6%</t>
+          <t>Btp-1mg31         6%</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -701,12 +701,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>IT0003256820</t>
+          <t>IT0003256820 -Btp-1fb33      5,75%Ultimo: 117,44Cedola: 2,875Scadenza: 01/02/2033IT0003256820</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Btp-1fb33 5,75%</t>
+          <t>Btp-1fb33      5,75%</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -748,12 +748,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>IT0003535157</t>
+          <t>IT0003535157 -Btp-1ag34         5%Ultimo: 113,20Cedola: 2,50Scadenza: 01/08/2034IT0003535157</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Btp-1ag34 5%</t>
+          <t>Btp-1ag34         5%</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -795,12 +795,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>IT0003745541</t>
+          <t>IT0003745541 -Btpi-15st35    2,35%Ultimo: 108,13Cedola: 1,175Scadenza: 15/09/2035IT0003745541</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Btpi-15st35 2,35%</t>
+          <t>Btpi-15st35    2,35%</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -842,12 +842,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>IT0003934657</t>
+          <t>IT0003934657 -Btp-1fb37         4%Ultimo: 104,34Cedola: 2,00Scadenza: 01/02/2037IT0003934657</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Btp-1fb37 4%</t>
+          <t>Btp-1fb37         4%</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -889,12 +889,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>IT0004286966</t>
+          <t>IT0004286966 -Btp-1ag39         5%Ultimo: 113,50Cedola: 2,50Scadenza: 01/08/2039IT0004286966</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Btp-1ag39 5%</t>
+          <t>Btp-1ag39         5%</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -936,7 +936,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>IT0004532559</t>
+          <t>IT0004532559 -Btp-1st40 5%Ultimo: 113,26Cedola: 2,50Scadenza: 01/09/2040IT0004532559</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -983,7 +983,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>IT0004545890</t>
+          <t>IT0004545890 -Btpi-15st41 2,55%Ultimo: 107,78Cedola: 1,275Scadenza: 15/09/2041IT0004545890</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1030,7 +1030,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>IT0004644735</t>
+          <t>IT0004644735 -Btp-1mz26 4,5%Ultimo: 101,368Cedola: 2,25Scadenza: 01/03/2026IT0004644735</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1077,7 +1077,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>IT0004735152</t>
+          <t>IT0004735152 -Btpi-15st26 3,1%Ultimo: 103,00Cedola: 1,55Scadenza: 15/09/2026IT0004735152</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1124,7 +1124,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>IT0004848443</t>
+          <t>IT0004848443 -Btp Coupon Strip Zc Nv26 EurUltimo: 97,87Cedola:Scadenza: 01/11/2026IT0004848443</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1147,7 +1147,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>IT0004848476</t>
+          <t>IT0004848476 -Btp Coupon Strip Zc Nv27 EurUltimo: 95,49Cedola:Scadenza: 01/11/2027IT0004848476</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1170,7 +1170,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>IT0004848484</t>
+          <t>IT0004848484 -Btp Coupon Strip Zc Nv29 EurUltimo: 90,42Cedola:Scadenza: 01/11/2029IT0004848484</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1193,7 +1193,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>IT0004848492</t>
+          <t>IT0004848492 -Btp Coupon Strip Zc Mg31 EurUltimo: 85,68Cedola:Scadenza: 01/05/2031IT0004848492</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1216,7 +1216,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>IT0004848534</t>
+          <t>IT0004848534 -Btpstripital Zc Feb33 EurUltimo: 79,57Cedola:Scadenza: 01/02/2033IT0004848534</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1239,7 +1239,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>IT0004848641</t>
+          <t>IT0004848641 -Btpstripital Zc Feb37 EurUltimo:Cedola:Scadenza: 01/02/2037IT0004848641</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1259,7 +1259,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>IT0004848690</t>
+          <t>IT0004848690 -Btpstripital Zc Ago39Ultimo:Cedola:Scadenza: 01/08/2039IT0004848690</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1279,7 +1279,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>IT0004889033</t>
+          <t>IT0004889033 -Btp Tf 4,75% St28 EurUltimo: 107,17Cedola: 2,375Scadenza: 01/09/2028IT0004889033</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1326,7 +1326,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>IT0004923998</t>
+          <t>IT0004923998 -Btp Tf 4,75% St44 EurUltimo: 109,78Cedola: 2,375Scadenza: 01/09/2044IT0004923998</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1373,7 +1373,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>IT0004976525</t>
+          <t>IT0004976525 -Btp Coupon Strip Zc St28 EurUltimo: 93,41Cedola:Scadenza: 01/09/2028IT0004976525</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1396,7 +1396,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>IT0004976558</t>
+          <t>IT0004976558 -Btp Coupon Strip Zc Mz30 EurUltimo: 89,16Cedola:Scadenza: 01/03/2030IT0004976558</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1419,7 +1419,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>IT0004976590</t>
+          <t>IT0004976590 -Btpstripital Zc Mar32Ultimo: 83,11Cedola:Scadenza: 01/03/2032IT0004976590</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1442,7 +1442,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>IT0004976632</t>
+          <t>IT0004976632 -Btpstripital Zc Mar34Ultimo:Cedola:Scadenza: 01/03/2034IT0004976632</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1462,7 +1462,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>IT0004976657</t>
+          <t>IT0004976657 -Btpstripital Zc Mar35 EurUltimo:Cedola:Scadenza: 01/03/2035IT0004976657</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1482,7 +1482,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>IT0004976681</t>
+          <t>IT0004976681 -Btpstripital Zc Sep36 EurUltimo:Cedola:Scadenza: 01/09/2036IT0004976681</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1502,7 +1502,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>IT0004976715</t>
+          <t>IT0004976715 -Btpstripital Zc Mar38Ultimo: 62,47Cedola:Scadenza: 01/03/2038IT0004976715</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1525,7 +1525,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>IT0005024234</t>
+          <t>IT0005024234 -Btp Tf 3,50% Mz30 EurUltimo: 104,03Cedola: 1,75Scadenza: 01/03/2030IT0005024234</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1572,7 +1572,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>IT0005083057</t>
+          <t>IT0005083057 -Btp Tf 3,25% St46 EurUltimo: 88,26Cedola: 1,625Scadenza: 01/09/2046IT0005083057</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1619,7 +1619,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>IT0005094088</t>
+          <t>IT0005094088 -Btp Tf 1,65% Mz32 EurUltimo: 92,38Cedola: 0,825Scadenza: 01/03/2032IT0005094088</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1666,7 +1666,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>IT0005127086</t>
+          <t>IT0005127086 -Btp Tf 2,00% Dc25 EurUltimo: 100,007Cedola: 1,00Scadenza: 01/12/2025IT0005127086</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1713,7 +1713,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>IT0005138828</t>
+          <t>IT0005138828 -Btpi Tf 1,25% St32 EurUltimo: 100,28Cedola: 0,625Scadenza: 15/09/2032IT0005138828</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1760,7 +1760,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>IT0005162828</t>
+          <t>IT0005162828 -Btp Tf 2,7% Mz47 EurUltimo: 80,33Cedola: 1,35Scadenza: 01/03/2047IT0005162828</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1807,7 +1807,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>IT0005170839</t>
+          <t>IT0005170839 -Btp Tf 1,60% Gn26 EurUltimo: 99,727Cedola: 0,80Scadenza: 01/06/2026IT0005170839</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1854,7 +1854,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>IT0005177909</t>
+          <t>IT0005177909 -Btp Tf 2,25% St36 EurUltimo: 88,43Cedola: 1,125Scadenza: 01/09/2036IT0005177909</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1901,7 +1901,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>IT0005210650</t>
+          <t>IT0005210650 -Btp Tf 1.25% Dc26 EurUltimo: 99,14Cedola: 0,625Scadenza: 01/12/2026IT0005210650</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1948,7 +1948,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>IT0005217390</t>
+          <t>IT0005217390 -Btp Tf 2,8% Mz67 EurUltimo: 71,49Cedola: 1,40Scadenza: 01/03/2067IT0005217390</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1995,7 +1995,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>IT0005240350</t>
+          <t>IT0005240350 -Btp Tf 2,45% St33 EurUltimo: 95,04Cedola: 1,225Scadenza: 01/09/2033IT0005240350</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2042,7 +2042,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>IT0005240830</t>
+          <t>IT0005240830 -Btp Tf 2,20% Gn27 EurUltimo: 100,29Cedola: 1,10Scadenza: 01/06/2027IT0005240830</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2089,7 +2089,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>IT0005246134</t>
+          <t>IT0005246134 -Btpi Tf 1,30% Mg28 EurUltimo:Cedola: 0,65Scadenza: 15/05/2028IT0005246134</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2118,7 +2118,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>IT0005273013</t>
+          <t>IT0005273013 -Btp Tf 3,45% Mz48 EurUltimo: 90,32Cedola: 1,725Scadenza: 01/03/2048IT0005273013</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2165,7 +2165,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>IT0005274805</t>
+          <t>IT0005274805 -Btp Tf 2,05% Ag27 EurUltimo: 99,95Cedola: 1,025Scadenza: 01/08/2027IT0005274805</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2212,7 +2212,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>IT0005321325</t>
+          <t>IT0005321325 -Btp Tf 2,95% St38 EurUltimo: 92,32Cedola: 1,475Scadenza: 01/09/2038IT0005321325</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2259,7 +2259,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>IT0005323032</t>
+          <t>IT0005323032 -Btp Tf 2,00% Fb28 EurUltimo: 99,63Cedola: 1,00Scadenza: 01/02/2028IT0005323032</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2306,7 +2306,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>IT0005332835</t>
+          <t>IT0005332835 -Btp Italia Mg26 EurUltimo: 99,90Cedola: 0,275Scadenza: 21/05/2026IT0005332835</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2353,7 +2353,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>IT0005340929</t>
+          <t>IT0005340929 -Btp Tf 2,80% Dc28 EurUltimo: 101,55Cedola: 1,40Scadenza: 01/12/2028IT0005340929</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2400,7 +2400,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>IT0005345183</t>
+          <t>IT0005345183 -Btp Tf 2.50% Nv25 EurUltimo: 100,116Cedola: 1,25Scadenza: 15/11/2025IT0005345183</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2447,7 +2447,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>IT0005358806</t>
+          <t>IT0005358806 -Btp Tf 3,35% Mz35 EurUltimo: 100,06Cedola: 1,675Scadenza: 01/03/2035IT0005358806</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2494,7 +2494,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>IT0005363111</t>
+          <t>IT0005363111 -Btp Tf 3,85% St49 EurUltimo: 95,50Cedola: 1,925Scadenza: 01/09/2049IT0005363111</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2541,7 +2541,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>IT0005365165</t>
+          <t>IT0005365165 -Btp Tf 3,00% Ag29 EurUltimo: 102,10Cedola: 1,50Scadenza: 01/08/2029IT0005365165</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2588,7 +2588,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>IT0005370306</t>
+          <t>IT0005370306 -Btp Tf 2,10% Lg26 EurUltimo: 100,106Cedola: 1,05Scadenza: 15/07/2026IT0005370306</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2635,7 +2635,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>IT0005377152</t>
+          <t>IT0005377152 -Btp Tf 3,1% Mz40 EurUltimo: 92,09Cedola: 1,55Scadenza: 01/03/2040IT0005377152</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2682,7 +2682,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>IT0005383309</t>
+          <t>IT0005383309 -Btp Tf 1,35% Ap30 EurUltimo: 94,68Cedola: 0,675Scadenza: 01/04/2030IT0005383309</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2729,7 +2729,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>IT0005387052</t>
+          <t>IT0005387052 -Btpi Tf 0,4% Mg30 EurUltimo: 97,38Cedola: 0,20Scadenza: 15/05/2030IT0005387052</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2776,7 +2776,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>IT0005388175</t>
+          <t>IT0005388175 -Btp Italia Ot27 EurUltimo: 99,88Cedola: 0,325Scadenza: 28/10/2027IT0005388175</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2823,7 +2823,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>IT0005390874</t>
+          <t>IT0005390874 -Btp Tf 0,85% Ge27 EurUltimo: 98,43Cedola: 0,425Scadenza: 15/01/2027IT0005390874</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2870,7 +2870,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>IT0005398406</t>
+          <t>IT0005398406 -Btp Tf 2,45% St50 EurUltimo: 73,43Cedola: 1,225Scadenza: 01/09/2050IT0005398406</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2917,7 +2917,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>IT0005402117</t>
+          <t>IT0005402117 -Btp Tf 1,45% Mz36 EurUltimo: 82,06Cedola: 0,725Scadenza: 01/03/2036IT0005402117</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2964,7 +2964,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>IT0005403396</t>
+          <t>IT0005403396 -Btp Tf 0,95% Ag30 EurUltimo: 92,11Cedola: 0,475Scadenza: 01/08/2030IT0005403396</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -3011,7 +3011,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>IT0005413171</t>
+          <t>IT0005413171 -Btp Tf 1,65% Dc30 EurUltimo: 94,69Cedola: 0,825Scadenza: 01/12/2030IT0005413171</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -3058,7 +3058,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>IT0005415291</t>
+          <t>IT0005415291 -Btp Futura Lg30 EurUltimo: 94,01Cedola: 0,65Scadenza: 14/07/2030IT0005415291</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -3105,7 +3105,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>IT0005415416</t>
+          <t>IT0005415416 -Btpi Tf 0,65% Mg26 EurUltimo:Cedola: 0,325Scadenza: 15/05/2026IT0005415416</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -3134,7 +3134,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>IT0005416570</t>
+          <t>IT0005416570 -Btp Tf 0,95% St27 EurUltimo: 97,68Cedola: 0,475Scadenza: 15/09/2027IT0005416570</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -3181,7 +3181,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>IT0005419848</t>
+          <t>IT0005419848 -Btp Tf 0,50% Fb26 EurUltimo: 99,31Cedola: 0,25Scadenza: 01/02/2026IT0005419848</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -3228,7 +3228,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>IT0005421703</t>
+          <t>IT0005421703 -Btp Tf 1,8% Mz41 EurUltimo: 75,76Cedola: 0,90Scadenza: 01/03/2041IT0005421703</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -3275,7 +3275,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>IT0005422891</t>
+          <t>IT0005422891 -Btp Tf 0,90% Ap31 EurUltimo: 90,18Cedola: 0,45Scadenza: 01/04/2031IT0005422891</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -3322,7 +3322,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>IT0005425233</t>
+          <t>IT0005425233 -Btp Tf 1,7% St51 EurUltimo: 61,64Cedola: 0,85Scadenza: 01/09/2051IT0005425233</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -3369,7 +3369,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>IT0005425761</t>
+          <t>IT0005425761 -Btp Futura Nv28 EurUltimo: 95,41Cedola: 0,30Scadenza: 17/11/2028IT0005425761</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3416,7 +3416,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>IT0005433195</t>
+          <t>IT0005433195 -Btp Tf 0,95% Mz37 EurUltimo: 75,25Cedola: 0,475Scadenza: 01/03/2037IT0005433195</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3463,7 +3463,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>IT0005433690</t>
+          <t>IT0005433690 -Btp Tf 0,25% Mz28 EurUltimo: 95,14Cedola: 0,125Scadenza: 15/03/2028IT0005433690</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3510,7 +3510,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>IT0005436693</t>
+          <t>IT0005436693 -Btp Tf 0,6% Ag31 EurUltimo: 87,75Cedola: 0,30Scadenza: 01/08/2031IT0005436693</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3557,7 +3557,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>IT0005436701</t>
+          <t>IT0005436701 -Btpi Tf 0,15% Mg51 EurUltimo: 61,09Cedola: 0,075Scadenza: 15/05/2051IT0005436701</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3604,7 +3604,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>IT0005437147</t>
+          <t>IT0005437147 -Btp Tf 0% Ap26 EurUltimo: 98,794Cedola:Scadenza: 01/04/2026IT0005437147</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3627,7 +3627,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>IT0005438004</t>
+          <t>IT0005438004 -Btpgreen 1,5%Ap45eurUltimo: 66,23Cedola: 0,75Scadenza: 30/04/2045IT0005438004</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3674,7 +3674,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>IT0005441883</t>
+          <t>IT0005441883 -Btp Tf 2,15% Mz72 EurUltimo: 58,70Cedola: 1,075Scadenza: 01/03/2072IT0005441883</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3721,7 +3721,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>IT0005442097</t>
+          <t>IT0005442097 -Btp Futura Ap37 EurUltimo: 79,30Cedola: 0,60Scadenza: 27/04/2037IT0005442097</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3768,7 +3768,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>IT0005445306</t>
+          <t>IT0005445306 -Btp Tf 0,5% Lg28 EurUltimo: 95,05Cedola: 0,25Scadenza: 15/07/2028IT0005445306</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3815,7 +3815,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>IT0005449969</t>
+          <t>IT0005449969 -Btp Tf 0,95% Dc31 EurUltimo: 88,85Cedola: 0,475Scadenza: 01/12/2031IT0005449969</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3862,7 +3862,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>IT0005454241</t>
+          <t>IT0005454241 -Btp Tf 0% Ag26 EurUltimo: 98,272Cedola:Scadenza: 01/08/2026IT0005454241</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3885,7 +3885,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>IT0005466013</t>
+          <t>IT0005466013 -Btp Tf 0,95% Gn32 EurUltimo: 87,61Cedola: 0,475Scadenza: 01/06/2032IT0005466013</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3932,7 +3932,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>IT0005466351</t>
+          <t>IT0005466351 -Btp Futura Nv33 EurUltimo: 87,53Cedola: 0,375Scadenza: 16/11/2033IT0005466351</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3979,7 +3979,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>IT0005467482</t>
+          <t>IT0005467482 -Btp Tf 0,45% Fb29 EurUltimo: 93,51Cedola: 0,225Scadenza: 15/02/2029IT0005467482</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -4026,7 +4026,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>IT0005480980</t>
+          <t>IT0005480980 -Btp Tf 2,15% St52 EurUltimo: 67,47Cedola: 1,075Scadenza: 01/09/2052IT0005480980</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -4073,7 +4073,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>IT0005482994</t>
+          <t>IT0005482994 -Btpi Tf 0,1% Mg33 EurUltimo: 90,42Cedola: 0,05Scadenza: 15/05/2033IT0005482994</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -4120,7 +4120,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>IT0005484552</t>
+          <t>IT0005484552 -Btp Tf 1,1% Ap27 EurUltimo: 98,45Cedola: 0,55Scadenza: 01/04/2027IT0005484552</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -4167,7 +4167,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>IT0005493298</t>
+          <t>IT0005493298 -Btp Tf 1,2% Ag25 EurUltimo: 99,989Cedola: 0,60Scadenza: 15/08/2025IT0005493298</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -4214,7 +4214,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>IT0005494239</t>
+          <t>IT0005494239 -Btp Tf 2,5% Dc32 EurUltimo: 96,37Cedola: 1,25Scadenza: 01/12/2032IT0005494239</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -4261,7 +4261,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>IT0005495731</t>
+          <t>IT0005495731 -Btp Tf 2,80% Gn29 EurUltimo: 101,20Cedola: 1,40Scadenza: 15/06/2029IT0005495731</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -4308,7 +4308,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>IT0005496770</t>
+          <t>IT0005496770 -Btp Tf 3,25% Mz38 EurUltimo: 95,72Cedola: 1,625Scadenza: 01/03/2038IT0005496770</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -4355,7 +4355,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>IT0005497000</t>
+          <t>IT0005497000 -Btp Italia Gn30 EurUltimo: 101,10Cedola: 0,80Scadenza: 28/06/2030IT0005497000</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -4402,7 +4402,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>IT0005498685</t>
+          <t>IT0005498685 -Btpstripital Zc Dec25 EurUltimo:Cedola:Scadenza: 15/12/2025IT0005498685</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -4422,7 +4422,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>IT0005498693</t>
+          <t>IT0005498693 -Btpstripital Zc Jun26 EurUltimo:Cedola:Scadenza: 15/06/2026IT0005498693</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -4442,7 +4442,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>IT0005498701</t>
+          <t>IT0005498701 -Btpstripital Zc Dec26 EurUltimo:Cedola:Scadenza: 15/12/2026IT0005498701</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -4462,7 +4462,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>IT0005498719</t>
+          <t>IT0005498719 -Btpstripital Zc Jun27 EurUltimo:Cedola:Scadenza: 15/06/2027IT0005498719</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -4482,7 +4482,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>IT0005498727</t>
+          <t>IT0005498727 -Btpstripital Zc Dec27 EurUltimo:Cedola:Scadenza: 15/12/2027IT0005498727</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -4502,7 +4502,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>IT0005498735</t>
+          <t>IT0005498735 -Btpstripital Zc Jun28 EurUltimo:Cedola:Scadenza: 15/06/2028IT0005498735</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -4522,7 +4522,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>IT0005498743</t>
+          <t>IT0005498743 -Btpstripital Zc Dec28 EurUltimo:Cedola:Scadenza: 15/12/2028IT0005498743</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -4542,7 +4542,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>IT0005498750</t>
+          <t>IT0005498750 -Btpstripital Zc Jun29 EurUltimo:Cedola:Scadenza: 15/06/2029IT0005498750</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -4562,7 +4562,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>IT0005500068</t>
+          <t>IT0005500068 -Btp Tf 2,65% Dc27 EurUltimo: 101,04Cedola: 1,325Scadenza: 01/12/2027IT0005500068</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -4609,7 +4609,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>IT0005508590</t>
+          <t>IT0005508590 -Btpgreen 4%Ap35eurUltimo: 105,67Cedola: 2,00Scadenza: 30/04/2035IT0005508590</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -4656,7 +4656,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>IT0005514473</t>
+          <t>IT0005514473 -Btp Tf 3,5% Ge26 EurUltimo: 100,627Cedola: 1,75Scadenza: 15/01/2026IT0005514473</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -4703,7 +4703,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>IT0005517195</t>
+          <t>IT0005517195 -Btp Italia Nv28 EurUltimo: 101,60Cedola: 0,80Scadenza: 22/11/2028IT0005517195</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -4750,7 +4750,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>IT0005518128</t>
+          <t>IT0005518128 -Btp Tf 4,40% Mg33 EurUltimo: 108,63Cedola: 2,20Scadenza: 01/05/2033IT0005518128</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -4797,7 +4797,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>IT0005519787</t>
+          <t>IT0005519787 -Btp Tf 3,85% Dc29 EurUltimo: 105,18Cedola: 1,925Scadenza: 15/12/2029IT0005519787</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -4844,7 +4844,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>IT0005521981</t>
+          <t>IT0005521981 -Btp Tf 3,4% Ap28 EurUltimo: 102,91Cedola: 1,70Scadenza: 01/04/2028IT0005521981</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -4891,7 +4891,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>IT0005526162</t>
+          <t>IT0005526162 -Btpstripital Zc Dec29 EurUltimo:Cedola:Scadenza: 15/12/2029IT0005526162</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -4911,7 +4911,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>IT0005530032</t>
+          <t>IT0005530032 -Btp Tf 4,45% St43 EurUltimo: 105,36Cedola: 2,225Scadenza: 01/09/2043IT0005530032</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -4958,7 +4958,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>IT0005532723</t>
+          <t>IT0005532723 -Btp Italia Mz28 EurUltimo: 102,42Cedola: 1,00Scadenza: 14/03/2028IT0005532723</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -5005,7 +5005,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>IT0005534141</t>
+          <t>IT0005534141 -Btp Tf 4,5% Ot53 EurUltimo: 103,12Cedola: 2,25Scadenza: 01/10/2053IT0005534141</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -5052,7 +5052,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>IT0005538597</t>
+          <t>IT0005538597 -Btp Tf 3,80% Ap26 EurUltimo: 101,19Cedola: 1,90Scadenza: 15/04/2026IT0005538597</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -5099,7 +5099,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>IT0005542359</t>
+          <t>IT0005542359 -Btpgreen 4%Ot31eurUltimo: 106,49Cedola: 2,00Scadenza: 30/10/2031IT0005542359</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -5146,7 +5146,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>IT0005542797</t>
+          <t>IT0005542797 -Btp Tf 3,7% Gn30 EurUltimo: 104,61Cedola: 1,85Scadenza: 15/06/2030IT0005542797</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -5193,7 +5193,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>IT0005543803</t>
+          <t>IT0005543803 -Btpi Tf 1.5% Mg29 EurUltimo: 101,96Cedola: 0,75Scadenza: 15/05/2029IT0005543803</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -5240,7 +5240,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>IT0005544082</t>
+          <t>IT0005544082 -Btp Tf 4,35% Nv33 EurUltimo: 108,16Cedola: 2,175Scadenza: 01/11/2033IT0005544082</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -5287,7 +5287,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>IT0005547408</t>
+          <t>IT0005547408 -Btp Valore Gn27 EurUltimo: 102,87Cedola: 2,00Scadenza: 13/06/2027IT0005547408</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -5334,7 +5334,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>IT0005547812</t>
+          <t>IT0005547812 -Btpi Tf 2,4% Mg39 EurUltimo: 104,30Cedola: 1,20Scadenza: 15/05/2039IT0005547812</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -5381,7 +5381,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>IT0005548315</t>
+          <t>IT0005548315 -Btp Tf 3,8% Ag28 EurUltimo: 104,24Cedola: 1,90Scadenza: 01/08/2028IT0005548315</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -5428,7 +5428,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>IT0005550204</t>
+          <t>IT0005550204 -Btpstripital Zc Ott39Ultimo: 57,85Cedola:Scadenza: 01/10/2039IT0005550204</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -5451,7 +5451,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>IT0005556011</t>
+          <t>IT0005556011 -Btp Tf 3,85% St26 EurUltimo: 101,89Cedola: 1,925Scadenza: 15/09/2026IT0005556011</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -5498,7 +5498,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>IT0005557084</t>
+          <t>IT0005557084 -Btp Tf 3,6% St25 EurUltimo: 100,202Cedola: 1,80Scadenza: 29/09/2025IT0005557084</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -5545,7 +5545,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>IT0005560948</t>
+          <t>IT0005560948 -Btp Tf 4,2% Mz34 EurUltimo: 107,00Cedola: 2,10Scadenza: 01/03/2034IT0005560948</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -5592,7 +5592,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>IT0005561888</t>
+          <t>IT0005561888 -Btp Fx 4% Nov30 EurUltimo: 106,02Cedola: 2,00Scadenza: 15/11/2030IT0005561888</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -5639,7 +5639,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>IT0005565400</t>
+          <t>IT0005565400 -Btp Valore Sc Oct28 EurUltimo: 105,15Cedola: 1,025Scadenza: 10/10/2028IT0005565400</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -5686,7 +5686,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>IT0005566408</t>
+          <t>IT0005566408 -Btp Fx 4.1% Feb29 EurUltimo: 105,55Cedola:Scadenza: 01/02/2029IT0005566408</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -5709,7 +5709,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>IT0005580045</t>
+          <t>IT0005580045 -Btp Fx 2.95% Feb27 EurUltimo: 101,21Cedola: 1,475Scadenza: 15/02/2027IT0005580045</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -5756,7 +5756,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>IT0005580094</t>
+          <t>IT0005580094 -Btp Fx 3.5% Feb31 EurUltimo: 103,47Cedola: 1,75Scadenza: 15/02/2031IT0005580094</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -5803,7 +5803,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>IT0005582421</t>
+          <t>IT0005582421 -Btp Fx 4.15% Oct39 EurUltimo: 103,70Cedola:Scadenza: 01/10/2039IT0005582421</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -5826,7 +5826,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>IT0005583486</t>
+          <t>IT0005583486 -Btp Valore Sc Mz30 EurUltimo: 103,74Cedola: 0,8125Scadenza: 05/03/2030IT0005583486</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -5873,7 +5873,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>IT0005584302</t>
+          <t>IT0005584302 -Btp Fx 3.2% Jan26 EurUltimo: 100,516Cedola: 1,60Scadenza: 28/01/2026IT0005584302</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -5920,7 +5920,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>IT0005584849</t>
+          <t>IT0005584849 -Btp Fx 3.35% Jul29 EurUltimo: 103,08Cedola: 1,675Scadenza: 01/07/2029IT0005584849</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -5967,7 +5967,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>IT0005584856</t>
+          <t>IT0005584856 -Btp Fx 3.85% Jul34 EurUltimo: 104,19Cedola: 1,925Scadenza: 01/07/2034IT0005584856</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -6014,7 +6014,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>IT0005588881</t>
+          <t>IT0005588881 -Btpi Fx May36 EurUltimo: 99,87Cedola: 0,90Scadenza: 15/05/2036IT0005588881</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -6061,7 +6061,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>IT0005594483</t>
+          <t>IT0005594483 -Btp Valore Sc Mg30 EurUltimo: 103,67Cedola: 0,8375Scadenza: 14/05/2030IT0005594483</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -6108,7 +6108,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>IT0005595803</t>
+          <t>IT0005595803 -Btp Fx 3.45% Jul31 EurUltimo: 103,02Cedola: 1,725Scadenza: 15/07/2031IT0005595803</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -6155,7 +6155,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>IT0005596470</t>
+          <t>IT0005596470 -Btp Green Fx 4.05% Oct37 EurUltimo: 104,12Cedola: 2,025Scadenza: 30/10/2037IT0005596470</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -6202,7 +6202,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>IT0005599904</t>
+          <t>IT0005599904 -Btp Fx 3.45% Jul27 EurUltimo: 102,45Cedola: 1,725Scadenza: 15/07/2027IT0005599904</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -6249,7 +6249,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>IT0005607269</t>
+          <t>IT0005607269 -Btp Fx 3.1% Aug26 EurUltimo: 101,06Cedola: 1,55Scadenza: 28/08/2026IT0005607269</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -6296,7 +6296,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>IT0005607970</t>
+          <t>IT0005607970 -Btp Fx 3.85% Feb35 EurUltimo: 103,78Cedola: 1,925Scadenza: 01/02/2035IT0005607970</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -6343,7 +6343,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>IT0005611055</t>
+          <t>IT0005611055 -Btp Fx 3% Oct29 EurUltimo: 102,20Cedola: 1,50Scadenza: 01/10/2029IT0005611055</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -6390,7 +6390,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>IT0005611741</t>
+          <t>IT0005611741 -Btp Fx 4.3% Oct54 EurUltimo: 99,23Cedola: 2,15Scadenza: 01/10/2054IT0005611741</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -6437,7 +6437,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>IT0005619546</t>
+          <t>IT0005619546 -Btp Fx 3.15% Nov31 EurUltimo: 101,17Cedola: 1,575Scadenza: 15/11/2031IT0005619546</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -6484,7 +6484,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>IT0005622128</t>
+          <t>IT0005622128 -Btp Fx 2.7% Oct27 EurUltimo: 101,07Cedola: 1,35Scadenza: 15/10/2027IT0005622128</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -6531,7 +6531,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>IT0005631590</t>
+          <t>IT0005631590 -Btp Fx 3.65% Aug35 EurUltimo: 101,69Cedola: 1,825Scadenza: 01/08/2035IT0005631590</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -6578,7 +6578,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>IT0005631608</t>
+          <t>IT0005631608 -Btp Green Fx 4.1% Apr46 EurUltimo: 100,66Cedola: 2,05Scadenza: 30/04/2046IT0005631608</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -6625,7 +6625,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>IT0005633794</t>
+          <t>IT0005633794 -Btp Fx 2.55% Feb27 EurUltimo: 100,68Cedola: 1,275Scadenza: 25/02/2027IT0005633794</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -6672,7 +6672,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>IT0005634800</t>
+          <t>IT0005634800 -Btp Piu' Sc Fb33 EurUltimo: 100,74Cedola: 0,7125Scadenza: 25/02/2033IT0005634800</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -6719,7 +6719,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>IT0005635583</t>
+          <t>IT0005635583 -Btp Fx 3.85% Oct40 EurUltimo: 99,50Cedola: 1,925Scadenza: 01/10/2040IT0005635583</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -6766,7 +6766,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>IT0005637399</t>
+          <t>IT0005637399 -Btp Fx 2.95% Jul30 EurUltimo: 101,14Cedola: 1,475Scadenza: 01/07/2030IT0005637399</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -6813,7 +6813,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>IT0005641029</t>
+          <t>IT0005641029 -Btp Fx 2.65% Jun28 EurUltimo: 100,93Cedola: 1,325Scadenza: 15/06/2028IT0005641029</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -6860,7 +6860,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>IT0005647265</t>
+          <t>IT0005647265 -Btp Fx 3.25% Jul32 EurUltimo: 101,23Cedola: 1,625Scadenza: 15/07/2032IT0005647265</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -6907,7 +6907,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>IT0005647273</t>
+          <t>IT0005647273 -Btpi Fx May56 EurUltimo: 101,38Cedola: 1,275Scadenza: 15/05/2056IT0005647273</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -6954,7 +6954,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>IT0005648149</t>
+          <t>IT0005648149 -Btp Fx 3.6% Oct35 EurUltimo: 101,10Cedola: 1,49508Scadenza: 01/10/2035IT0005648149</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -7001,7 +7001,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>IT0005648255</t>
+          <t>IT0005648255 -Btp Italia Jun32 EurUltimo: 100,73Cedola: 0,925Scadenza: 04/06/2032IT0005648255</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -7048,7 +7048,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>IT0005654642</t>
+          <t>IT0005654642 -Btp Fx 2.7% Oct30 EurUltimo: 99,71Cedola: 0,82623Scadenza: 01/10/2030IT0005654642</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -7095,7 +7095,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>IT0005657330</t>
+          <t>IT0005657330 -Btp Fx 2.1% Aug27 EurUltimo: 99,85Cedola: 0,34807Scadenza: 26/08/2027IT0005657330</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -7142,7 +7142,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>IT0005657348</t>
+          <t>IT0005657348 -Btpi Fx Aug31 EurUltimo: 99,70Cedola: 0,1489Scadenza: 15/08/2031IT0005657348</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -7189,7 +7189,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>IT0005660052</t>
+          <t>IT0005660052 -Btp Fx 2.35% Jan29 EurUltimo: 99,70Cedola: 1,175Scadenza: 15/01/2029IT0005660052</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">

--- a/btp_dati.xlsx
+++ b/btp_dati.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M160"/>
+  <dimension ref="A1:M159"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="121" customWidth="1" min="1" max="1"/>
@@ -513,7 +513,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>IT0001086567 -Btp-1nv26      7,25%Ultimo: 106,31Cedola: 3,625Scadenza: 01/11/2026IT0001086567</t>
+          <t>IT0001086567 -Btp-1nv26      7,25%Ultimo: 106,25Cedola: 3,625Scadenza: 01/11/2026IT0001086567</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -522,7 +522,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>106.31</v>
+        <v>106.25</v>
       </c>
       <c r="D2" t="n">
         <v>3.625</v>
@@ -536,7 +536,7 @@
         <v>7.25</v>
       </c>
       <c r="G2" t="n">
-        <v>6.819</v>
+        <v>6.823</v>
       </c>
       <c r="H2" t="n">
         <v>3</v>
@@ -545,22 +545,22 @@
         <v>110.875</v>
       </c>
       <c r="J2" t="n">
-        <v>4.564999999999998</v>
+        <v>4.625</v>
       </c>
       <c r="K2" t="n">
-        <v>3.994</v>
+        <v>4.046</v>
       </c>
       <c r="L2" t="n">
-        <v>3.719</v>
+        <v>3.793</v>
       </c>
       <c r="M2" t="n">
-        <v>3.254</v>
+        <v>3.318</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>IT0001174611 -Btp-1nv27       6,5%Ultimo: 109,37Cedola: 3,25Scadenza: 01/11/2027IT0001174611</t>
+          <t>IT0001174611 -Btp-1nv27       6,5%Ultimo: 109,40Cedola: 3,25Scadenza: 01/11/2027IT0001174611</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>109.37</v>
+        <v>109.4</v>
       </c>
       <c r="D3" t="n">
         <v>3.25</v>
@@ -583,7 +583,7 @@
         <v>6.5</v>
       </c>
       <c r="G3" t="n">
-        <v>5.943</v>
+        <v>5.941</v>
       </c>
       <c r="H3" t="n">
         <v>5</v>
@@ -592,22 +592,22 @@
         <v>116.25</v>
       </c>
       <c r="J3" t="n">
-        <v>6.879999999999995</v>
+        <v>6.849999999999994</v>
       </c>
       <c r="K3" t="n">
-        <v>6.019</v>
+        <v>5.993</v>
       </c>
       <c r="L3" t="n">
-        <v>3.088</v>
+        <v>3.086</v>
       </c>
       <c r="M3" t="n">
-        <v>2.702</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>IT0001278511 -Btp-1nv29      5,25%Ultimo: 111,14Cedola: 2,625Scadenza: 01/11/2029IT0001278511</t>
+          <t>IT0001278511 -Btp-1nv29      5,25%Ultimo: 111,23Cedola: 2,625Scadenza: 01/11/2029IT0001278511</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -616,7 +616,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>111.14</v>
+        <v>111.23</v>
       </c>
       <c r="D4" t="n">
         <v>2.625</v>
@@ -630,7 +630,7 @@
         <v>5.25</v>
       </c>
       <c r="G4" t="n">
-        <v>4.723</v>
+        <v>4.719</v>
       </c>
       <c r="H4" t="n">
         <v>9</v>
@@ -639,22 +639,22 @@
         <v>123.625</v>
       </c>
       <c r="J4" t="n">
-        <v>12.485</v>
+        <v>12.395</v>
       </c>
       <c r="K4" t="n">
-        <v>10.924</v>
+        <v>10.845</v>
       </c>
       <c r="L4" t="n">
-        <v>2.951</v>
+        <v>2.935</v>
       </c>
       <c r="M4" t="n">
-        <v>2.582</v>
+        <v>2.568</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>IT0001444378 -Btp-1mg31         6%Ultimo: 117,05Cedola: 3,00Scadenza: 01/05/2031IT0001444378</t>
+          <t>IT0001444378 -Btp-1mg31         6%Ultimo: 117,23Cedola: 3,00Scadenza: 01/05/2031IT0001444378</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -663,7 +663,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>117.05</v>
+        <v>117.23</v>
       </c>
       <c r="D5" t="n">
         <v>3</v>
@@ -677,7 +677,7 @@
         <v>6</v>
       </c>
       <c r="G5" t="n">
-        <v>5.126</v>
+        <v>5.118</v>
       </c>
       <c r="H5" t="n">
         <v>12</v>
@@ -686,22 +686,22 @@
         <v>136</v>
       </c>
       <c r="J5" t="n">
-        <v>18.95</v>
+        <v>18.77</v>
       </c>
       <c r="K5" t="n">
-        <v>16.581</v>
+        <v>16.423</v>
       </c>
       <c r="L5" t="n">
-        <v>3.309</v>
+        <v>3.282</v>
       </c>
       <c r="M5" t="n">
-        <v>2.895</v>
+        <v>2.871</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>IT0003256820 -Btp-1fb33      5,75%Ultimo: 117,44Cedola: 2,875Scadenza: 01/02/2033IT0003256820</t>
+          <t>IT0003256820 -Btp-1fb33      5,75%Ultimo: 117,63Cedola: 2,875Scadenza: 01/02/2033IT0003256820</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -710,7 +710,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>117.44</v>
+        <v>117.63</v>
       </c>
       <c r="D6" t="n">
         <v>2.875</v>
@@ -724,7 +724,7 @@
         <v>5.75</v>
       </c>
       <c r="G6" t="n">
-        <v>4.896</v>
+        <v>4.888</v>
       </c>
       <c r="H6" t="n">
         <v>15</v>
@@ -733,22 +733,22 @@
         <v>143.125</v>
       </c>
       <c r="J6" t="n">
-        <v>25.685</v>
+        <v>25.495</v>
       </c>
       <c r="K6" t="n">
-        <v>22.474</v>
+        <v>22.308</v>
       </c>
       <c r="L6" t="n">
-        <v>3.431</v>
+        <v>3.409</v>
       </c>
       <c r="M6" t="n">
-        <v>3.002</v>
+        <v>2.982</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>IT0003535157 -Btp-1ag34         5%Ultimo: 113,20Cedola: 2,50Scadenza: 01/08/2034IT0003535157</t>
+          <t>IT0003535157 -Btp-1ag34         5%Ultimo: 113,39Cedola: 2,50Scadenza: 01/08/2034IT0003535157</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -757,7 +757,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>113.2</v>
+        <v>113.39</v>
       </c>
       <c r="D7" t="n">
         <v>2.5</v>
@@ -771,7 +771,7 @@
         <v>5</v>
       </c>
       <c r="G7" t="n">
-        <v>4.416</v>
+        <v>4.409</v>
       </c>
       <c r="H7" t="n">
         <v>18</v>
@@ -780,22 +780,22 @@
         <v>145</v>
       </c>
       <c r="J7" t="n">
-        <v>31.8</v>
+        <v>31.61</v>
       </c>
       <c r="K7" t="n">
-        <v>27.824</v>
+        <v>27.658</v>
       </c>
       <c r="L7" t="n">
-        <v>3.54</v>
+        <v>3.522</v>
       </c>
       <c r="M7" t="n">
-        <v>3.097</v>
+        <v>3.081</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>IT0003745541 -Btpi-15st35    2,35%Ultimo: 108,13Cedola: 1,175Scadenza: 15/09/2035IT0003745541</t>
+          <t>IT0003745541 -Btpi-15st35    2,35%Ultimo: 108,20Cedola: 1,175Scadenza: 15/09/2035IT0003745541</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -804,7 +804,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>108.13</v>
+        <v>108.2</v>
       </c>
       <c r="D8" t="n">
         <v>1.175</v>
@@ -818,7 +818,7 @@
         <v>2.35</v>
       </c>
       <c r="G8" t="n">
-        <v>2.173</v>
+        <v>2.171</v>
       </c>
       <c r="H8" t="n">
         <v>21</v>
@@ -827,22 +827,22 @@
         <v>124.675</v>
       </c>
       <c r="J8" t="n">
-        <v>16.545</v>
+        <v>16.47499999999999</v>
       </c>
       <c r="K8" t="n">
-        <v>14.476</v>
+        <v>14.415</v>
       </c>
       <c r="L8" t="n">
-        <v>1.637</v>
+        <v>1.631</v>
       </c>
       <c r="M8" t="n">
-        <v>1.432</v>
+        <v>1.427</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>IT0003934657 -Btp-1fb37         4%Ultimo: 104,34Cedola: 2,00Scadenza: 01/02/2037IT0003934657</t>
+          <t>IT0003934657 -Btp-1fb37         4%Ultimo: 104,54Cedola: 2,00Scadenza: 01/02/2037IT0003934657</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>104.34</v>
+        <v>104.54</v>
       </c>
       <c r="D9" t="n">
         <v>2</v>
@@ -865,7 +865,7 @@
         <v>4</v>
       </c>
       <c r="G9" t="n">
-        <v>3.833</v>
+        <v>3.826</v>
       </c>
       <c r="H9" t="n">
         <v>23</v>
@@ -874,22 +874,22 @@
         <v>146</v>
       </c>
       <c r="J9" t="n">
-        <v>41.66</v>
+        <v>41.45999999999999</v>
       </c>
       <c r="K9" t="n">
-        <v>36.452</v>
+        <v>36.277</v>
       </c>
       <c r="L9" t="n">
-        <v>3.626</v>
+        <v>3.611</v>
       </c>
       <c r="M9" t="n">
-        <v>3.172</v>
+        <v>3.159</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>IT0004286966 -Btp-1ag39         5%Ultimo: 113,50Cedola: 2,50Scadenza: 01/08/2039IT0004286966</t>
+          <t>IT0004286966 -Btp-1ag39         5%Ultimo: 113,63Cedola: 2,50Scadenza: 01/08/2039IT0004286966</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -898,7 +898,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>113.5</v>
+        <v>113.63</v>
       </c>
       <c r="D10" t="n">
         <v>2.5</v>
@@ -912,7 +912,7 @@
         <v>5</v>
       </c>
       <c r="G10" t="n">
-        <v>4.405</v>
+        <v>4.4</v>
       </c>
       <c r="H10" t="n">
         <v>28</v>
@@ -921,22 +921,22 @@
         <v>170</v>
       </c>
       <c r="J10" t="n">
-        <v>56.5</v>
+        <v>56.37</v>
       </c>
       <c r="K10" t="n">
-        <v>49.437</v>
+        <v>49.323</v>
       </c>
       <c r="L10" t="n">
-        <v>4.04</v>
+        <v>4.033</v>
       </c>
       <c r="M10" t="n">
-        <v>3.535</v>
+        <v>3.528</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>IT0004532559 -Btp-1st40 5%Ultimo: 113,26Cedola: 2,50Scadenza: 01/09/2040IT0004532559</t>
+          <t>IT0004532559 -Btp-1st40 5%Ultimo: 113,48Cedola: 2,50Scadenza: 01/09/2040IT0004532559</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -945,7 +945,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>113.26</v>
+        <v>113.48</v>
       </c>
       <c r="D11" t="n">
         <v>2.5</v>
@@ -959,7 +959,7 @@
         <v>5</v>
       </c>
       <c r="G11" t="n">
-        <v>4.414</v>
+        <v>4.406</v>
       </c>
       <c r="H11" t="n">
         <v>31</v>
@@ -968,22 +968,22 @@
         <v>177.5</v>
       </c>
       <c r="J11" t="n">
-        <v>64.23999999999999</v>
+        <v>64.02</v>
       </c>
       <c r="K11" t="n">
-        <v>56.209</v>
+        <v>56.017</v>
       </c>
       <c r="L11" t="n">
-        <v>4.262</v>
+        <v>4.25</v>
       </c>
       <c r="M11" t="n">
-        <v>3.729</v>
+        <v>3.718</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>IT0004545890 -Btpi-15st41 2,55%Ultimo: 107,78Cedola: 1,275Scadenza: 15/09/2041IT0004545890</t>
+          <t>IT0004545890 -Btpi-15st41 2,55%Ultimo: 107,79Cedola: 1,275Scadenza: 15/09/2041IT0004545890</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -992,7 +992,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>107.78</v>
+        <v>107.79</v>
       </c>
       <c r="D12" t="n">
         <v>1.275</v>
@@ -1015,13 +1015,13 @@
         <v>142.075</v>
       </c>
       <c r="J12" t="n">
-        <v>34.29499999999999</v>
+        <v>34.28499999999998</v>
       </c>
       <c r="K12" t="n">
-        <v>30.008</v>
+        <v>29.999</v>
       </c>
       <c r="L12" t="n">
-        <v>2.128</v>
+        <v>2.129</v>
       </c>
       <c r="M12" t="n">
         <v>1.862</v>
@@ -1030,7 +1030,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>IT0004644735 -Btp-1mz26 4,5%Ultimo: 101,368Cedola: 2,25Scadenza: 01/03/2026IT0004644735</t>
+          <t>IT0004644735 -Btp-1mz26 4,5%Ultimo: 101,369Cedola: 2,25Scadenza: 01/03/2026IT0004644735</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1039,7 +1039,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>101.368</v>
+        <v>101.369</v>
       </c>
       <c r="D13" t="n">
         <v>2.25</v>
@@ -1062,22 +1062,22 @@
         <v>104.5</v>
       </c>
       <c r="J13" t="n">
-        <v>3.132000000000005</v>
+        <v>3.131</v>
       </c>
       <c r="K13" t="n">
-        <v>2.74</v>
+        <v>2.739</v>
       </c>
       <c r="L13" t="n">
-        <v>5.631</v>
+        <v>5.714</v>
       </c>
       <c r="M13" t="n">
-        <v>4.927</v>
+        <v>4.999</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>IT0004735152 -Btpi-15st26 3,1%Ultimo: 103,00Cedola: 1,55Scadenza: 15/09/2026IT0004735152</t>
+          <t>IT0004735152 -Btpi-15st26 3,1%Ultimo: 102,94Cedola: 1,55Scadenza: 15/09/2026IT0004735152</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1086,7 +1086,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>103</v>
+        <v>102.94</v>
       </c>
       <c r="D14" t="n">
         <v>1.55</v>
@@ -1100,7 +1100,7 @@
         <v>3.1</v>
       </c>
       <c r="G14" t="n">
-        <v>3.009</v>
+        <v>3.011</v>
       </c>
       <c r="H14" t="n">
         <v>3</v>
@@ -1109,22 +1109,22 @@
         <v>104.65</v>
       </c>
       <c r="J14" t="n">
-        <v>1.650000000000006</v>
+        <v>1.710000000000008</v>
       </c>
       <c r="K14" t="n">
-        <v>1.443</v>
+        <v>1.496</v>
       </c>
       <c r="L14" t="n">
-        <v>1.501</v>
+        <v>1.568</v>
       </c>
       <c r="M14" t="n">
-        <v>1.313</v>
+        <v>1.372</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>IT0004848443 -Btp Coupon Strip Zc Nv26 EurUltimo: 97,87Cedola:Scadenza: 01/11/2026IT0004848443</t>
+          <t>IT0004848443 -Btp Coupon Strip Zc Nv26 EurUltimo: 97,76Cedola:Scadenza: 01/11/2026IT0004848443</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1133,7 +1133,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>97.87</v>
+        <v>97.76000000000001</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>IT0004848476 -Btp Coupon Strip Zc Nv27 EurUltimo: 95,49Cedola:Scadenza: 01/11/2027IT0004848476</t>
+          <t>IT0004848476 -Btp Coupon Strip Zc Nv27 EurUltimo: 95,56Cedola:Scadenza: 01/11/2027IT0004848476</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1156,7 +1156,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>95.48999999999999</v>
+        <v>95.56</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -1170,7 +1170,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>IT0004848484 -Btp Coupon Strip Zc Nv29 EurUltimo: 90,42Cedola:Scadenza: 01/11/2029IT0004848484</t>
+          <t>IT0004848484 -Btp Coupon Strip Zc Nv29 EurUltimo: 90,31Cedola:Scadenza: 01/11/2029IT0004848484</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>90.42</v>
+        <v>90.31</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>IT0004848492 -Btp Coupon Strip Zc Mg31 EurUltimo: 85,68Cedola:Scadenza: 01/05/2031IT0004848492</t>
+          <t>IT0004848492 -Btp Coupon Strip Zc Mg31 EurUltimo: 85,58Cedola:Scadenza: 01/05/2031IT0004848492</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1202,7 +1202,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>85.68000000000001</v>
+        <v>85.58</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1216,16 +1216,13 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>IT0004848534 -Btpstripital Zc Feb33 EurUltimo: 79,57Cedola:Scadenza: 01/02/2033IT0004848534</t>
+          <t>IT0004848534 -Btpstripital Zc Feb33 EurUltimo:Cedola:Scadenza: 01/02/2033IT0004848534</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
           <t>Btpstripital Zc Feb33 Eur</t>
         </is>
-      </c>
-      <c r="C19" t="n">
-        <v>79.56999999999999</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1259,13 +1256,16 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>IT0004848690 -Btpstripital Zc Ago39Ultimo:Cedola:Scadenza: 01/08/2039IT0004848690</t>
+          <t>IT0004848690 -Btpstripital Zc Ago39Ultimo: 58,69Cedola:Scadenza: 01/08/2039IT0004848690</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
           <t>Btpstripital Zc Ago39</t>
         </is>
+      </c>
+      <c r="C21" t="n">
+        <v>58.69</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1279,16 +1279,13 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>IT0004889033 -Btp Tf 4,75% St28 EurUltimo: 107,17Cedola: 2,375Scadenza: 01/09/2028IT0004889033</t>
+          <t>IT0004889033 -Btp Tf 4,75% St28 EurUltimo:Cedola: 2,375Scadenza: 01/09/2028IT0004889033</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
           <t>Btp Tf 4,75% St28 Eur</t>
         </is>
-      </c>
-      <c r="C22" t="n">
-        <v>107.17</v>
       </c>
       <c r="D22" t="n">
         <v>2.375</v>
@@ -1301,32 +1298,17 @@
       <c r="F22" t="n">
         <v>4.75</v>
       </c>
-      <c r="G22" t="n">
-        <v>4.432</v>
-      </c>
       <c r="H22" t="n">
         <v>7</v>
       </c>
       <c r="I22" t="n">
         <v>116.625</v>
       </c>
-      <c r="J22" t="n">
-        <v>9.454999999999998</v>
-      </c>
-      <c r="K22" t="n">
-        <v>8.273</v>
-      </c>
-      <c r="L22" t="n">
-        <v>3.086</v>
-      </c>
-      <c r="M22" t="n">
-        <v>2.7</v>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>IT0004923998 -Btp Tf 4,75% St44 EurUltimo: 109,78Cedola: 2,375Scadenza: 01/09/2044IT0004923998</t>
+          <t>IT0004923998 -Btp Tf 4,75% St44 EurUltimo: 109,95Cedola: 2,375Scadenza: 01/09/2044IT0004923998</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1335,7 +1317,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>109.78</v>
+        <v>109.95</v>
       </c>
       <c r="D23" t="n">
         <v>2.375</v>
@@ -1349,7 +1331,7 @@
         <v>4.75</v>
       </c>
       <c r="G23" t="n">
-        <v>4.326</v>
+        <v>4.32</v>
       </c>
       <c r="H23" t="n">
         <v>39</v>
@@ -1358,22 +1340,22 @@
         <v>192.625</v>
       </c>
       <c r="J23" t="n">
-        <v>82.845</v>
+        <v>82.675</v>
       </c>
       <c r="K23" t="n">
-        <v>72.489</v>
+        <v>72.34</v>
       </c>
       <c r="L23" t="n">
-        <v>4.343</v>
+        <v>4.336</v>
       </c>
       <c r="M23" t="n">
-        <v>3.8</v>
+        <v>3.794</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>IT0004976525 -Btp Coupon Strip Zc St28 EurUltimo: 93,41Cedola:Scadenza: 01/09/2028IT0004976525</t>
+          <t>IT0004976525 -Btp Coupon Strip Zc St28 EurUltimo: 93,40Cedola:Scadenza: 01/09/2028IT0004976525</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1382,7 +1364,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>93.41</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -1396,7 +1378,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>IT0004976558 -Btp Coupon Strip Zc Mz30 EurUltimo: 89,16Cedola:Scadenza: 01/03/2030IT0004976558</t>
+          <t>IT0004976558 -Btp Coupon Strip Zc Mz30 EurUltimo: 89,37Cedola:Scadenza: 01/03/2030IT0004976558</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1405,7 +1387,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>89.16</v>
+        <v>89.37</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -1419,16 +1401,13 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>IT0004976590 -Btpstripital Zc Mar32Ultimo: 83,11Cedola:Scadenza: 01/03/2032IT0004976590</t>
+          <t>IT0004976590 -Btpstripital Zc Mar32Ultimo:Cedola:Scadenza: 01/03/2032IT0004976590</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
           <t>Btpstripital Zc Mar32</t>
         </is>
-      </c>
-      <c r="C26" t="n">
-        <v>83.11</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -1502,16 +1481,13 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>IT0004976715 -Btpstripital Zc Mar38Ultimo: 62,47Cedola:Scadenza: 01/03/2038IT0004976715</t>
+          <t>IT0004976715 -Btpstripital Zc Mar38Ultimo:Cedola:Scadenza: 01/03/2038IT0004976715</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
           <t>Btpstripital Zc Mar38</t>
         </is>
-      </c>
-      <c r="C30" t="n">
-        <v>62.47</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -1525,7 +1501,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>IT0005024234 -Btp Tf 3,50% Mz30 EurUltimo: 104,03Cedola: 1,75Scadenza: 01/03/2030IT0005024234</t>
+          <t>IT0005024234 -Btp Tf 3,50% Mz30 EurUltimo: 104,20Cedola: 1,75Scadenza: 01/03/2030IT0005024234</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1534,7 +1510,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>104.03</v>
+        <v>104.2</v>
       </c>
       <c r="D31" t="n">
         <v>1.75</v>
@@ -1548,7 +1524,7 @@
         <v>3.5</v>
       </c>
       <c r="G31" t="n">
-        <v>3.364</v>
+        <v>3.358</v>
       </c>
       <c r="H31" t="n">
         <v>10</v>
@@ -1557,22 +1533,22 @@
         <v>117.5</v>
       </c>
       <c r="J31" t="n">
-        <v>13.47</v>
+        <v>13.3</v>
       </c>
       <c r="K31" t="n">
-        <v>11.786</v>
+        <v>11.637</v>
       </c>
       <c r="L31" t="n">
-        <v>2.954</v>
+        <v>2.922</v>
       </c>
       <c r="M31" t="n">
-        <v>2.584</v>
+        <v>2.556</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>IT0005083057 -Btp Tf 3,25% St46 EurUltimo: 88,26Cedola: 1,625Scadenza: 01/09/2046IT0005083057</t>
+          <t>IT0005083057 -Btp Tf 3,25% St46 EurUltimo: 88,39Cedola: 1,625Scadenza: 01/09/2046IT0005083057</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1581,7 +1557,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>88.26000000000001</v>
+        <v>88.39</v>
       </c>
       <c r="D32" t="n">
         <v>1.625</v>
@@ -1595,7 +1571,7 @@
         <v>3.25</v>
       </c>
       <c r="G32" t="n">
-        <v>3.682</v>
+        <v>3.676</v>
       </c>
       <c r="H32" t="n">
         <v>43</v>
@@ -1604,22 +1580,22 @@
         <v>169.875</v>
       </c>
       <c r="J32" t="n">
-        <v>81.61499999999999</v>
+        <v>81.485</v>
       </c>
       <c r="K32" t="n">
-        <v>71.413</v>
+        <v>71.29900000000001</v>
       </c>
       <c r="L32" t="n">
-        <v>3.872</v>
+        <v>3.868</v>
       </c>
       <c r="M32" t="n">
-        <v>3.388</v>
+        <v>3.384</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>IT0005094088 -Btp Tf 1,65% Mz32 EurUltimo: 92,38Cedola: 0,825Scadenza: 01/03/2032IT0005094088</t>
+          <t>IT0005094088 -Btp Tf 1,65% Mz32 EurUltimo: 92,61Cedola: 0,825Scadenza: 01/03/2032IT0005094088</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1628,7 +1604,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>92.38</v>
+        <v>92.61</v>
       </c>
       <c r="D33" t="n">
         <v>0.825</v>
@@ -1642,7 +1618,7 @@
         <v>1.65</v>
       </c>
       <c r="G33" t="n">
-        <v>1.786</v>
+        <v>1.781</v>
       </c>
       <c r="H33" t="n">
         <v>14</v>
@@ -1651,22 +1627,22 @@
         <v>111.55</v>
       </c>
       <c r="J33" t="n">
-        <v>19.17</v>
+        <v>18.94</v>
       </c>
       <c r="K33" t="n">
-        <v>16.773</v>
+        <v>16.572</v>
       </c>
       <c r="L33" t="n">
-        <v>2.921</v>
+        <v>2.89</v>
       </c>
       <c r="M33" t="n">
-        <v>2.555</v>
+        <v>2.528</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>IT0005127086 -Btp Tf 2,00% Dc25 EurUltimo: 100,007Cedola: 1,00Scadenza: 01/12/2025IT0005127086</t>
+          <t>IT0005127086 -Btp Tf 2,00% Dc25 EurUltimo: 100,00Cedola: 1,00Scadenza: 01/12/2025IT0005127086</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1675,7 +1651,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>100.007</v>
+        <v>100</v>
       </c>
       <c r="D34" t="n">
         <v>1</v>
@@ -1689,7 +1665,7 @@
         <v>2</v>
       </c>
       <c r="G34" t="n">
-        <v>1.999</v>
+        <v>2</v>
       </c>
       <c r="H34" t="n">
         <v>1</v>
@@ -1698,22 +1674,22 @@
         <v>101</v>
       </c>
       <c r="J34" t="n">
-        <v>0.992999999999995</v>
+        <v>1</v>
       </c>
       <c r="K34" t="n">
-        <v>0.868</v>
+        <v>0.875</v>
       </c>
       <c r="L34" t="n">
-        <v>3.207</v>
+        <v>3.318</v>
       </c>
       <c r="M34" t="n">
-        <v>2.806</v>
+        <v>2.903</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>IT0005138828 -Btpi Tf 1,25% St32 EurUltimo: 100,28Cedola: 0,625Scadenza: 15/09/2032IT0005138828</t>
+          <t>IT0005138828 -Btpi Tf 1,25% St32 EurUltimo: 100,49Cedola: 0,625Scadenza: 15/09/2032IT0005138828</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1722,7 +1698,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>100.28</v>
+        <v>100.49</v>
       </c>
       <c r="D35" t="n">
         <v>0.625</v>
@@ -1736,7 +1712,7 @@
         <v>1.25</v>
       </c>
       <c r="G35" t="n">
-        <v>1.246</v>
+        <v>1.243</v>
       </c>
       <c r="H35" t="n">
         <v>15</v>
@@ -1745,22 +1721,22 @@
         <v>109.375</v>
       </c>
       <c r="J35" t="n">
-        <v>9.094999999999999</v>
+        <v>8.885000000000005</v>
       </c>
       <c r="K35" t="n">
-        <v>7.958</v>
+        <v>7.774</v>
       </c>
       <c r="L35" t="n">
-        <v>1.28</v>
+        <v>1.252</v>
       </c>
       <c r="M35" t="n">
-        <v>1.12</v>
+        <v>1.095</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>IT0005162828 -Btp Tf 2,7% Mz47 EurUltimo: 80,33Cedola: 1,35Scadenza: 01/03/2047IT0005162828</t>
+          <t>IT0005162828 -Btp Tf 2,7% Mz47 EurUltimo: 80,40Cedola: 1,35Scadenza: 01/03/2047IT0005162828</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1769,7 +1745,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>80.33</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="D36" t="n">
         <v>1.35</v>
@@ -1783,7 +1759,7 @@
         <v>2.7</v>
       </c>
       <c r="G36" t="n">
-        <v>3.361</v>
+        <v>3.358</v>
       </c>
       <c r="H36" t="n">
         <v>44</v>
@@ -1792,22 +1768,22 @@
         <v>159.4</v>
       </c>
       <c r="J36" t="n">
-        <v>79.07000000000001</v>
+        <v>79</v>
       </c>
       <c r="K36" t="n">
-        <v>69.18600000000001</v>
+        <v>69.125</v>
       </c>
       <c r="L36" t="n">
-        <v>3.665</v>
+        <v>3.663</v>
       </c>
       <c r="M36" t="n">
-        <v>3.206</v>
+        <v>3.205</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>IT0005170839 -Btp Tf 1,60% Gn26 EurUltimo: 99,727Cedola: 0,80Scadenza: 01/06/2026IT0005170839</t>
+          <t>IT0005170839 -Btp Tf 1,60% Gn26 EurUltimo: 99,734Cedola: 0,80Scadenza: 01/06/2026IT0005170839</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1816,7 +1792,7 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>99.727</v>
+        <v>99.73399999999999</v>
       </c>
       <c r="D37" t="n">
         <v>0.8</v>
@@ -1839,22 +1815,22 @@
         <v>101.6</v>
       </c>
       <c r="J37" t="n">
-        <v>1.87299999999999</v>
+        <v>1.866</v>
       </c>
       <c r="K37" t="n">
-        <v>1.638</v>
+        <v>1.632</v>
       </c>
       <c r="L37" t="n">
-        <v>2.317</v>
+        <v>2.332</v>
       </c>
       <c r="M37" t="n">
-        <v>2.027</v>
+        <v>2.04</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>IT0005177909 -Btp Tf 2,25% St36 EurUltimo: 88,43Cedola: 1,125Scadenza: 01/09/2036IT0005177909</t>
+          <t>IT0005177909 -Btp Tf 2,25% St36 EurUltimo: 88,60Cedola: 1,125Scadenza: 01/09/2036IT0005177909</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1863,7 +1839,7 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>88.43000000000001</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="D38" t="n">
         <v>1.125</v>
@@ -1877,7 +1853,7 @@
         <v>2.25</v>
       </c>
       <c r="G38" t="n">
-        <v>2.544</v>
+        <v>2.539</v>
       </c>
       <c r="H38" t="n">
         <v>23</v>
@@ -1886,16 +1862,16 @@
         <v>125.875</v>
       </c>
       <c r="J38" t="n">
-        <v>37.44499999999999</v>
+        <v>37.27500000000001</v>
       </c>
       <c r="K38" t="n">
-        <v>32.764</v>
+        <v>32.615</v>
       </c>
       <c r="L38" t="n">
-        <v>3.383</v>
+        <v>3.37</v>
       </c>
       <c r="M38" t="n">
-        <v>2.96</v>
+        <v>2.948</v>
       </c>
     </row>
     <row r="39">
@@ -1939,16 +1915,16 @@
         <v>2.393</v>
       </c>
       <c r="L39" t="n">
-        <v>2.088</v>
+        <v>2.101</v>
       </c>
       <c r="M39" t="n">
-        <v>1.827</v>
+        <v>1.838</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>IT0005217390 -Btp Tf 2,8% Mz67 EurUltimo: 71,49Cedola: 1,40Scadenza: 01/03/2067IT0005217390</t>
+          <t>IT0005217390 -Btp Tf 2,8% Mz67 EurUltimo: 71,40Cedola: 1,40Scadenza: 01/03/2067IT0005217390</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1957,7 +1933,7 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>71.48999999999999</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="D40" t="n">
         <v>1.4</v>
@@ -1971,7 +1947,7 @@
         <v>2.8</v>
       </c>
       <c r="G40" t="n">
-        <v>3.916</v>
+        <v>3.921</v>
       </c>
       <c r="H40" t="n">
         <v>84</v>
@@ -1980,22 +1956,22 @@
         <v>217.6</v>
       </c>
       <c r="J40" t="n">
-        <v>146.11</v>
+        <v>146.2</v>
       </c>
       <c r="K40" t="n">
-        <v>127.846</v>
+        <v>127.924</v>
       </c>
       <c r="L40" t="n">
-        <v>3.513</v>
+        <v>3.516</v>
       </c>
       <c r="M40" t="n">
-        <v>3.073</v>
+        <v>3.076</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>IT0005240350 -Btp Tf 2,45% St33 EurUltimo: 95,04Cedola: 1,225Scadenza: 01/09/2033IT0005240350</t>
+          <t>IT0005240350 -Btp Tf 2,45% St33 EurUltimo: 95,24Cedola: 1,225Scadenza: 01/09/2033IT0005240350</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2004,7 +1980,7 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>95.04000000000001</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="D41" t="n">
         <v>1.225</v>
@@ -2018,7 +1994,7 @@
         <v>2.45</v>
       </c>
       <c r="G41" t="n">
-        <v>2.577</v>
+        <v>2.572</v>
       </c>
       <c r="H41" t="n">
         <v>17</v>
@@ -2027,22 +2003,22 @@
         <v>120.825</v>
       </c>
       <c r="J41" t="n">
-        <v>25.785</v>
+        <v>25.58500000000001</v>
       </c>
       <c r="K41" t="n">
-        <v>22.561</v>
+        <v>22.386</v>
       </c>
       <c r="L41" t="n">
-        <v>3.196</v>
+        <v>3.175</v>
       </c>
       <c r="M41" t="n">
-        <v>2.796</v>
+        <v>2.778</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>IT0005240830 -Btp Tf 2,20% Gn27 EurUltimo: 100,29Cedola: 1,10Scadenza: 01/06/2027IT0005240830</t>
+          <t>IT0005240830 -Btp Tf 2,20% Gn27 EurUltimo: 100,32Cedola: 1,10Scadenza: 01/06/2027IT0005240830</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2051,7 +2027,7 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>100.29</v>
+        <v>100.32</v>
       </c>
       <c r="D42" t="n">
         <v>1.1</v>
@@ -2065,7 +2041,7 @@
         <v>2.2</v>
       </c>
       <c r="G42" t="n">
-        <v>2.193</v>
+        <v>2.192</v>
       </c>
       <c r="H42" t="n">
         <v>4</v>
@@ -2074,28 +2050,31 @@
         <v>104.4</v>
       </c>
       <c r="J42" t="n">
-        <v>4.109999999999999</v>
+        <v>4.080000000000013</v>
       </c>
       <c r="K42" t="n">
-        <v>3.596</v>
+        <v>3.57</v>
       </c>
       <c r="L42" t="n">
-        <v>2.272</v>
+        <v>2.266</v>
       </c>
       <c r="M42" t="n">
-        <v>1.987</v>
+        <v>1.982</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>IT0005246134 -Btpi Tf 1,30% Mg28 EurUltimo:Cedola: 0,65Scadenza: 15/05/2028IT0005246134</t>
+          <t>IT0005246134 -Btpi Tf 1,30% Mg28 EurUltimo: 101,41Cedola: 0,65Scadenza: 15/05/2028IT0005246134</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
           <t>Btpi Tf 1,30% Mg28 Eur</t>
         </is>
+      </c>
+      <c r="C43" t="n">
+        <v>101.41</v>
       </c>
       <c r="D43" t="n">
         <v>0.65</v>
@@ -2108,17 +2087,32 @@
       <c r="F43" t="n">
         <v>1.3</v>
       </c>
+      <c r="G43" t="n">
+        <v>1.281</v>
+      </c>
       <c r="H43" t="n">
         <v>6</v>
       </c>
       <c r="I43" t="n">
         <v>103.9</v>
       </c>
+      <c r="J43" t="n">
+        <v>2.490000000000009</v>
+      </c>
+      <c r="K43" t="n">
+        <v>2.178</v>
+      </c>
+      <c r="L43" t="n">
+        <v>0.903</v>
+      </c>
+      <c r="M43" t="n">
+        <v>0.79</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>IT0005273013 -Btp Tf 3,45% Mz48 EurUltimo: 90,32Cedola: 1,725Scadenza: 01/03/2048IT0005273013</t>
+          <t>IT0005273013 -Btp Tf 3,45% Mz48 EurUltimo: 90,35Cedola: 1,725Scadenza: 01/03/2048IT0005273013</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2127,7 +2121,7 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>90.31999999999999</v>
+        <v>90.34999999999999</v>
       </c>
       <c r="D44" t="n">
         <v>1.725</v>
@@ -2141,7 +2135,7 @@
         <v>3.45</v>
       </c>
       <c r="G44" t="n">
-        <v>3.819</v>
+        <v>3.818</v>
       </c>
       <c r="H44" t="n">
         <v>46</v>
@@ -2150,10 +2144,10 @@
         <v>179.35</v>
       </c>
       <c r="J44" t="n">
-        <v>89.03000000000003</v>
+        <v>89.00000000000003</v>
       </c>
       <c r="K44" t="n">
-        <v>77.901</v>
+        <v>77.875</v>
       </c>
       <c r="L44" t="n">
         <v>3.944</v>
@@ -2165,7 +2159,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>IT0005274805 -Btp Tf 2,05% Ag27 EurUltimo: 99,95Cedola: 1,025Scadenza: 01/08/2027IT0005274805</t>
+          <t>IT0005274805 -Btp Tf 2,05% Ag27 EurUltimo: 99,97Cedola: 1,025Scadenza: 01/08/2027IT0005274805</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2174,7 +2168,7 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>99.95</v>
+        <v>99.97</v>
       </c>
       <c r="D45" t="n">
         <v>1.025</v>
@@ -2188,7 +2182,7 @@
         <v>2.05</v>
       </c>
       <c r="G45" t="n">
-        <v>2.051</v>
+        <v>2.05</v>
       </c>
       <c r="H45" t="n">
         <v>4</v>
@@ -2197,22 +2191,22 @@
         <v>104.1</v>
       </c>
       <c r="J45" t="n">
-        <v>4.149999999999991</v>
+        <v>4.129999999999995</v>
       </c>
       <c r="K45" t="n">
-        <v>3.631</v>
+        <v>3.613</v>
       </c>
       <c r="L45" t="n">
-        <v>2.1</v>
+        <v>2.099</v>
       </c>
       <c r="M45" t="n">
-        <v>1.837</v>
+        <v>1.836</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>IT0005321325 -Btp Tf 2,95% St38 EurUltimo: 92,32Cedola: 1,475Scadenza: 01/09/2038IT0005321325</t>
+          <t>IT0005321325 -Btp Tf 2,95% St38 EurUltimo: 92,53Cedola: 1,475Scadenza: 01/09/2038IT0005321325</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2221,7 +2215,7 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>92.31999999999999</v>
+        <v>92.53</v>
       </c>
       <c r="D46" t="n">
         <v>1.475</v>
@@ -2235,7 +2229,7 @@
         <v>2.95</v>
       </c>
       <c r="G46" t="n">
-        <v>3.195</v>
+        <v>3.188</v>
       </c>
       <c r="H46" t="n">
         <v>27</v>
@@ -2244,22 +2238,22 @@
         <v>139.825</v>
       </c>
       <c r="J46" t="n">
-        <v>47.505</v>
+        <v>47.29499999999999</v>
       </c>
       <c r="K46" t="n">
-        <v>41.566</v>
+        <v>41.383</v>
       </c>
       <c r="L46" t="n">
-        <v>3.635</v>
+        <v>3.621</v>
       </c>
       <c r="M46" t="n">
-        <v>3.18</v>
+        <v>3.168</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>IT0005323032 -Btp Tf 2,00% Fb28 EurUltimo: 99,63Cedola: 1,00Scadenza: 01/02/2028IT0005323032</t>
+          <t>IT0005323032 -Btp Tf 2,00% Fb28 EurUltimo: 99,74Cedola: 1,00Scadenza: 01/02/2028IT0005323032</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2268,7 +2262,7 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>99.63</v>
+        <v>99.73999999999999</v>
       </c>
       <c r="D47" t="n">
         <v>1</v>
@@ -2282,7 +2276,7 @@
         <v>2</v>
       </c>
       <c r="G47" t="n">
-        <v>2.007</v>
+        <v>2.005</v>
       </c>
       <c r="H47" t="n">
         <v>5</v>
@@ -2291,22 +2285,22 @@
         <v>105</v>
       </c>
       <c r="J47" t="n">
-        <v>5.370000000000005</v>
+        <v>5.260000000000005</v>
       </c>
       <c r="K47" t="n">
-        <v>4.698</v>
+        <v>4.602</v>
       </c>
       <c r="L47" t="n">
-        <v>2.165</v>
+        <v>2.128</v>
       </c>
       <c r="M47" t="n">
-        <v>1.894</v>
+        <v>1.862</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>IT0005332835 -Btp Italia Mg26 EurUltimo: 99,90Cedola: 0,275Scadenza: 21/05/2026IT0005332835</t>
+          <t>IT0005332835 -Btp Italia Mg26 EurUltimo: 100,001Cedola: 0,275Scadenza: 21/05/2026IT0005332835</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2315,7 +2309,7 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>99.90000000000001</v>
+        <v>100.001</v>
       </c>
       <c r="D48" t="n">
         <v>0.275</v>
@@ -2329,7 +2323,7 @@
         <v>0.55</v>
       </c>
       <c r="G48" t="n">
-        <v>0.55</v>
+        <v>0.549</v>
       </c>
       <c r="H48" t="n">
         <v>2</v>
@@ -2338,22 +2332,22 @@
         <v>100.55</v>
       </c>
       <c r="J48" t="n">
-        <v>0.6499999999999915</v>
+        <v>0.5489999999999924</v>
       </c>
       <c r="K48" t="n">
-        <v>0.5679999999999999</v>
+        <v>0.48</v>
       </c>
       <c r="L48" t="n">
-        <v>0.835</v>
+        <v>0.713</v>
       </c>
       <c r="M48" t="n">
-        <v>0.73</v>
+        <v>0.623</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>IT0005340929 -Btp Tf 2,80% Dc28 EurUltimo: 101,55Cedola: 1,40Scadenza: 01/12/2028IT0005340929</t>
+          <t>IT0005340929 -Btp Tf 2,80% Dc28 EurUltimo: 101,76Cedola: 1,40Scadenza: 01/12/2028IT0005340929</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2362,7 +2356,7 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>101.55</v>
+        <v>101.76</v>
       </c>
       <c r="D49" t="n">
         <v>1.4</v>
@@ -2376,7 +2370,7 @@
         <v>2.8</v>
       </c>
       <c r="G49" t="n">
-        <v>2.757</v>
+        <v>2.751</v>
       </c>
       <c r="H49" t="n">
         <v>7</v>
@@ -2385,22 +2379,22 @@
         <v>109.8</v>
       </c>
       <c r="J49" t="n">
-        <v>8.25</v>
+        <v>8.039999999999992</v>
       </c>
       <c r="K49" t="n">
-        <v>7.218</v>
+        <v>7.034</v>
       </c>
       <c r="L49" t="n">
-        <v>2.49</v>
+        <v>2.433</v>
       </c>
       <c r="M49" t="n">
-        <v>2.178</v>
+        <v>2.128</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>IT0005345183 -Btp Tf 2.50% Nv25 EurUltimo: 100,116Cedola: 1,25Scadenza: 15/11/2025IT0005345183</t>
+          <t>IT0005345183 -Btp Tf 2.50% Nv25 EurUltimo: 100,109Cedola: 1,25Scadenza: 15/11/2025IT0005345183</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2409,7 +2403,7 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>100.116</v>
+        <v>100.109</v>
       </c>
       <c r="D50" t="n">
         <v>1.25</v>
@@ -2432,22 +2426,22 @@
         <v>101.25</v>
       </c>
       <c r="J50" t="n">
-        <v>1.134</v>
+        <v>1.141000000000005</v>
       </c>
       <c r="K50" t="n">
-        <v>0.992</v>
+        <v>0.998</v>
       </c>
       <c r="L50" t="n">
-        <v>4.267</v>
+        <v>4.43</v>
       </c>
       <c r="M50" t="n">
-        <v>3.733</v>
+        <v>3.876</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>IT0005358806 -Btp Tf 3,35% Mz35 EurUltimo: 100,06Cedola: 1,675Scadenza: 01/03/2035IT0005358806</t>
+          <t>IT0005358806 -Btp Tf 3,35% Mz35 EurUltimo: 100,26Cedola: 1,675Scadenza: 01/03/2035IT0005358806</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2456,7 +2450,7 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>100.06</v>
+        <v>100.26</v>
       </c>
       <c r="D51" t="n">
         <v>1.675</v>
@@ -2470,7 +2464,7 @@
         <v>3.35</v>
       </c>
       <c r="G51" t="n">
-        <v>3.347</v>
+        <v>3.341</v>
       </c>
       <c r="H51" t="n">
         <v>20</v>
@@ -2479,22 +2473,22 @@
         <v>133.5</v>
       </c>
       <c r="J51" t="n">
-        <v>33.44</v>
+        <v>33.23999999999999</v>
       </c>
       <c r="K51" t="n">
-        <v>29.259</v>
+        <v>29.084</v>
       </c>
       <c r="L51" t="n">
-        <v>3.497</v>
+        <v>3.479</v>
       </c>
       <c r="M51" t="n">
-        <v>3.059</v>
+        <v>3.044</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>IT0005363111 -Btp Tf 3,85% St49 EurUltimo: 95,50Cedola: 1,925Scadenza: 01/09/2049IT0005363111</t>
+          <t>IT0005363111 -Btp Tf 3,85% St49 EurUltimo: 95,59Cedola: 1,925Scadenza: 01/09/2049IT0005363111</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2503,7 +2497,7 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>95.5</v>
+        <v>95.59</v>
       </c>
       <c r="D52" t="n">
         <v>1.925</v>
@@ -2517,7 +2511,7 @@
         <v>3.85</v>
       </c>
       <c r="G52" t="n">
-        <v>4.031</v>
+        <v>4.027</v>
       </c>
       <c r="H52" t="n">
         <v>49</v>
@@ -2526,22 +2520,22 @@
         <v>194.325</v>
       </c>
       <c r="J52" t="n">
-        <v>98.82499999999999</v>
+        <v>98.73499999999999</v>
       </c>
       <c r="K52" t="n">
-        <v>86.471</v>
+        <v>86.393</v>
       </c>
       <c r="L52" t="n">
-        <v>4.104</v>
+        <v>4.102</v>
       </c>
       <c r="M52" t="n">
-        <v>3.591</v>
+        <v>3.589</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>IT0005365165 -Btp Tf 3,00% Ag29 EurUltimo: 102,10Cedola: 1,50Scadenza: 01/08/2029IT0005365165</t>
+          <t>IT0005365165 -Btp Tf 3,00% Ag29 EurUltimo: 102,21Cedola: 1,50Scadenza: 01/08/2029IT0005365165</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2550,7 +2544,7 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>102.1</v>
+        <v>102.21</v>
       </c>
       <c r="D53" t="n">
         <v>1.5</v>
@@ -2564,7 +2558,7 @@
         <v>3</v>
       </c>
       <c r="G53" t="n">
-        <v>2.938</v>
+        <v>2.935</v>
       </c>
       <c r="H53" t="n">
         <v>8</v>
@@ -2573,22 +2567,22 @@
         <v>112</v>
       </c>
       <c r="J53" t="n">
-        <v>9.900000000000006</v>
+        <v>9.790000000000006</v>
       </c>
       <c r="K53" t="n">
-        <v>8.662000000000001</v>
+        <v>8.566000000000001</v>
       </c>
       <c r="L53" t="n">
-        <v>2.488</v>
+        <v>2.466</v>
       </c>
       <c r="M53" t="n">
-        <v>2.177</v>
+        <v>2.157</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>IT0005370306 -Btp Tf 2,10% Lg26 EurUltimo: 100,106Cedola: 1,05Scadenza: 15/07/2026IT0005370306</t>
+          <t>IT0005370306 -Btp Tf 2,10% Lg26 EurUltimo: 100,097Cedola: 1,05Scadenza: 15/07/2026IT0005370306</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2597,7 +2591,7 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>100.106</v>
+        <v>100.097</v>
       </c>
       <c r="D54" t="n">
         <v>1.05</v>
@@ -2620,22 +2614,22 @@
         <v>102.1</v>
       </c>
       <c r="J54" t="n">
-        <v>1.994</v>
+        <v>2.003</v>
       </c>
       <c r="K54" t="n">
-        <v>1.744</v>
+        <v>1.752</v>
       </c>
       <c r="L54" t="n">
-        <v>2.146</v>
+        <v>2.175</v>
       </c>
       <c r="M54" t="n">
-        <v>1.877</v>
+        <v>1.903</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>IT0005377152 -Btp Tf 3,1% Mz40 EurUltimo: 92,09Cedola: 1,55Scadenza: 01/03/2040IT0005377152</t>
+          <t>IT0005377152 -Btp Tf 3,1% Mz40 EurUltimo: 92,26Cedola: 1,55Scadenza: 01/03/2040IT0005377152</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2644,7 +2638,7 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>92.09</v>
+        <v>92.26000000000001</v>
       </c>
       <c r="D55" t="n">
         <v>1.55</v>
@@ -2658,7 +2652,7 @@
         <v>3.1</v>
       </c>
       <c r="G55" t="n">
-        <v>3.366</v>
+        <v>3.36</v>
       </c>
       <c r="H55" t="n">
         <v>30</v>
@@ -2667,22 +2661,22 @@
         <v>146.5</v>
       </c>
       <c r="J55" t="n">
-        <v>54.41</v>
+        <v>54.23999999999999</v>
       </c>
       <c r="K55" t="n">
-        <v>47.608</v>
+        <v>47.459</v>
       </c>
       <c r="L55" t="n">
-        <v>3.735</v>
+        <v>3.725</v>
       </c>
       <c r="M55" t="n">
-        <v>3.268</v>
+        <v>3.259</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>IT0005383309 -Btp Tf 1,35% Ap30 EurUltimo: 94,68Cedola: 0,675Scadenza: 01/04/2030IT0005383309</t>
+          <t>IT0005383309 -Btp Tf 1,35% Ap30 EurUltimo: 94,80Cedola: 0,675Scadenza: 01/04/2030IT0005383309</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2691,7 +2685,7 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>94.68000000000001</v>
+        <v>94.8</v>
       </c>
       <c r="D56" t="n">
         <v>0.675</v>
@@ -2705,7 +2699,7 @@
         <v>1.35</v>
       </c>
       <c r="G56" t="n">
-        <v>1.425</v>
+        <v>1.424</v>
       </c>
       <c r="H56" t="n">
         <v>10</v>
@@ -2714,22 +2708,22 @@
         <v>106.75</v>
       </c>
       <c r="J56" t="n">
-        <v>12.06999999999999</v>
+        <v>11.95</v>
       </c>
       <c r="K56" t="n">
-        <v>10.561</v>
+        <v>10.456</v>
       </c>
       <c r="L56" t="n">
-        <v>2.599</v>
+        <v>2.577</v>
       </c>
       <c r="M56" t="n">
-        <v>2.274</v>
+        <v>2.254</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>IT0005387052 -Btpi Tf 0,4% Mg30 EurUltimo: 97,38Cedola: 0,20Scadenza: 15/05/2030IT0005387052</t>
+          <t>IT0005387052 -Btpi Tf 0,4% Mg30 EurUltimo: 97,49Cedola: 0,20Scadenza: 15/05/2030IT0005387052</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2738,7 +2732,7 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>97.38</v>
+        <v>97.48999999999999</v>
       </c>
       <c r="D57" t="n">
         <v>0.2</v>
@@ -2761,22 +2755,22 @@
         <v>102</v>
       </c>
       <c r="J57" t="n">
-        <v>4.620000000000005</v>
+        <v>4.510000000000005</v>
       </c>
       <c r="K57" t="n">
-        <v>4.042</v>
+        <v>3.946</v>
       </c>
       <c r="L57" t="n">
-        <v>0.969</v>
+        <v>0.948</v>
       </c>
       <c r="M57" t="n">
-        <v>0.847</v>
+        <v>0.829</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>IT0005388175 -Btp Italia Ot27 EurUltimo: 99,88Cedola: 0,325Scadenza: 28/10/2027IT0005388175</t>
+          <t>IT0005388175 -Btp Italia Ot27 EurUltimo: 99,95Cedola: 0,325Scadenza: 28/10/2027IT0005388175</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2785,7 +2779,7 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>99.88</v>
+        <v>99.95</v>
       </c>
       <c r="D58" t="n">
         <v>0.325</v>
@@ -2808,22 +2802,22 @@
         <v>101.625</v>
       </c>
       <c r="J58" t="n">
-        <v>1.745000000000005</v>
+        <v>1.674999999999997</v>
       </c>
       <c r="K58" t="n">
-        <v>1.526</v>
+        <v>1.465</v>
       </c>
       <c r="L58" t="n">
-        <v>0.787</v>
+        <v>0.758</v>
       </c>
       <c r="M58" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.663</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>IT0005390874 -Btp Tf 0,85% Ge27 EurUltimo: 98,43Cedola: 0,425Scadenza: 15/01/2027IT0005390874</t>
+          <t>IT0005390874 -Btp Tf 0,85% Ge27 EurUltimo: 98,45Cedola: 0,425Scadenza: 15/01/2027IT0005390874</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2832,7 +2826,7 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>98.43000000000001</v>
+        <v>98.45</v>
       </c>
       <c r="D59" t="n">
         <v>0.425</v>
@@ -2855,22 +2849,22 @@
         <v>101.275</v>
       </c>
       <c r="J59" t="n">
-        <v>2.844999999999999</v>
+        <v>2.825000000000003</v>
       </c>
       <c r="K59" t="n">
-        <v>2.489</v>
+        <v>2.471</v>
       </c>
       <c r="L59" t="n">
-        <v>1.985</v>
+        <v>1.982</v>
       </c>
       <c r="M59" t="n">
-        <v>1.736</v>
+        <v>1.734</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>IT0005398406 -Btp Tf 2,45% St50 EurUltimo: 73,43Cedola: 1,225Scadenza: 01/09/2050IT0005398406</t>
+          <t>IT0005398406 -Btp Tf 2,45% St50 EurUltimo: 73,49Cedola: 1,225Scadenza: 01/09/2050IT0005398406</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2879,7 +2873,7 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>73.43000000000001</v>
+        <v>73.48999999999999</v>
       </c>
       <c r="D60" t="n">
         <v>1.225</v>
@@ -2893,7 +2887,7 @@
         <v>2.45</v>
       </c>
       <c r="G60" t="n">
-        <v>3.336</v>
+        <v>3.333</v>
       </c>
       <c r="H60" t="n">
         <v>51</v>
@@ -2902,22 +2896,22 @@
         <v>162.475</v>
       </c>
       <c r="J60" t="n">
-        <v>89.04499999999999</v>
+        <v>88.985</v>
       </c>
       <c r="K60" t="n">
-        <v>77.914</v>
+        <v>77.861</v>
       </c>
       <c r="L60" t="n">
-        <v>3.55</v>
+        <v>3.549</v>
       </c>
       <c r="M60" t="n">
-        <v>3.106</v>
+        <v>3.105</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>IT0005402117 -Btp Tf 1,45% Mz36 EurUltimo: 82,06Cedola: 0,725Scadenza: 01/03/2036IT0005402117</t>
+          <t>IT0005402117 -Btp Tf 1,45% Mz36 EurUltimo: 82,20Cedola: 0,725Scadenza: 01/03/2036IT0005402117</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2926,7 +2920,7 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>82.06</v>
+        <v>82.2</v>
       </c>
       <c r="D61" t="n">
         <v>0.725</v>
@@ -2940,7 +2934,7 @@
         <v>1.45</v>
       </c>
       <c r="G61" t="n">
-        <v>1.766</v>
+        <v>1.763</v>
       </c>
       <c r="H61" t="n">
         <v>22</v>
@@ -2949,22 +2943,22 @@
         <v>115.95</v>
       </c>
       <c r="J61" t="n">
-        <v>33.89</v>
+        <v>33.75</v>
       </c>
       <c r="K61" t="n">
-        <v>29.653</v>
+        <v>29.531</v>
       </c>
       <c r="L61" t="n">
-        <v>3.207</v>
+        <v>3.197</v>
       </c>
       <c r="M61" t="n">
-        <v>2.806</v>
+        <v>2.797</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>IT0005403396 -Btp Tf 0,95% Ag30 EurUltimo: 92,11Cedola: 0,475Scadenza: 01/08/2030IT0005403396</t>
+          <t>IT0005403396 -Btp Tf 0,95% Ag30 EurUltimo: 92,30Cedola: 0,475Scadenza: 01/08/2030IT0005403396</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2973,7 +2967,7 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>92.11</v>
+        <v>92.3</v>
       </c>
       <c r="D62" t="n">
         <v>0.475</v>
@@ -2987,7 +2981,7 @@
         <v>0.95</v>
       </c>
       <c r="G62" t="n">
-        <v>1.031</v>
+        <v>1.029</v>
       </c>
       <c r="H62" t="n">
         <v>10</v>
@@ -2996,22 +2990,22 @@
         <v>104.75</v>
       </c>
       <c r="J62" t="n">
-        <v>12.64</v>
+        <v>12.45</v>
       </c>
       <c r="K62" t="n">
-        <v>11.06</v>
+        <v>10.893</v>
       </c>
       <c r="L62" t="n">
-        <v>2.539</v>
+        <v>2.505</v>
       </c>
       <c r="M62" t="n">
-        <v>2.221</v>
+        <v>2.191</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>IT0005413171 -Btp Tf 1,65% Dc30 EurUltimo: 94,69Cedola: 0,825Scadenza: 01/12/2030IT0005413171</t>
+          <t>IT0005413171 -Btp Tf 1,65% Dc30 EurUltimo: 94,85Cedola: 0,825Scadenza: 01/12/2030IT0005413171</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -3020,7 +3014,7 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>94.69</v>
+        <v>94.84999999999999</v>
       </c>
       <c r="D63" t="n">
         <v>0.825</v>
@@ -3034,7 +3028,7 @@
         <v>1.65</v>
       </c>
       <c r="G63" t="n">
-        <v>1.742</v>
+        <v>1.739</v>
       </c>
       <c r="H63" t="n">
         <v>11</v>
@@ -3043,22 +3037,22 @@
         <v>109.075</v>
       </c>
       <c r="J63" t="n">
-        <v>14.38500000000001</v>
+        <v>14.22500000000001</v>
       </c>
       <c r="K63" t="n">
-        <v>12.586</v>
+        <v>12.446</v>
       </c>
       <c r="L63" t="n">
-        <v>2.707</v>
+        <v>2.681</v>
       </c>
       <c r="M63" t="n">
-        <v>2.368</v>
+        <v>2.345</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>IT0005415291 -Btp Futura Lg30 EurUltimo: 94,01Cedola: 0,65Scadenza: 14/07/2030IT0005415291</t>
+          <t>IT0005415291 -Btp Futura Lg30 EurUltimo: 93,91Cedola: 0,65Scadenza: 14/07/2030IT0005415291</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -3067,7 +3061,7 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>94.01000000000001</v>
+        <v>93.91</v>
       </c>
       <c r="D64" t="n">
         <v>0.65</v>
@@ -3081,7 +3075,7 @@
         <v>1.3</v>
       </c>
       <c r="G64" t="n">
-        <v>1.382</v>
+        <v>1.384</v>
       </c>
       <c r="H64" t="n">
         <v>10</v>
@@ -3090,28 +3084,31 @@
         <v>106.5</v>
       </c>
       <c r="J64" t="n">
-        <v>12.48999999999999</v>
+        <v>12.59</v>
       </c>
       <c r="K64" t="n">
-        <v>10.928</v>
+        <v>11.016</v>
       </c>
       <c r="L64" t="n">
-        <v>2.534</v>
+        <v>2.558</v>
       </c>
       <c r="M64" t="n">
-        <v>2.217</v>
+        <v>2.238</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>IT0005415416 -Btpi Tf 0,65% Mg26 EurUltimo:Cedola: 0,325Scadenza: 15/05/2026IT0005415416</t>
+          <t>IT0005415416 -Btpi Tf 0,65% Mg26 EurUltimo: 99,609Cedola: 0,325Scadenza: 15/05/2026IT0005415416</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
           <t>Btpi Tf 0,65% Mg26 Eur</t>
         </is>
+      </c>
+      <c r="C65" t="n">
+        <v>99.60899999999999</v>
       </c>
       <c r="D65" t="n">
         <v>0.325</v>
@@ -3124,17 +3121,32 @@
       <c r="F65" t="n">
         <v>0.65</v>
       </c>
+      <c r="G65" t="n">
+        <v>0.652</v>
+      </c>
       <c r="H65" t="n">
         <v>2</v>
       </c>
       <c r="I65" t="n">
         <v>100.65</v>
       </c>
+      <c r="J65" t="n">
+        <v>1.041000000000011</v>
+      </c>
+      <c r="K65" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="L65" t="n">
+        <v>1.381</v>
+      </c>
+      <c r="M65" t="n">
+        <v>1.208</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>IT0005416570 -Btp Tf 0,95% St27 EurUltimo: 97,68Cedola: 0,475Scadenza: 15/09/2027IT0005416570</t>
+          <t>IT0005416570 -Btp Tf 0,95% St27 EurUltimo: 97,78Cedola: 0,475Scadenza: 15/09/2027IT0005416570</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -3143,7 +3155,7 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>97.68000000000001</v>
+        <v>97.78</v>
       </c>
       <c r="D66" t="n">
         <v>0.475</v>
@@ -3157,7 +3169,7 @@
         <v>0.95</v>
       </c>
       <c r="G66" t="n">
-        <v>0.972</v>
+        <v>0.971</v>
       </c>
       <c r="H66" t="n">
         <v>5</v>
@@ -3166,22 +3178,22 @@
         <v>102.375</v>
       </c>
       <c r="J66" t="n">
-        <v>4.694999999999993</v>
+        <v>4.594999999999999</v>
       </c>
       <c r="K66" t="n">
-        <v>4.108</v>
+        <v>4.02</v>
       </c>
       <c r="L66" t="n">
-        <v>2.237</v>
+        <v>2.198</v>
       </c>
       <c r="M66" t="n">
-        <v>1.957</v>
+        <v>1.923</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>IT0005419848 -Btp Tf 0,50% Fb26 EurUltimo: 99,31Cedola: 0,25Scadenza: 01/02/2026IT0005419848</t>
+          <t>IT0005419848 -Btp Tf 0,50% Fb26 EurUltimo: 99,323Cedola: 0,25Scadenza: 01/02/2026IT0005419848</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -3190,7 +3202,7 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>99.31</v>
+        <v>99.32299999999999</v>
       </c>
       <c r="D67" t="n">
         <v>0.25</v>
@@ -3213,22 +3225,22 @@
         <v>100.25</v>
       </c>
       <c r="J67" t="n">
-        <v>0.9399999999999977</v>
+        <v>0.9270000000000067</v>
       </c>
       <c r="K67" t="n">
-        <v>0.822</v>
+        <v>0.8110000000000001</v>
       </c>
       <c r="L67" t="n">
-        <v>1.96</v>
+        <v>1.967</v>
       </c>
       <c r="M67" t="n">
-        <v>1.714</v>
+        <v>1.721</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>IT0005421703 -Btp Tf 1,8% Mz41 EurUltimo: 75,76Cedola: 0,90Scadenza: 01/03/2041IT0005421703</t>
+          <t>IT0005421703 -Btp Tf 1,8% Mz41 EurUltimo: 75,87Cedola: 0,90Scadenza: 01/03/2041IT0005421703</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -3237,7 +3249,7 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>75.76000000000001</v>
+        <v>75.87</v>
       </c>
       <c r="D68" t="n">
         <v>0.9</v>
@@ -3251,7 +3263,7 @@
         <v>1.8</v>
       </c>
       <c r="G68" t="n">
-        <v>2.375</v>
+        <v>2.372</v>
       </c>
       <c r="H68" t="n">
         <v>32</v>
@@ -3260,22 +3272,22 @@
         <v>128.8</v>
       </c>
       <c r="J68" t="n">
-        <v>53.04000000000001</v>
+        <v>52.93000000000001</v>
       </c>
       <c r="K68" t="n">
-        <v>46.41</v>
+        <v>46.313</v>
       </c>
       <c r="L68" t="n">
-        <v>3.407</v>
+        <v>3.401</v>
       </c>
       <c r="M68" t="n">
-        <v>2.981</v>
+        <v>2.975</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>IT0005422891 -Btp Tf 0,90% Ap31 EurUltimo: 90,18Cedola: 0,45Scadenza: 01/04/2031IT0005422891</t>
+          <t>IT0005422891 -Btp Tf 0,90% Ap31 EurUltimo: 90,38Cedola: 0,45Scadenza: 01/04/2031IT0005422891</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -3284,7 +3296,7 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>90.18000000000001</v>
+        <v>90.38</v>
       </c>
       <c r="D69" t="n">
         <v>0.45</v>
@@ -3298,7 +3310,7 @@
         <v>0.9</v>
       </c>
       <c r="G69" t="n">
-        <v>0.998</v>
+        <v>0.995</v>
       </c>
       <c r="H69" t="n">
         <v>12</v>
@@ -3307,22 +3319,22 @@
         <v>105.4</v>
       </c>
       <c r="J69" t="n">
-        <v>15.22</v>
+        <v>15.02000000000001</v>
       </c>
       <c r="K69" t="n">
-        <v>13.317</v>
+        <v>13.142</v>
       </c>
       <c r="L69" t="n">
-        <v>2.696</v>
+        <v>2.665</v>
       </c>
       <c r="M69" t="n">
-        <v>2.359</v>
+        <v>2.331</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>IT0005425233 -Btp Tf 1,7% St51 EurUltimo: 61,64Cedola: 0,85Scadenza: 01/09/2051IT0005425233</t>
+          <t>IT0005425233 -Btp Tf 1,7% St51 EurUltimo: 61,56Cedola: 0,85Scadenza: 01/09/2051IT0005425233</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -3331,7 +3343,7 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>61.64</v>
+        <v>61.56</v>
       </c>
       <c r="D70" t="n">
         <v>0.85</v>
@@ -3345,7 +3357,7 @@
         <v>1.7</v>
       </c>
       <c r="G70" t="n">
-        <v>2.757</v>
+        <v>2.761</v>
       </c>
       <c r="H70" t="n">
         <v>53</v>
@@ -3354,22 +3366,22 @@
         <v>145.05</v>
       </c>
       <c r="J70" t="n">
-        <v>83.41000000000001</v>
+        <v>83.49000000000001</v>
       </c>
       <c r="K70" t="n">
-        <v>72.983</v>
+        <v>73.053</v>
       </c>
       <c r="L70" t="n">
-        <v>3.198</v>
+        <v>3.202</v>
       </c>
       <c r="M70" t="n">
-        <v>2.798</v>
+        <v>2.801</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>IT0005425761 -Btp Futura Nv28 EurUltimo: 95,41Cedola: 0,30Scadenza: 17/11/2028IT0005425761</t>
+          <t>IT0005425761 -Btp Futura Nv28 EurUltimo: 95,32Cedola: 0,30Scadenza: 17/11/2028IT0005425761</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3378,7 +3390,7 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>95.41</v>
+        <v>95.31999999999999</v>
       </c>
       <c r="D71" t="n">
         <v>0.3</v>
@@ -3392,7 +3404,7 @@
         <v>0.6</v>
       </c>
       <c r="G71" t="n">
-        <v>0.628</v>
+        <v>0.629</v>
       </c>
       <c r="H71" t="n">
         <v>7</v>
@@ -3401,22 +3413,22 @@
         <v>102.1</v>
       </c>
       <c r="J71" t="n">
-        <v>6.689999999999998</v>
+        <v>6.780000000000001</v>
       </c>
       <c r="K71" t="n">
-        <v>5.853</v>
+        <v>5.932</v>
       </c>
       <c r="L71" t="n">
-        <v>2.043</v>
+        <v>2.076</v>
       </c>
       <c r="M71" t="n">
-        <v>1.787</v>
+        <v>1.816</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>IT0005433195 -Btp Tf 0,95% Mz37 EurUltimo: 75,25Cedola: 0,475Scadenza: 01/03/2037IT0005433195</t>
+          <t>IT0005433195 -Btp Tf 0,95% Mz37 EurUltimo: 75,38Cedola: 0,475Scadenza: 01/03/2037IT0005433195</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3425,7 +3437,7 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>75.25</v>
+        <v>75.38</v>
       </c>
       <c r="D72" t="n">
         <v>0.475</v>
@@ -3439,7 +3451,7 @@
         <v>0.95</v>
       </c>
       <c r="G72" t="n">
-        <v>1.262</v>
+        <v>1.26</v>
       </c>
       <c r="H72" t="n">
         <v>24</v>
@@ -3448,22 +3460,22 @@
         <v>111.4</v>
       </c>
       <c r="J72" t="n">
-        <v>36.15000000000001</v>
+        <v>36.02000000000001</v>
       </c>
       <c r="K72" t="n">
-        <v>31.631</v>
+        <v>31.517</v>
       </c>
       <c r="L72" t="n">
-        <v>3.125</v>
+        <v>3.116</v>
       </c>
       <c r="M72" t="n">
-        <v>2.734</v>
+        <v>2.726</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>IT0005433690 -Btp Tf 0,25% Mz28 EurUltimo: 95,14Cedola: 0,125Scadenza: 15/03/2028IT0005433690</t>
+          <t>IT0005433690 -Btp Tf 0,25% Mz28 EurUltimo: 95,27Cedola: 0,125Scadenza: 15/03/2028IT0005433690</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3472,7 +3484,7 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>95.14</v>
+        <v>95.27</v>
       </c>
       <c r="D73" t="n">
         <v>0.125</v>
@@ -3495,22 +3507,22 @@
         <v>100.75</v>
       </c>
       <c r="J73" t="n">
-        <v>5.609999999999999</v>
+        <v>5.480000000000004</v>
       </c>
       <c r="K73" t="n">
-        <v>4.908</v>
+        <v>4.795</v>
       </c>
       <c r="L73" t="n">
-        <v>2.159</v>
+        <v>2.116</v>
       </c>
       <c r="M73" t="n">
-        <v>1.889</v>
+        <v>1.851</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>IT0005436693 -Btp Tf 0,6% Ag31 EurUltimo: 87,75Cedola: 0,30Scadenza: 01/08/2031IT0005436693</t>
+          <t>IT0005436693 -Btp Tf 0,6% Ag31 EurUltimo: 87,94Cedola: 0,30Scadenza: 01/08/2031IT0005436693</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3519,7 +3531,7 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>87.75</v>
+        <v>87.94</v>
       </c>
       <c r="D74" t="n">
         <v>0.3</v>
@@ -3533,7 +3545,7 @@
         <v>0.6</v>
       </c>
       <c r="G74" t="n">
-        <v>0.6830000000000001</v>
+        <v>0.6820000000000001</v>
       </c>
       <c r="H74" t="n">
         <v>12</v>
@@ -3542,22 +3554,22 @@
         <v>103.6</v>
       </c>
       <c r="J74" t="n">
-        <v>15.84999999999999</v>
+        <v>15.66</v>
       </c>
       <c r="K74" t="n">
-        <v>13.868</v>
+        <v>13.702</v>
       </c>
       <c r="L74" t="n">
-        <v>2.651</v>
+        <v>2.623</v>
       </c>
       <c r="M74" t="n">
-        <v>2.319</v>
+        <v>2.295</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>IT0005436701 -Btpi Tf 0,15% Mg51 EurUltimo: 61,09Cedola: 0,075Scadenza: 15/05/2051IT0005436701</t>
+          <t>IT0005436701 -Btpi Tf 0,15% Mg51 EurUltimo: 60,90Cedola: 0,075Scadenza: 15/05/2051IT0005436701</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3566,7 +3578,7 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>61.09</v>
+        <v>60.9</v>
       </c>
       <c r="D75" t="n">
         <v>0.075</v>
@@ -3580,7 +3592,7 @@
         <v>0.15</v>
       </c>
       <c r="G75" t="n">
-        <v>0.245</v>
+        <v>0.246</v>
       </c>
       <c r="H75" t="n">
         <v>52</v>
@@ -3589,22 +3601,22 @@
         <v>103.9</v>
       </c>
       <c r="J75" t="n">
-        <v>42.81</v>
+        <v>43.00000000000001</v>
       </c>
       <c r="K75" t="n">
-        <v>37.458</v>
+        <v>37.625</v>
       </c>
       <c r="L75" t="n">
-        <v>1.66</v>
+        <v>1.668</v>
       </c>
       <c r="M75" t="n">
-        <v>1.452</v>
+        <v>1.459</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>IT0005437147 -Btp Tf 0% Ap26 EurUltimo: 98,794Cedola:Scadenza: 01/04/2026IT0005437147</t>
+          <t>IT0005437147 -Btp Tf 0% Ap26 EurUltimo: 98,808Cedola:Scadenza: 01/04/2026IT0005437147</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3613,7 +3625,7 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>98.794</v>
+        <v>98.80800000000001</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
@@ -3627,7 +3639,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>IT0005438004 -Btpgreen 1,5%Ap45eurUltimo: 66,23Cedola: 0,75Scadenza: 30/04/2045IT0005438004</t>
+          <t>IT0005438004 -Btpgreen 1,5%Ap45eurUltimo: 66,25Cedola: 0,75Scadenza: 30/04/2045IT0005438004</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3636,7 +3648,7 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>66.23</v>
+        <v>66.25</v>
       </c>
       <c r="D77" t="n">
         <v>0.75</v>
@@ -3659,10 +3671,10 @@
         <v>130</v>
       </c>
       <c r="J77" t="n">
-        <v>63.77</v>
+        <v>63.75</v>
       </c>
       <c r="K77" t="n">
-        <v>55.798</v>
+        <v>55.781</v>
       </c>
       <c r="L77" t="n">
         <v>3.231</v>
@@ -3674,7 +3686,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>IT0005441883 -Btp Tf 2,15% Mz72 EurUltimo: 58,70Cedola: 1,075Scadenza: 01/03/2072IT0005441883</t>
+          <t>IT0005441883 -Btp Tf 2,15% Mz72 EurUltimo: 58,63Cedola: 1,075Scadenza: 01/03/2072IT0005441883</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3683,7 +3695,7 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>58.7</v>
+        <v>58.63</v>
       </c>
       <c r="D78" t="n">
         <v>1.075</v>
@@ -3697,7 +3709,7 @@
         <v>2.15</v>
       </c>
       <c r="G78" t="n">
-        <v>3.662</v>
+        <v>3.667</v>
       </c>
       <c r="H78" t="n">
         <v>94</v>
@@ -3706,22 +3718,22 @@
         <v>201.05</v>
       </c>
       <c r="J78" t="n">
-        <v>142.35</v>
+        <v>142.42</v>
       </c>
       <c r="K78" t="n">
-        <v>124.556</v>
+        <v>124.617</v>
       </c>
       <c r="L78" t="n">
-        <v>3.055</v>
+        <v>3.057</v>
       </c>
       <c r="M78" t="n">
-        <v>2.673</v>
+        <v>2.674</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>IT0005442097 -Btp Futura Ap37 EurUltimo: 79,30Cedola: 0,60Scadenza: 27/04/2037IT0005442097</t>
+          <t>IT0005442097 -Btp Futura Ap37 EurUltimo: 79,53Cedola: 0,60Scadenza: 27/04/2037IT0005442097</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3730,7 +3742,7 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>79.3</v>
+        <v>79.53</v>
       </c>
       <c r="D79" t="n">
         <v>0.6</v>
@@ -3744,7 +3756,7 @@
         <v>1.2</v>
       </c>
       <c r="G79" t="n">
-        <v>1.513</v>
+        <v>1.508</v>
       </c>
       <c r="H79" t="n">
         <v>24</v>
@@ -3753,22 +3765,22 @@
         <v>114.4</v>
       </c>
       <c r="J79" t="n">
-        <v>35.10000000000001</v>
+        <v>34.87</v>
       </c>
       <c r="K79" t="n">
-        <v>30.712</v>
+        <v>30.511</v>
       </c>
       <c r="L79" t="n">
-        <v>2.994</v>
+        <v>2.977</v>
       </c>
       <c r="M79" t="n">
-        <v>2.619</v>
+        <v>2.604</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>IT0005445306 -Btp Tf 0,5% Lg28 EurUltimo: 95,05Cedola: 0,25Scadenza: 15/07/2028IT0005445306</t>
+          <t>IT0005445306 -Btp Tf 0,5% Lg28 EurUltimo: 95,22Cedola: 0,25Scadenza: 15/07/2028IT0005445306</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3777,7 +3789,7 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>95.05</v>
+        <v>95.22</v>
       </c>
       <c r="D80" t="n">
         <v>0.25</v>
@@ -3791,7 +3803,7 @@
         <v>0.5</v>
       </c>
       <c r="G80" t="n">
-        <v>0.526</v>
+        <v>0.525</v>
       </c>
       <c r="H80" t="n">
         <v>6</v>
@@ -3800,22 +3812,22 @@
         <v>101.5</v>
       </c>
       <c r="J80" t="n">
-        <v>6.450000000000003</v>
+        <v>6.280000000000001</v>
       </c>
       <c r="K80" t="n">
-        <v>5.643</v>
+        <v>5.495</v>
       </c>
       <c r="L80" t="n">
-        <v>2.2</v>
+        <v>2.148</v>
       </c>
       <c r="M80" t="n">
-        <v>1.925</v>
+        <v>1.879</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>IT0005449969 -Btp Tf 0,95% Dc31 EurUltimo: 88,85Cedola: 0,475Scadenza: 01/12/2031IT0005449969</t>
+          <t>IT0005449969 -Btp Tf 0,95% Dc31 EurUltimo: 89,03Cedola: 0,475Scadenza: 01/12/2031IT0005449969</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3824,7 +3836,7 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>88.84999999999999</v>
+        <v>89.03</v>
       </c>
       <c r="D81" t="n">
         <v>0.475</v>
@@ -3838,7 +3850,7 @@
         <v>0.95</v>
       </c>
       <c r="G81" t="n">
-        <v>1.069</v>
+        <v>1.067</v>
       </c>
       <c r="H81" t="n">
         <v>13</v>
@@ -3847,22 +3859,22 @@
         <v>106.175</v>
       </c>
       <c r="J81" t="n">
-        <v>17.325</v>
+        <v>17.145</v>
       </c>
       <c r="K81" t="n">
-        <v>15.159</v>
+        <v>15.001</v>
       </c>
       <c r="L81" t="n">
-        <v>2.744</v>
+        <v>2.719</v>
       </c>
       <c r="M81" t="n">
-        <v>2.401</v>
+        <v>2.379</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>IT0005454241 -Btp Tf 0% Ag26 EurUltimo: 98,272Cedola:Scadenza: 01/08/2026IT0005454241</t>
+          <t>IT0005454241 -Btp Tf 0% Ag26 EurUltimo: 98,252Cedola:Scadenza: 01/08/2026IT0005454241</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3871,7 +3883,7 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>98.27200000000001</v>
+        <v>98.252</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
@@ -3885,7 +3897,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>IT0005466013 -Btp Tf 0,95% Gn32 EurUltimo: 87,61Cedola: 0,475Scadenza: 01/06/2032IT0005466013</t>
+          <t>IT0005466013 -Btp Tf 0,95% Gn32 EurUltimo: 87,80Cedola: 0,475Scadenza: 01/06/2032IT0005466013</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3894,7 +3906,7 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>87.61</v>
+        <v>87.8</v>
       </c>
       <c r="D83" t="n">
         <v>0.475</v>
@@ -3908,7 +3920,7 @@
         <v>0.95</v>
       </c>
       <c r="G83" t="n">
-        <v>1.084</v>
+        <v>1.082</v>
       </c>
       <c r="H83" t="n">
         <v>14</v>
@@ -3917,22 +3929,22 @@
         <v>106.65</v>
       </c>
       <c r="J83" t="n">
-        <v>19.04000000000001</v>
+        <v>18.85000000000001</v>
       </c>
       <c r="K83" t="n">
-        <v>16.66</v>
+        <v>16.493</v>
       </c>
       <c r="L83" t="n">
-        <v>2.794</v>
+        <v>2.769</v>
       </c>
       <c r="M83" t="n">
-        <v>2.444</v>
+        <v>2.422</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>IT0005466351 -Btp Futura Nv33 EurUltimo: 87,53Cedola: 0,375Scadenza: 16/11/2033IT0005466351</t>
+          <t>IT0005466351 -Btp Futura Nv33 EurUltimo: 87,75Cedola: 0,375Scadenza: 16/11/2033IT0005466351</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3941,7 +3953,7 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>87.53</v>
+        <v>87.75</v>
       </c>
       <c r="D84" t="n">
         <v>0.375</v>
@@ -3955,7 +3967,7 @@
         <v>0.75</v>
       </c>
       <c r="G84" t="n">
-        <v>0.856</v>
+        <v>0.854</v>
       </c>
       <c r="H84" t="n">
         <v>17</v>
@@ -3964,22 +3976,22 @@
         <v>106.375</v>
       </c>
       <c r="J84" t="n">
-        <v>18.845</v>
+        <v>18.625</v>
       </c>
       <c r="K84" t="n">
-        <v>16.489</v>
+        <v>16.296</v>
       </c>
       <c r="L84" t="n">
-        <v>2.277</v>
+        <v>2.253</v>
       </c>
       <c r="M84" t="n">
-        <v>1.992</v>
+        <v>1.971</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>IT0005467482 -Btp Tf 0,45% Fb29 EurUltimo: 93,51Cedola: 0,225Scadenza: 15/02/2029IT0005467482</t>
+          <t>IT0005467482 -Btp Tf 0,45% Fb29 EurUltimo: 93,66Cedola: 0,225Scadenza: 15/02/2029IT0005467482</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3988,7 +4000,7 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>93.51000000000001</v>
+        <v>93.66</v>
       </c>
       <c r="D85" t="n">
         <v>0.225</v>
@@ -4002,7 +4014,7 @@
         <v>0.45</v>
       </c>
       <c r="G85" t="n">
-        <v>0.481</v>
+        <v>0.48</v>
       </c>
       <c r="H85" t="n">
         <v>8</v>
@@ -4011,22 +4023,22 @@
         <v>101.8</v>
       </c>
       <c r="J85" t="n">
-        <v>8.289999999999992</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="K85" t="n">
-        <v>7.253</v>
+        <v>7.122</v>
       </c>
       <c r="L85" t="n">
-        <v>2.354</v>
+        <v>2.317</v>
       </c>
       <c r="M85" t="n">
-        <v>2.059</v>
+        <v>2.027</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>IT0005480980 -Btp Tf 2,15% St52 EurUltimo: 67,47Cedola: 1,075Scadenza: 01/09/2052IT0005480980</t>
+          <t>IT0005480980 -Btp Tf 2,15% St52 EurUltimo: 67,33Cedola: 1,075Scadenza: 01/09/2052IT0005480980</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -4035,7 +4047,7 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>67.47</v>
+        <v>67.33</v>
       </c>
       <c r="D86" t="n">
         <v>1.075</v>
@@ -4049,7 +4061,7 @@
         <v>2.15</v>
       </c>
       <c r="G86" t="n">
-        <v>3.186</v>
+        <v>3.193</v>
       </c>
       <c r="H86" t="n">
         <v>55</v>
@@ -4058,16 +4070,16 @@
         <v>159.125</v>
       </c>
       <c r="J86" t="n">
-        <v>91.655</v>
+        <v>91.795</v>
       </c>
       <c r="K86" t="n">
-        <v>80.19799999999999</v>
+        <v>80.31999999999999</v>
       </c>
       <c r="L86" t="n">
-        <v>3.384</v>
+        <v>3.39</v>
       </c>
       <c r="M86" t="n">
-        <v>2.961</v>
+        <v>2.966</v>
       </c>
     </row>
     <row r="87">
@@ -4111,7 +4123,7 @@
         <v>9.082000000000001</v>
       </c>
       <c r="L87" t="n">
-        <v>1.336</v>
+        <v>1.337</v>
       </c>
       <c r="M87" t="n">
         <v>1.169</v>
@@ -4120,7 +4132,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>IT0005484552 -Btp Tf 1,1% Ap27 EurUltimo: 98,45Cedola: 0,55Scadenza: 01/04/2027IT0005484552</t>
+          <t>IT0005484552 -Btp Tf 1,1% Ap27 EurUltimo: 98,54Cedola: 0,55Scadenza: 01/04/2027IT0005484552</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -4129,7 +4141,7 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>98.45</v>
+        <v>98.54000000000001</v>
       </c>
       <c r="D88" t="n">
         <v>0.55</v>
@@ -4143,7 +4155,7 @@
         <v>1.1</v>
       </c>
       <c r="G88" t="n">
-        <v>1.117</v>
+        <v>1.116</v>
       </c>
       <c r="H88" t="n">
         <v>4</v>
@@ -4152,3085 +4164,3038 @@
         <v>102.2</v>
       </c>
       <c r="J88" t="n">
-        <v>3.75</v>
+        <v>3.659999999999997</v>
       </c>
       <c r="K88" t="n">
-        <v>3.281</v>
+        <v>3.202</v>
       </c>
       <c r="L88" t="n">
-        <v>2.285</v>
+        <v>2.241</v>
       </c>
       <c r="M88" t="n">
-        <v>1.999</v>
+        <v>1.96</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>IT0005493298 -Btp Tf 1,2% Ag25 EurUltimo: 99,989Cedola: 0,60Scadenza: 15/08/2025IT0005493298</t>
+          <t>IT0005494239 -Btp Tf 2,5% Dc32 EurUltimo: 96,58Cedola: 1,25Scadenza: 01/12/2032IT0005494239</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Btp Tf 1,2% Ag25 Eur</t>
+          <t>Btp Tf 2,5% Dc32 Eur</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>99.989</v>
+        <v>96.58</v>
       </c>
       <c r="D89" t="n">
-        <v>0.6</v>
+        <v>1.25</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>15-08-25</t>
+          <t>01-12-32</t>
         </is>
       </c>
       <c r="F89" t="n">
-        <v>1.2</v>
+        <v>2.5</v>
       </c>
       <c r="G89" t="n">
-        <v>1.2</v>
+        <v>2.588</v>
       </c>
       <c r="H89" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="I89" t="n">
-        <v>100.6</v>
+        <v>118.75</v>
       </c>
       <c r="J89" t="n">
-        <v>0.61099999999999</v>
+        <v>22.17</v>
       </c>
       <c r="K89" t="n">
-        <v>0.534</v>
+        <v>19.398</v>
       </c>
       <c r="L89" t="n">
-        <v>44.602</v>
+        <v>3.034</v>
       </c>
       <c r="M89" t="n">
-        <v>39.026</v>
+        <v>2.654</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>IT0005494239 -Btp Tf 2,5% Dc32 EurUltimo: 96,37Cedola: 1,25Scadenza: 01/12/2032IT0005494239</t>
+          <t>IT0005495731 -Btp Tf 2,80% Gn29 EurUltimo: 101,32Cedola: 1,40Scadenza: 15/06/2029IT0005495731</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Btp Tf 2,5% Dc32 Eur</t>
+          <t>Btp Tf 2,80% Gn29 Eur</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>96.37</v>
+        <v>101.32</v>
       </c>
       <c r="D90" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>01-12-32</t>
+          <t>15-06-29</t>
         </is>
       </c>
       <c r="F90" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="G90" t="n">
-        <v>2.594</v>
+        <v>2.763</v>
       </c>
       <c r="H90" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="I90" t="n">
-        <v>118.75</v>
+        <v>111.2</v>
       </c>
       <c r="J90" t="n">
-        <v>22.38</v>
+        <v>9.88000000000001</v>
       </c>
       <c r="K90" t="n">
-        <v>19.582</v>
+        <v>8.645</v>
       </c>
       <c r="L90" t="n">
-        <v>3.059</v>
+        <v>2.572</v>
       </c>
       <c r="M90" t="n">
-        <v>2.676</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>IT0005495731 -Btp Tf 2,80% Gn29 EurUltimo: 101,20Cedola: 1,40Scadenza: 15/06/2029IT0005495731</t>
+          <t>IT0005496770 -Btp Tf 3,25% Mz38 EurUltimo: 95,93Cedola: 1,625Scadenza: 01/03/2038IT0005496770</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Btp Tf 2,80% Gn29 Eur</t>
+          <t>Btp Tf 3,25% Mz38 Eur</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>101.2</v>
+        <v>95.93000000000001</v>
       </c>
       <c r="D91" t="n">
-        <v>1.4</v>
+        <v>1.625</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>15-06-29</t>
+          <t>01-03-38</t>
         </is>
       </c>
       <c r="F91" t="n">
-        <v>2.8</v>
+        <v>3.25</v>
       </c>
       <c r="G91" t="n">
-        <v>2.766</v>
+        <v>3.387</v>
       </c>
       <c r="H91" t="n">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="I91" t="n">
-        <v>111.2</v>
+        <v>142.25</v>
       </c>
       <c r="J91" t="n">
-        <v>10</v>
+        <v>46.31999999999999</v>
       </c>
       <c r="K91" t="n">
-        <v>8.75</v>
+        <v>40.529</v>
       </c>
       <c r="L91" t="n">
-        <v>2.597</v>
+        <v>3.689</v>
       </c>
       <c r="M91" t="n">
-        <v>2.272</v>
+        <v>3.227</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>IT0005496770 -Btp Tf 3,25% Mz38 EurUltimo: 95,72Cedola: 1,625Scadenza: 01/03/2038IT0005496770</t>
+          <t>IT0005497000 -Btp Italia Gn30 EurUltimo: 101,17Cedola: 0,80Scadenza: 28/06/2030IT0005497000</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Btp Tf 3,25% Mz38 Eur</t>
+          <t>Btp Italia Gn30 Eur</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>95.72</v>
+        <v>101.17</v>
       </c>
       <c r="D92" t="n">
-        <v>1.625</v>
+        <v>0.8</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>01-03-38</t>
+          <t>28-06-30</t>
         </is>
       </c>
       <c r="F92" t="n">
-        <v>3.25</v>
+        <v>1.6</v>
       </c>
       <c r="G92" t="n">
-        <v>3.395</v>
+        <v>1.581</v>
       </c>
       <c r="H92" t="n">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="I92" t="n">
-        <v>142.25</v>
+        <v>108</v>
       </c>
       <c r="J92" t="n">
-        <v>46.53</v>
+        <v>6.829999999999998</v>
       </c>
       <c r="K92" t="n">
-        <v>40.713</v>
+        <v>5.976</v>
       </c>
       <c r="L92" t="n">
-        <v>3.703</v>
+        <v>1.4</v>
       </c>
       <c r="M92" t="n">
-        <v>3.24</v>
+        <v>1.224</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>IT0005497000 -Btp Italia Gn30 EurUltimo: 101,10Cedola: 0,80Scadenza: 28/06/2030IT0005497000</t>
+          <t>IT0005498685 -Btpstripital Zc Dec25 EurUltimo:Cedola:Scadenza: 15/12/2025IT0005498685</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Btp Italia Gn30 Eur</t>
-        </is>
-      </c>
-      <c r="C93" t="n">
-        <v>101.1</v>
-      </c>
-      <c r="D93" t="n">
-        <v>0.8</v>
+          <t>Btpstripital Zc Dec25 Eur</t>
+        </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>28-06-30</t>
-        </is>
-      </c>
-      <c r="F93" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="G93" t="n">
-        <v>1.582</v>
+          <t>15-12-25</t>
+        </is>
       </c>
       <c r="H93" t="n">
-        <v>10</v>
-      </c>
-      <c r="I93" t="n">
-        <v>108</v>
-      </c>
-      <c r="J93" t="n">
-        <v>6.900000000000006</v>
-      </c>
-      <c r="K93" t="n">
-        <v>6.037</v>
-      </c>
-      <c r="L93" t="n">
-        <v>1.412</v>
-      </c>
-      <c r="M93" t="n">
-        <v>1.235</v>
+        <v>1</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>IT0005498685 -Btpstripital Zc Dec25 EurUltimo:Cedola:Scadenza: 15/12/2025IT0005498685</t>
+          <t>IT0005498693 -Btpstripital Zc Jun26 EurUltimo:Cedola:Scadenza: 15/06/2026IT0005498693</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Btpstripital Zc Dec25 Eur</t>
+          <t>Btpstripital Zc Jun26 Eur</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>15-12-25</t>
+          <t>15-06-26</t>
         </is>
       </c>
       <c r="H94" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>IT0005498693 -Btpstripital Zc Jun26 EurUltimo:Cedola:Scadenza: 15/06/2026IT0005498693</t>
+          <t>IT0005498701 -Btpstripital Zc Dec26 EurUltimo:Cedola:Scadenza: 15/12/2026IT0005498701</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Btpstripital Zc Jun26 Eur</t>
+          <t>Btpstripital Zc Dec26 Eur</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>15-06-26</t>
+          <t>15-12-26</t>
         </is>
       </c>
       <c r="H95" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>IT0005498701 -Btpstripital Zc Dec26 EurUltimo:Cedola:Scadenza: 15/12/2026IT0005498701</t>
+          <t>IT0005498719 -Btpstripital Zc Jun27 EurUltimo:Cedola:Scadenza: 15/06/2027IT0005498719</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Btpstripital Zc Dec26 Eur</t>
+          <t>Btpstripital Zc Jun27 Eur</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>15-12-26</t>
+          <t>15-06-27</t>
         </is>
       </c>
       <c r="H96" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>IT0005498719 -Btpstripital Zc Jun27 EurUltimo:Cedola:Scadenza: 15/06/2027IT0005498719</t>
+          <t>IT0005498727 -Btpstripital Zc Dec27 EurUltimo:Cedola:Scadenza: 15/12/2027IT0005498727</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Btpstripital Zc Jun27 Eur</t>
+          <t>Btpstripital Zc Dec27 Eur</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>15-06-27</t>
+          <t>15-12-27</t>
         </is>
       </c>
       <c r="H97" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>IT0005498727 -Btpstripital Zc Dec27 EurUltimo:Cedola:Scadenza: 15/12/2027IT0005498727</t>
+          <t>IT0005498735 -Btpstripital Zc Jun28 EurUltimo:Cedola:Scadenza: 15/06/2028IT0005498735</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Btpstripital Zc Dec27 Eur</t>
+          <t>Btpstripital Zc Jun28 Eur</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>15-12-27</t>
+          <t>15-06-28</t>
         </is>
       </c>
       <c r="H98" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>IT0005498735 -Btpstripital Zc Jun28 EurUltimo:Cedola:Scadenza: 15/06/2028IT0005498735</t>
+          <t>IT0005498743 -Btpstripital Zc Dec28 EurUltimo:Cedola:Scadenza: 15/12/2028IT0005498743</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Btpstripital Zc Jun28 Eur</t>
+          <t>Btpstripital Zc Dec28 Eur</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>15-06-28</t>
+          <t>15-12-28</t>
         </is>
       </c>
       <c r="H99" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>IT0005498743 -Btpstripital Zc Dec28 EurUltimo:Cedola:Scadenza: 15/12/2028IT0005498743</t>
+          <t>IT0005498750 -Btpstripital Zc Jun29 EurUltimo:Cedola:Scadenza: 15/06/2029IT0005498750</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Btpstripital Zc Dec28 Eur</t>
+          <t>Btpstripital Zc Jun29 Eur</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>15-12-28</t>
+          <t>15-06-29</t>
         </is>
       </c>
       <c r="H100" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>IT0005498750 -Btpstripital Zc Jun29 EurUltimo:Cedola:Scadenza: 15/06/2029IT0005498750</t>
+          <t>IT0005500068 -Btp Tf 2,65% Dc27 EurUltimo: 101,14Cedola: 1,325Scadenza: 01/12/2027IT0005500068</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Btpstripital Zc Jun29 Eur</t>
-        </is>
+          <t>Btp Tf 2,65% Dc27 Eur</t>
+        </is>
+      </c>
+      <c r="C101" t="n">
+        <v>101.14</v>
+      </c>
+      <c r="D101" t="n">
+        <v>1.325</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>15-06-29</t>
-        </is>
+          <t>01-12-27</t>
+        </is>
+      </c>
+      <c r="F101" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="G101" t="n">
+        <v>2.62</v>
       </c>
       <c r="H101" t="n">
-        <v>8</v>
+        <v>5</v>
+      </c>
+      <c r="I101" t="n">
+        <v>106.625</v>
+      </c>
+      <c r="J101" t="n">
+        <v>5.484999999999999</v>
+      </c>
+      <c r="K101" t="n">
+        <v>4.799</v>
+      </c>
+      <c r="L101" t="n">
+        <v>2.383</v>
+      </c>
+      <c r="M101" t="n">
+        <v>2.085</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>IT0005500068 -Btp Tf 2,65% Dc27 EurUltimo: 101,04Cedola: 1,325Scadenza: 01/12/2027IT0005500068</t>
+          <t>IT0005508590 -Btpgreen 4%Ap35eurUltimo: 105,90Cedola: 2,00Scadenza: 30/04/2035IT0005508590</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Btp Tf 2,65% Dc27 Eur</t>
+          <t>Btpgreen 4%Ap35eur</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>101.04</v>
+        <v>105.9</v>
       </c>
       <c r="D102" t="n">
-        <v>1.325</v>
+        <v>2</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>01-12-27</t>
+          <t>30-04-35</t>
         </is>
       </c>
       <c r="F102" t="n">
-        <v>2.65</v>
+        <v>4</v>
       </c>
       <c r="G102" t="n">
-        <v>2.622</v>
+        <v>3.777</v>
       </c>
       <c r="H102" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="I102" t="n">
-        <v>106.625</v>
+        <v>140</v>
       </c>
       <c r="J102" t="n">
-        <v>5.584999999999994</v>
+        <v>34.09999999999999</v>
       </c>
       <c r="K102" t="n">
-        <v>4.886</v>
+        <v>29.837</v>
       </c>
       <c r="L102" t="n">
-        <v>2.418</v>
+        <v>3.509</v>
       </c>
       <c r="M102" t="n">
-        <v>2.115</v>
+        <v>3.07</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>IT0005508590 -Btpgreen 4%Ap35eurUltimo: 105,67Cedola: 2,00Scadenza: 30/04/2035IT0005508590</t>
+          <t>IT0005514473 -Btp Tf 3,5% Ge26 EurUltimo: 100,619Cedola: 1,75Scadenza: 15/01/2026IT0005514473</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Btpgreen 4%Ap35eur</t>
+          <t>Btp Tf 3,5% Ge26 Eur</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>105.67</v>
+        <v>100.619</v>
       </c>
       <c r="D103" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>30-04-35</t>
+          <t>15-01-26</t>
         </is>
       </c>
       <c r="F103" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="G103" t="n">
-        <v>3.785</v>
+        <v>3.478</v>
       </c>
       <c r="H103" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="I103" t="n">
-        <v>140</v>
+        <v>101.75</v>
       </c>
       <c r="J103" t="n">
-        <v>34.33</v>
+        <v>1.131</v>
       </c>
       <c r="K103" t="n">
-        <v>30.038</v>
+        <v>0.989</v>
       </c>
       <c r="L103" t="n">
-        <v>3.529</v>
+        <v>2.663</v>
       </c>
       <c r="M103" t="n">
-        <v>3.087</v>
+        <v>2.33</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>IT0005514473 -Btp Tf 3,5% Ge26 EurUltimo: 100,627Cedola: 1,75Scadenza: 15/01/2026IT0005514473</t>
+          <t>IT0005517195 -Btp Italia Nv28 EurUltimo: 101,69Cedola: 0,80Scadenza: 22/11/2028IT0005517195</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Btp Tf 3,5% Ge26 Eur</t>
+          <t>Btp Italia Nv28 Eur</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>100.627</v>
+        <v>101.69</v>
       </c>
       <c r="D104" t="n">
-        <v>1.75</v>
+        <v>0.8</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>15-01-26</t>
+          <t>22-11-28</t>
         </is>
       </c>
       <c r="F104" t="n">
-        <v>3.5</v>
+        <v>1.6</v>
       </c>
       <c r="G104" t="n">
-        <v>3.478</v>
+        <v>1.573</v>
       </c>
       <c r="H104" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I104" t="n">
-        <v>101.75</v>
+        <v>105.6</v>
       </c>
       <c r="J104" t="n">
-        <v>1.123000000000005</v>
+        <v>3.909999999999997</v>
       </c>
       <c r="K104" t="n">
-        <v>0.982</v>
+        <v>3.421</v>
       </c>
       <c r="L104" t="n">
-        <v>2.594</v>
+        <v>1.192</v>
       </c>
       <c r="M104" t="n">
-        <v>2.269</v>
+        <v>1.043</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>IT0005517195 -Btp Italia Nv28 EurUltimo: 101,60Cedola: 0,80Scadenza: 22/11/2028IT0005517195</t>
+          <t>IT0005518128 -Btp Tf 4,40% Mg33 EurUltimo: 108,82Cedola: 2,20Scadenza: 01/05/2033IT0005518128</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Btp Italia Nv28 Eur</t>
+          <t>Btp Tf 4,40% Mg33 Eur</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>101.6</v>
+        <v>108.82</v>
       </c>
       <c r="D105" t="n">
-        <v>0.8</v>
+        <v>2.2</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>22-11-28</t>
+          <t>01-05-33</t>
         </is>
       </c>
       <c r="F105" t="n">
-        <v>1.6</v>
+        <v>4.4</v>
       </c>
       <c r="G105" t="n">
-        <v>1.574</v>
+        <v>4.043</v>
       </c>
       <c r="H105" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="I105" t="n">
-        <v>105.6</v>
+        <v>135.2</v>
       </c>
       <c r="J105" t="n">
-        <v>4</v>
+        <v>26.38</v>
       </c>
       <c r="K105" t="n">
-        <v>3.5</v>
+        <v>23.082</v>
       </c>
       <c r="L105" t="n">
-        <v>1.216</v>
+        <v>3.416</v>
       </c>
       <c r="M105" t="n">
-        <v>1.064</v>
+        <v>2.989</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>IT0005518128 -Btp Tf 4,40% Mg33 EurUltimo: 108,63Cedola: 2,20Scadenza: 01/05/2033IT0005518128</t>
+          <t>IT0005519787 -Btp Tf 3,85% Dc29 EurUltimo: 105,35Cedola: 1,925Scadenza: 15/12/2029IT0005519787</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Btp Tf 4,40% Mg33 Eur</t>
+          <t>Btp Tf 3,85% Dc29 Eur</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>108.63</v>
+        <v>105.35</v>
       </c>
       <c r="D106" t="n">
-        <v>2.2</v>
+        <v>1.925</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>01-05-33</t>
+          <t>15-12-29</t>
         </is>
       </c>
       <c r="F106" t="n">
-        <v>4.4</v>
+        <v>3.85</v>
       </c>
       <c r="G106" t="n">
-        <v>4.05</v>
+        <v>3.654</v>
       </c>
       <c r="H106" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="I106" t="n">
-        <v>135.2</v>
+        <v>117.325</v>
       </c>
       <c r="J106" t="n">
-        <v>26.56999999999999</v>
+        <v>11.97500000000001</v>
       </c>
       <c r="K106" t="n">
-        <v>23.248</v>
+        <v>10.478</v>
       </c>
       <c r="L106" t="n">
-        <v>3.437</v>
+        <v>2.757</v>
       </c>
       <c r="M106" t="n">
-        <v>3.007</v>
+        <v>2.412</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>IT0005519787 -Btp Tf 3,85% Dc29 EurUltimo: 105,18Cedola: 1,925Scadenza: 15/12/2029IT0005519787</t>
+          <t>IT0005521981 -Btp Tf 3,4% Ap28 EurUltimo: 103,03Cedola: 1,70Scadenza: 01/04/2028IT0005521981</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Btp Tf 3,85% Dc29 Eur</t>
+          <t>Btp Tf 3,4% Ap28 Eur</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>105.18</v>
+        <v>103.03</v>
       </c>
       <c r="D107" t="n">
-        <v>1.925</v>
+        <v>1.7</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>15-12-29</t>
+          <t>01-04-28</t>
         </is>
       </c>
       <c r="F107" t="n">
-        <v>3.85</v>
+        <v>3.4</v>
       </c>
       <c r="G107" t="n">
-        <v>3.66</v>
+        <v>3.3</v>
       </c>
       <c r="H107" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I107" t="n">
-        <v>117.325</v>
+        <v>110.2</v>
       </c>
       <c r="J107" t="n">
-        <v>12.145</v>
+        <v>7.170000000000002</v>
       </c>
       <c r="K107" t="n">
-        <v>10.626</v>
+        <v>6.273</v>
       </c>
       <c r="L107" t="n">
-        <v>2.791</v>
+        <v>2.72</v>
       </c>
       <c r="M107" t="n">
-        <v>2.442</v>
+        <v>2.38</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>IT0005521981 -Btp Tf 3,4% Ap28 EurUltimo: 102,91Cedola: 1,70Scadenza: 01/04/2028IT0005521981</t>
+          <t>IT0005526162 -Btpstripital Zc Dec29 EurUltimo:Cedola:Scadenza: 15/12/2029IT0005526162</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Btp Tf 3,4% Ap28 Eur</t>
-        </is>
-      </c>
-      <c r="C108" t="n">
-        <v>102.91</v>
-      </c>
-      <c r="D108" t="n">
-        <v>1.7</v>
+          <t>Btpstripital Zc Dec29 Eur</t>
+        </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>01-04-28</t>
-        </is>
-      </c>
-      <c r="F108" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="G108" t="n">
-        <v>3.303</v>
+          <t>15-12-29</t>
+        </is>
       </c>
       <c r="H108" t="n">
-        <v>6</v>
-      </c>
-      <c r="I108" t="n">
-        <v>110.2</v>
-      </c>
-      <c r="J108" t="n">
-        <v>7.290000000000006</v>
-      </c>
-      <c r="K108" t="n">
-        <v>6.378</v>
-      </c>
-      <c r="L108" t="n">
-        <v>2.757</v>
-      </c>
-      <c r="M108" t="n">
-        <v>2.412</v>
+        <v>9</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>IT0005526162 -Btpstripital Zc Dec29 EurUltimo:Cedola:Scadenza: 15/12/2029IT0005526162</t>
+          <t>IT0005530032 -Btp Tf 4,45% St43 EurUltimo: 105,51Cedola: 2,225Scadenza: 01/09/2043IT0005530032</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Btpstripital Zc Dec29 Eur</t>
-        </is>
+          <t>Btp Tf 4,45% St43 Eur</t>
+        </is>
+      </c>
+      <c r="C109" t="n">
+        <v>105.51</v>
+      </c>
+      <c r="D109" t="n">
+        <v>2.225</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>15-12-29</t>
-        </is>
+          <t>01-09-43</t>
+        </is>
+      </c>
+      <c r="F109" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="G109" t="n">
+        <v>4.217</v>
       </c>
       <c r="H109" t="n">
-        <v>9</v>
+        <v>37</v>
+      </c>
+      <c r="I109" t="n">
+        <v>182.325</v>
+      </c>
+      <c r="J109" t="n">
+        <v>76.81499999999998</v>
+      </c>
+      <c r="K109" t="n">
+        <v>67.21299999999999</v>
+      </c>
+      <c r="L109" t="n">
+        <v>4.252</v>
+      </c>
+      <c r="M109" t="n">
+        <v>3.72</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>IT0005530032 -Btp Tf 4,45% St43 EurUltimo: 105,36Cedola: 2,225Scadenza: 01/09/2043IT0005530032</t>
+          <t>IT0005532723 -Btp Italia Mz28 EurUltimo: 102,52Cedola: 1,00Scadenza: 14/03/2028IT0005532723</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Btp Tf 4,45% St43 Eur</t>
+          <t>Btp Italia Mz28 Eur</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>105.36</v>
+        <v>102.52</v>
       </c>
       <c r="D110" t="n">
-        <v>2.225</v>
+        <v>1</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>01-09-43</t>
+          <t>14-03-28</t>
         </is>
       </c>
       <c r="F110" t="n">
-        <v>4.45</v>
+        <v>2</v>
       </c>
       <c r="G110" t="n">
-        <v>4.223</v>
+        <v>1.95</v>
       </c>
       <c r="H110" t="n">
-        <v>37</v>
+        <v>6</v>
       </c>
       <c r="I110" t="n">
-        <v>182.325</v>
+        <v>106</v>
       </c>
       <c r="J110" t="n">
-        <v>76.96499999999999</v>
+        <v>3.480000000000004</v>
       </c>
       <c r="K110" t="n">
-        <v>67.34399999999999</v>
+        <v>3.045</v>
       </c>
       <c r="L110" t="n">
-        <v>4.258</v>
+        <v>1.345</v>
       </c>
       <c r="M110" t="n">
-        <v>3.725</v>
+        <v>1.176</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>IT0005532723 -Btp Italia Mz28 EurUltimo: 102,42Cedola: 1,00Scadenza: 14/03/2028IT0005532723</t>
+          <t>IT0005534141 -Btp Tf 4,5% Ot53 EurUltimo: 103,07Cedola: 2,25Scadenza: 01/10/2053IT0005534141</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Btp Italia Mz28 Eur</t>
+          <t>Btp Tf 4,5% Ot53 Eur</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>102.42</v>
+        <v>103.07</v>
       </c>
       <c r="D111" t="n">
-        <v>1</v>
+        <v>2.25</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>14-03-28</t>
+          <t>01-10-53</t>
         </is>
       </c>
       <c r="F111" t="n">
-        <v>2</v>
+        <v>4.5</v>
       </c>
       <c r="G111" t="n">
-        <v>1.952</v>
+        <v>4.365</v>
       </c>
       <c r="H111" t="n">
-        <v>6</v>
+        <v>57</v>
       </c>
       <c r="I111" t="n">
-        <v>106</v>
+        <v>228.25</v>
       </c>
       <c r="J111" t="n">
-        <v>3.579999999999998</v>
+        <v>125.18</v>
       </c>
       <c r="K111" t="n">
-        <v>3.132</v>
+        <v>109.532</v>
       </c>
       <c r="L111" t="n">
-        <v>1.379</v>
+        <v>4.446</v>
       </c>
       <c r="M111" t="n">
-        <v>1.206</v>
+        <v>3.89</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>IT0005534141 -Btp Tf 4,5% Ot53 EurUltimo: 103,12Cedola: 2,25Scadenza: 01/10/2053IT0005534141</t>
+          <t>IT0005538597 -Btp Tf 3,80% Ap26 EurUltimo: 101,187Cedola: 1,90Scadenza: 15/04/2026IT0005538597</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Btp Tf 4,5% Ot53 Eur</t>
+          <t>Btp Tf 3,80% Ap26 Eur</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>103.12</v>
+        <v>101.187</v>
       </c>
       <c r="D112" t="n">
-        <v>2.25</v>
+        <v>1.9</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>01-10-53</t>
+          <t>15-04-26</t>
         </is>
       </c>
       <c r="F112" t="n">
-        <v>4.5</v>
+        <v>3.8</v>
       </c>
       <c r="G112" t="n">
-        <v>4.363</v>
+        <v>3.755</v>
       </c>
       <c r="H112" t="n">
-        <v>57</v>
+        <v>2</v>
       </c>
       <c r="I112" t="n">
-        <v>228.25</v>
+        <v>103.8</v>
       </c>
       <c r="J112" t="n">
-        <v>125.13</v>
+        <v>2.613</v>
       </c>
       <c r="K112" t="n">
-        <v>109.488</v>
+        <v>2.286</v>
       </c>
       <c r="L112" t="n">
-        <v>4.443</v>
+        <v>3.892</v>
       </c>
       <c r="M112" t="n">
-        <v>3.887</v>
+        <v>3.405</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>IT0005538597 -Btp Tf 3,80% Ap26 EurUltimo: 101,19Cedola: 1,90Scadenza: 15/04/2026IT0005538597</t>
+          <t>IT0005542359 -Btpgreen 4%Ot31eurUltimo: 106,69Cedola: 2,00Scadenza: 30/10/2031IT0005542359</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Btp Tf 3,80% Ap26 Eur</t>
+          <t>Btpgreen 4%Ot31eur</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>101.19</v>
+        <v>106.69</v>
       </c>
       <c r="D113" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>15-04-26</t>
+          <t>30-10-31</t>
         </is>
       </c>
       <c r="F113" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="G113" t="n">
-        <v>3.755</v>
+        <v>3.749</v>
       </c>
       <c r="H113" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="I113" t="n">
-        <v>103.8</v>
+        <v>126</v>
       </c>
       <c r="J113" t="n">
-        <v>2.609999999999999</v>
+        <v>19.31</v>
       </c>
       <c r="K113" t="n">
-        <v>2.283</v>
+        <v>16.896</v>
       </c>
       <c r="L113" t="n">
-        <v>3.841</v>
+        <v>3.106</v>
       </c>
       <c r="M113" t="n">
-        <v>3.36</v>
+        <v>2.717</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>IT0005542359 -Btpgreen 4%Ot31eurUltimo: 106,49Cedola: 2,00Scadenza: 30/10/2031IT0005542359</t>
+          <t>IT0005542797 -Btp Tf 3,7% Gn30 EurUltimo: 104,73Cedola: 1,85Scadenza: 15/06/2030IT0005542797</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Btpgreen 4%Ot31eur</t>
+          <t>Btp Tf 3,7% Gn30 Eur</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>106.49</v>
+        <v>104.73</v>
       </c>
       <c r="D114" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>30-10-31</t>
+          <t>15-06-30</t>
         </is>
       </c>
       <c r="F114" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="G114" t="n">
-        <v>3.756</v>
+        <v>3.532</v>
       </c>
       <c r="H114" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="I114" t="n">
-        <v>126</v>
+        <v>118.5</v>
       </c>
       <c r="J114" t="n">
-        <v>19.51000000000001</v>
+        <v>13.77</v>
       </c>
       <c r="K114" t="n">
-        <v>17.071</v>
+        <v>12.048</v>
       </c>
       <c r="L114" t="n">
-        <v>3.134</v>
+        <v>2.844</v>
       </c>
       <c r="M114" t="n">
-        <v>2.742</v>
+        <v>2.488</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>IT0005542797 -Btp Tf 3,7% Gn30 EurUltimo: 104,61Cedola: 1,85Scadenza: 15/06/2030IT0005542797</t>
+          <t>IT0005543803 -Btpi Tf 1.5% Mg29 EurUltimo: 102,03Cedola: 0,75Scadenza: 15/05/2029IT0005543803</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Btp Tf 3,7% Gn30 Eur</t>
+          <t>Btpi Tf 1.5% Mg29 Eur</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>104.61</v>
+        <v>102.03</v>
       </c>
       <c r="D115" t="n">
-        <v>1.85</v>
+        <v>0.75</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>15-06-30</t>
+          <t>15-05-29</t>
         </is>
       </c>
       <c r="F115" t="n">
-        <v>3.7</v>
+        <v>1.5</v>
       </c>
       <c r="G115" t="n">
-        <v>3.536</v>
+        <v>1.47</v>
       </c>
       <c r="H115" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I115" t="n">
-        <v>118.5</v>
+        <v>106</v>
       </c>
       <c r="J115" t="n">
-        <v>13.89</v>
+        <v>3.969999999999999</v>
       </c>
       <c r="K115" t="n">
-        <v>12.153</v>
+        <v>3.473</v>
       </c>
       <c r="L115" t="n">
-        <v>2.864</v>
+        <v>1.056</v>
       </c>
       <c r="M115" t="n">
-        <v>2.506</v>
+        <v>0.924</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>IT0005543803 -Btpi Tf 1.5% Mg29 EurUltimo: 101,96Cedola: 0,75Scadenza: 15/05/2029IT0005543803</t>
+          <t>IT0005544082 -Btp Tf 4,35% Nv33 EurUltimo: 108,26Cedola: 2,175Scadenza: 01/11/2033IT0005544082</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Btpi Tf 1.5% Mg29 Eur</t>
+          <t>Btp Tf 4,35% Nv33 Eur</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>101.96</v>
+        <v>108.26</v>
       </c>
       <c r="D116" t="n">
-        <v>0.75</v>
+        <v>2.175</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>15-05-29</t>
+          <t>01-11-33</t>
         </is>
       </c>
       <c r="F116" t="n">
-        <v>1.5</v>
+        <v>4.35</v>
       </c>
       <c r="G116" t="n">
-        <v>1.471</v>
+        <v>4.018</v>
       </c>
       <c r="H116" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="I116" t="n">
-        <v>106</v>
+        <v>136.975</v>
       </c>
       <c r="J116" t="n">
-        <v>4.040000000000006</v>
+        <v>28.71499999999999</v>
       </c>
       <c r="K116" t="n">
-        <v>3.535</v>
+        <v>25.125</v>
       </c>
       <c r="L116" t="n">
-        <v>1.073</v>
+        <v>3.491</v>
       </c>
       <c r="M116" t="n">
-        <v>0.9379999999999999</v>
+        <v>3.054</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>IT0005544082 -Btp Tf 4,35% Nv33 EurUltimo: 108,16Cedola: 2,175Scadenza: 01/11/2033IT0005544082</t>
+          <t>IT0005547408 -Btp Valore Gn27 EurUltimo: 103,00Cedola: 2,00Scadenza: 13/06/2027IT0005547408</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Btp Tf 4,35% Nv33 Eur</t>
+          <t>Btp Valore Gn27 Eur</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>108.16</v>
+        <v>103</v>
       </c>
       <c r="D117" t="n">
-        <v>2.175</v>
+        <v>2</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>01-11-33</t>
+          <t>13-06-27</t>
         </is>
       </c>
       <c r="F117" t="n">
-        <v>4.35</v>
+        <v>4</v>
       </c>
       <c r="G117" t="n">
-        <v>4.021</v>
+        <v>3.883</v>
       </c>
       <c r="H117" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="I117" t="n">
-        <v>136.975</v>
+        <v>108</v>
       </c>
       <c r="J117" t="n">
-        <v>28.815</v>
+        <v>5</v>
       </c>
       <c r="K117" t="n">
-        <v>25.213</v>
+        <v>4.375</v>
       </c>
       <c r="L117" t="n">
-        <v>3.499</v>
+        <v>2.727</v>
       </c>
       <c r="M117" t="n">
-        <v>3.061</v>
+        <v>2.386</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>IT0005547408 -Btp Valore Gn27 EurUltimo: 102,87Cedola: 2,00Scadenza: 13/06/2027IT0005547408</t>
+          <t>IT0005547812 -Btpi Tf 2,4% Mg39 EurUltimo: 104,45Cedola: 1,20Scadenza: 15/05/2039IT0005547812</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Btp Valore Gn27 Eur</t>
+          <t>Btpi Tf 2,4% Mg39 Eur</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>102.87</v>
+        <v>104.45</v>
       </c>
       <c r="D118" t="n">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>13-06-27</t>
+          <t>15-05-39</t>
         </is>
       </c>
       <c r="F118" t="n">
-        <v>4</v>
+        <v>2.4</v>
       </c>
       <c r="G118" t="n">
-        <v>3.888</v>
+        <v>2.297</v>
       </c>
       <c r="H118" t="n">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="I118" t="n">
-        <v>108</v>
+        <v>133.6</v>
       </c>
       <c r="J118" t="n">
-        <v>5.129999999999995</v>
+        <v>29.14999999999999</v>
       </c>
       <c r="K118" t="n">
-        <v>4.488</v>
+        <v>25.506</v>
       </c>
       <c r="L118" t="n">
-        <v>2.786</v>
+        <v>2.118</v>
       </c>
       <c r="M118" t="n">
-        <v>2.437</v>
+        <v>1.853</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>IT0005547812 -Btpi Tf 2,4% Mg39 EurUltimo: 104,30Cedola: 1,20Scadenza: 15/05/2039IT0005547812</t>
+          <t>IT0005548315 -Btp Tf 3,8% Ag28 EurUltimo: 104,36Cedola: 1,90Scadenza: 01/08/2028IT0005548315</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Btpi Tf 2,4% Mg39 Eur</t>
+          <t>Btp Tf 3,8% Ag28 Eur</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>104.3</v>
+        <v>104.36</v>
       </c>
       <c r="D119" t="n">
-        <v>1.2</v>
+        <v>1.9</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>15-05-39</t>
+          <t>01-08-28</t>
         </is>
       </c>
       <c r="F119" t="n">
-        <v>2.4</v>
+        <v>3.8</v>
       </c>
       <c r="G119" t="n">
-        <v>2.301</v>
+        <v>3.641</v>
       </c>
       <c r="H119" t="n">
-        <v>28</v>
+        <v>6</v>
       </c>
       <c r="I119" t="n">
-        <v>133.6</v>
+        <v>111.4</v>
       </c>
       <c r="J119" t="n">
-        <v>29.3</v>
+        <v>7.040000000000006</v>
       </c>
       <c r="K119" t="n">
-        <v>25.637</v>
+        <v>6.16</v>
       </c>
       <c r="L119" t="n">
-        <v>2.127</v>
+        <v>2.37</v>
       </c>
       <c r="M119" t="n">
-        <v>1.861</v>
+        <v>2.073</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>IT0005548315 -Btp Tf 3,8% Ag28 EurUltimo: 104,24Cedola: 1,90Scadenza: 01/08/2028IT0005548315</t>
+          <t>IT0005550204 -Btpstripital Zc Ott39Ultimo: 57,72Cedola:Scadenza: 01/10/2039IT0005550204</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Btp Tf 3,8% Ag28 Eur</t>
+          <t>Btpstripital Zc Ott39</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>104.24</v>
-      </c>
-      <c r="D120" t="n">
-        <v>1.9</v>
+        <v>57.72</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>01-08-28</t>
-        </is>
-      </c>
-      <c r="F120" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="G120" t="n">
-        <v>3.645</v>
+          <t>01-10-39</t>
+        </is>
       </c>
       <c r="H120" t="n">
-        <v>6</v>
-      </c>
-      <c r="I120" t="n">
-        <v>111.4</v>
-      </c>
-      <c r="J120" t="n">
-        <v>7.160000000000011</v>
-      </c>
-      <c r="K120" t="n">
-        <v>6.265</v>
-      </c>
-      <c r="L120" t="n">
-        <v>2.404</v>
-      </c>
-      <c r="M120" t="n">
-        <v>2.103</v>
+        <v>29</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>IT0005550204 -Btpstripital Zc Ott39Ultimo: 57,85Cedola:Scadenza: 01/10/2039IT0005550204</t>
+          <t>IT0005556011 -Btp Tf 3,85% St26 EurUltimo: 101,93Cedola: 1,925Scadenza: 15/09/2026IT0005556011</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Btpstripital Zc Ott39</t>
+          <t>Btp Tf 3,85% St26 Eur</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>57.85</v>
+        <v>101.93</v>
+      </c>
+      <c r="D121" t="n">
+        <v>1.925</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>01-10-39</t>
-        </is>
+          <t>15-09-26</t>
+        </is>
+      </c>
+      <c r="F121" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="G121" t="n">
+        <v>3.777</v>
       </c>
       <c r="H121" t="n">
-        <v>29</v>
+        <v>3</v>
+      </c>
+      <c r="I121" t="n">
+        <v>105.775</v>
+      </c>
+      <c r="J121" t="n">
+        <v>3.844999999999999</v>
+      </c>
+      <c r="K121" t="n">
+        <v>3.364</v>
+      </c>
+      <c r="L121" t="n">
+        <v>3.526</v>
+      </c>
+      <c r="M121" t="n">
+        <v>3.085</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>IT0005556011 -Btp Tf 3,85% St26 EurUltimo: 101,89Cedola: 1,925Scadenza: 15/09/2026IT0005556011</t>
+          <t>IT0005557084 -Btp Tf 3,6% St25 EurUltimo: 100,189Cedola: 1,80Scadenza: 29/09/2025IT0005557084</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Btp Tf 3,85% St26 Eur</t>
+          <t>Btp Tf 3,6% St25 Eur</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>101.89</v>
+        <v>100.189</v>
       </c>
       <c r="D122" t="n">
-        <v>1.925</v>
+        <v>1.8</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>15-09-26</t>
+          <t>29-09-25</t>
         </is>
       </c>
       <c r="F122" t="n">
-        <v>3.85</v>
+        <v>3.6</v>
       </c>
       <c r="G122" t="n">
-        <v>3.778</v>
+        <v>3.593</v>
       </c>
       <c r="H122" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I122" t="n">
-        <v>105.775</v>
+        <v>101.8</v>
       </c>
       <c r="J122" t="n">
-        <v>3.885000000000005</v>
+        <v>1.611000000000004</v>
       </c>
       <c r="K122" t="n">
-        <v>3.399</v>
+        <v>1.409</v>
       </c>
       <c r="L122" t="n">
-        <v>3.536</v>
+        <v>12.51</v>
       </c>
       <c r="M122" t="n">
-        <v>3.094</v>
+        <v>10.946</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>IT0005557084 -Btp Tf 3,6% St25 EurUltimo: 100,202Cedola: 1,80Scadenza: 29/09/2025IT0005557084</t>
+          <t>IT0005560948 -Btp Tf 4,2% Mz34 EurUltimo: 107,18Cedola: 2,10Scadenza: 01/03/2034IT0005560948</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Btp Tf 3,6% St25 Eur</t>
+          <t>Btp Tf 4,2% Mz34 Eur</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>100.202</v>
+        <v>107.18</v>
       </c>
       <c r="D123" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>29-09-25</t>
+          <t>01-03-34</t>
         </is>
       </c>
       <c r="F123" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="G123" t="n">
-        <v>3.592</v>
+        <v>3.918</v>
       </c>
       <c r="H123" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="I123" t="n">
-        <v>101.8</v>
+        <v>137.8</v>
       </c>
       <c r="J123" t="n">
-        <v>1.597999999999999</v>
+        <v>30.62</v>
       </c>
       <c r="K123" t="n">
-        <v>1.398</v>
+        <v>26.792</v>
       </c>
       <c r="L123" t="n">
-        <v>11.665</v>
+        <v>3.579</v>
       </c>
       <c r="M123" t="n">
-        <v>10.206</v>
+        <v>3.131</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>IT0005560948 -Btp Tf 4,2% Mz34 EurUltimo: 107,00Cedola: 2,10Scadenza: 01/03/2034IT0005560948</t>
+          <t>IT0005561888 -Btp Fx 4% Nov30 EurUltimo: 106,14Cedola: 2,00Scadenza: 15/11/2030IT0005561888</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Btp Tf 4,2% Mz34 Eur</t>
+          <t>Btp Fx 4% Nov30 Eur</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>107</v>
+        <v>106.14</v>
       </c>
       <c r="D124" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>01-03-34</t>
+          <t>15-11-30</t>
         </is>
       </c>
       <c r="F124" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="G124" t="n">
-        <v>3.925</v>
+        <v>3.768</v>
       </c>
       <c r="H124" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="I124" t="n">
-        <v>137.8</v>
+        <v>122</v>
       </c>
       <c r="J124" t="n">
-        <v>30.80000000000001</v>
+        <v>15.86</v>
       </c>
       <c r="K124" t="n">
-        <v>26.95</v>
+        <v>13.877</v>
       </c>
       <c r="L124" t="n">
-        <v>3.597</v>
+        <v>3.015</v>
       </c>
       <c r="M124" t="n">
-        <v>3.147</v>
+        <v>2.638</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>IT0005561888 -Btp Fx 4% Nov30 EurUltimo: 106,02Cedola: 2,00Scadenza: 15/11/2030IT0005561888</t>
+          <t>IT0005565400 -Btp Valore Sc Oct28 EurUltimo: 105,48Cedola: 1,025Scadenza: 10/10/2028IT0005565400</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Btp Fx 4% Nov30 Eur</t>
+          <t>Btp Valore Sc Oct28 Eur</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>106.02</v>
+        <v>105.48</v>
       </c>
       <c r="D125" t="n">
-        <v>2</v>
+        <v>1.025</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>15-11-30</t>
+          <t>10-10-28</t>
         </is>
       </c>
       <c r="F125" t="n">
-        <v>4</v>
+        <v>2.05</v>
       </c>
       <c r="G125" t="n">
-        <v>3.772</v>
+        <v>1.943</v>
       </c>
       <c r="H125" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="I125" t="n">
-        <v>122</v>
+        <v>107.175</v>
       </c>
       <c r="J125" t="n">
-        <v>15.98</v>
+        <v>1.694999999999993</v>
       </c>
       <c r="K125" t="n">
-        <v>13.982</v>
+        <v>1.483</v>
       </c>
       <c r="L125" t="n">
-        <v>3.033</v>
+        <v>0.536</v>
       </c>
       <c r="M125" t="n">
-        <v>2.653</v>
+        <v>0.469</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>IT0005565400 -Btp Valore Sc Oct28 EurUltimo: 105,15Cedola: 1,025Scadenza: 10/10/2028IT0005565400</t>
+          <t>IT0005566408 -Btp Fx 4.1% Feb29 EurUltimo: 105,69Cedola:Scadenza: 01/02/2029IT0005566408</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Btp Valore Sc Oct28 Eur</t>
+          <t>Btp Fx 4.1% Feb29 Eur</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>105.15</v>
-      </c>
-      <c r="D126" t="n">
-        <v>1.025</v>
+        <v>105.69</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>10-10-28</t>
-        </is>
-      </c>
-      <c r="F126" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="G126" t="n">
-        <v>1.949</v>
+          <t>01-02-29</t>
+        </is>
       </c>
       <c r="H126" t="n">
         <v>7</v>
       </c>
-      <c r="I126" t="n">
-        <v>107.175</v>
-      </c>
-      <c r="J126" t="n">
-        <v>2.024999999999991</v>
-      </c>
-      <c r="K126" t="n">
-        <v>1.771</v>
-      </c>
-      <c r="L126" t="n">
-        <v>0.638</v>
-      </c>
-      <c r="M126" t="n">
-        <v>0.5580000000000001</v>
-      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>IT0005566408 -Btp Fx 4.1% Feb29 EurUltimo: 105,55Cedola:Scadenza: 01/02/2029IT0005566408</t>
+          <t>IT0005580045 -Btp Fx 2.95% Feb27 EurUltimo: 101,23Cedola: 1,475Scadenza: 15/02/2027IT0005580045</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Btp Fx 4.1% Feb29 Eur</t>
+          <t>Btp Fx 2.95% Feb27 Eur</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>105.55</v>
+        <v>101.23</v>
+      </c>
+      <c r="D127" t="n">
+        <v>1.475</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>01-02-29</t>
-        </is>
+          <t>15-02-27</t>
+        </is>
+      </c>
+      <c r="F127" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="G127" t="n">
+        <v>2.914</v>
       </c>
       <c r="H127" t="n">
-        <v>7</v>
+        <v>4</v>
+      </c>
+      <c r="I127" t="n">
+        <v>105.9</v>
+      </c>
+      <c r="J127" t="n">
+        <v>4.670000000000002</v>
+      </c>
+      <c r="K127" t="n">
+        <v>4.086</v>
+      </c>
+      <c r="L127" t="n">
+        <v>3.093</v>
+      </c>
+      <c r="M127" t="n">
+        <v>2.706</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>IT0005580045 -Btp Fx 2.95% Feb27 EurUltimo: 101,21Cedola: 1,475Scadenza: 15/02/2027IT0005580045</t>
+          <t>IT0005580094 -Btp Fx 3.5% Feb31 EurUltimo: 103,62Cedola: 1,75Scadenza: 15/02/2031IT0005580094</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Btp Fx 2.95% Feb27 Eur</t>
+          <t>Btp Fx 3.5% Feb31 Eur</t>
         </is>
       </c>
       <c r="C128" t="n">
-        <v>101.21</v>
+        <v>103.62</v>
       </c>
       <c r="D128" t="n">
-        <v>1.475</v>
+        <v>1.75</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>15-02-27</t>
+          <t>15-02-31</t>
         </is>
       </c>
       <c r="F128" t="n">
-        <v>2.95</v>
+        <v>3.5</v>
       </c>
       <c r="G128" t="n">
-        <v>2.914</v>
+        <v>3.377</v>
       </c>
       <c r="H128" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="I128" t="n">
-        <v>105.9</v>
+        <v>121</v>
       </c>
       <c r="J128" t="n">
-        <v>4.690000000000012</v>
+        <v>17.38</v>
       </c>
       <c r="K128" t="n">
-        <v>4.103</v>
+        <v>15.207</v>
       </c>
       <c r="L128" t="n">
-        <v>3.089</v>
+        <v>3.152</v>
       </c>
       <c r="M128" t="n">
-        <v>2.702</v>
+        <v>2.758</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>IT0005580094 -Btp Fx 3.5% Feb31 EurUltimo: 103,47Cedola: 1,75Scadenza: 15/02/2031IT0005580094</t>
+          <t>IT0005582421 -Btp Fx 4.15% Oct39 EurUltimo: 103,91Cedola:Scadenza: 01/10/2039IT0005582421</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Btp Fx 3.5% Feb31 Eur</t>
+          <t>Btp Fx 4.15% Oct39 Eur</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>103.47</v>
-      </c>
-      <c r="D129" t="n">
-        <v>1.75</v>
+        <v>103.91</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>15-02-31</t>
-        </is>
-      </c>
-      <c r="F129" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="G129" t="n">
-        <v>3.382</v>
+          <t>01-10-39</t>
+        </is>
       </c>
       <c r="H129" t="n">
-        <v>12</v>
-      </c>
-      <c r="I129" t="n">
-        <v>121</v>
-      </c>
-      <c r="J129" t="n">
-        <v>17.53</v>
-      </c>
-      <c r="K129" t="n">
-        <v>15.338</v>
-      </c>
-      <c r="L129" t="n">
-        <v>3.175</v>
-      </c>
-      <c r="M129" t="n">
-        <v>2.778</v>
+        <v>29</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>IT0005582421 -Btp Fx 4.15% Oct39 EurUltimo: 103,70Cedola:Scadenza: 01/10/2039IT0005582421</t>
+          <t>IT0005583486 -Btp Valore Sc Mz30 EurUltimo: 103,95Cedola: 0,8125Scadenza: 05/03/2030IT0005583486</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Btp Fx 4.15% Oct39 Eur</t>
+          <t>Btp Valore Sc Mz30 Eur</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>103.7</v>
+        <v>103.95</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.8125</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>01-10-39</t>
-        </is>
+          <t>05-03-30</t>
+        </is>
+      </c>
+      <c r="F130" t="n">
+        <v>1.625</v>
+      </c>
+      <c r="G130" t="n">
+        <v>1.563</v>
       </c>
       <c r="H130" t="n">
-        <v>29</v>
+        <v>10</v>
+      </c>
+      <c r="I130" t="n">
+        <v>108.125</v>
+      </c>
+      <c r="J130" t="n">
+        <v>4.174999999999997</v>
+      </c>
+      <c r="K130" t="n">
+        <v>3.653</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.915</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.8</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>IT0005583486 -Btp Valore Sc Mz30 EurUltimo: 103,74Cedola: 0,8125Scadenza: 05/03/2030IT0005583486</t>
+          <t>IT0005584302 -Btp Fx 3.2% Jan26 EurUltimo: 100,53Cedola: 1,60Scadenza: 28/01/2026IT0005584302</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Btp Valore Sc Mz30 Eur</t>
+          <t>Btp Fx 3.2% Jan26 Eur</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>103.74</v>
+        <v>100.53</v>
       </c>
       <c r="D131" t="n">
-        <v>0.8125</v>
+        <v>1.6</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>05-03-30</t>
+          <t>28-01-26</t>
         </is>
       </c>
       <c r="F131" t="n">
-        <v>1.625</v>
+        <v>3.2</v>
       </c>
       <c r="G131" t="n">
-        <v>1.566</v>
+        <v>3.183</v>
       </c>
       <c r="H131" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="I131" t="n">
-        <v>108.125</v>
+        <v>101.6</v>
       </c>
       <c r="J131" t="n">
-        <v>4.385000000000005</v>
+        <v>1.069999999999993</v>
       </c>
       <c r="K131" t="n">
-        <v>3.836</v>
+        <v>0.9360000000000001</v>
       </c>
       <c r="L131" t="n">
-        <v>0.959</v>
+        <v>2.324</v>
       </c>
       <c r="M131" t="n">
-        <v>0.839</v>
+        <v>2.033</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>IT0005584302 -Btp Fx 3.2% Jan26 EurUltimo: 100,516Cedola: 1,60Scadenza: 28/01/2026IT0005584302</t>
+          <t>IT0005584849 -Btp Fx 3.35% Jul29 EurUltimo: 103,20Cedola: 1,675Scadenza: 01/07/2029IT0005584849</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Btp Fx 3.2% Jan26 Eur</t>
+          <t>Btp Fx 3.35% Jul29 Eur</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>100.516</v>
+        <v>103.2</v>
       </c>
       <c r="D132" t="n">
-        <v>1.6</v>
+        <v>1.675</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>28-01-26</t>
+          <t>01-07-29</t>
         </is>
       </c>
       <c r="F132" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="G132" t="n">
-        <v>3.183</v>
+        <v>3.246</v>
       </c>
       <c r="H132" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="I132" t="n">
-        <v>101.6</v>
+        <v>113.4</v>
       </c>
       <c r="J132" t="n">
-        <v>1.083999999999989</v>
+        <v>10.2</v>
       </c>
       <c r="K132" t="n">
-        <v>0.948</v>
+        <v>8.925000000000001</v>
       </c>
       <c r="L132" t="n">
-        <v>2.313</v>
+        <v>2.625</v>
       </c>
       <c r="M132" t="n">
-        <v>2.023</v>
+        <v>2.296</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>IT0005584849 -Btp Fx 3.35% Jul29 EurUltimo: 103,08Cedola: 1,675Scadenza: 01/07/2029IT0005584849</t>
+          <t>IT0005584856 -Btp Fx 3.85% Jul34 EurUltimo: 104,35Cedola: 1,925Scadenza: 01/07/2034IT0005584856</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Btp Fx 3.35% Jul29 Eur</t>
+          <t>Btp Fx 3.85% Jul34 Eur</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>103.08</v>
+        <v>104.35</v>
       </c>
       <c r="D133" t="n">
-        <v>1.675</v>
+        <v>1.925</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>01-07-29</t>
+          <t>01-07-34</t>
         </is>
       </c>
       <c r="F133" t="n">
-        <v>3.35</v>
+        <v>3.85</v>
       </c>
       <c r="G133" t="n">
-        <v>3.249</v>
+        <v>3.689</v>
       </c>
       <c r="H133" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="I133" t="n">
-        <v>113.4</v>
+        <v>134.65</v>
       </c>
       <c r="J133" t="n">
-        <v>10.32000000000001</v>
+        <v>30.30000000000001</v>
       </c>
       <c r="K133" t="n">
-        <v>9.029999999999999</v>
+        <v>26.512</v>
       </c>
       <c r="L133" t="n">
-        <v>2.65</v>
+        <v>3.409</v>
       </c>
       <c r="M133" t="n">
-        <v>2.318</v>
+        <v>2.982</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>IT0005584856 -Btp Fx 3.85% Jul34 EurUltimo: 104,19Cedola: 1,925Scadenza: 01/07/2034IT0005584856</t>
+          <t>IT0005588881 -Btpi Fx May36 EurUltimo: 99,91Cedola: 0,90Scadenza: 15/05/2036IT0005588881</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Btp Fx 3.85% Jul34 Eur</t>
+          <t>Btpi Fx May36 Eur</t>
         </is>
       </c>
       <c r="C134" t="n">
-        <v>104.19</v>
+        <v>99.91</v>
       </c>
       <c r="D134" t="n">
-        <v>1.925</v>
+        <v>0.9</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>01-07-34</t>
+          <t>15-05-36</t>
         </is>
       </c>
       <c r="F134" t="n">
-        <v>3.85</v>
+        <v>1.8</v>
       </c>
       <c r="G134" t="n">
-        <v>3.695</v>
+        <v>1.801</v>
       </c>
       <c r="H134" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="I134" t="n">
-        <v>134.65</v>
+        <v>119.8</v>
       </c>
       <c r="J134" t="n">
-        <v>30.46000000000001</v>
+        <v>19.89</v>
       </c>
       <c r="K134" t="n">
-        <v>26.652</v>
+        <v>17.403</v>
       </c>
       <c r="L134" t="n">
-        <v>3.424</v>
+        <v>1.848</v>
       </c>
       <c r="M134" t="n">
-        <v>2.996</v>
+        <v>1.617</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>IT0005588881 -Btpi Fx May36 EurUltimo: 99,87Cedola: 0,90Scadenza: 15/05/2036IT0005588881</t>
+          <t>IT0005594483 -Btp Valore Sc Mg30 EurUltimo: 103,81Cedola: 0,8375Scadenza: 14/05/2030IT0005594483</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Btpi Fx May36 Eur</t>
+          <t>Btp Valore Sc Mg30 Eur</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>99.87</v>
+        <v>103.81</v>
       </c>
       <c r="D135" t="n">
-        <v>0.9</v>
+        <v>0.8375</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>15-05-36</t>
+          <t>14-05-30</t>
         </is>
       </c>
       <c r="F135" t="n">
-        <v>1.8</v>
+        <v>1.675</v>
       </c>
       <c r="G135" t="n">
-        <v>1.802</v>
+        <v>1.613</v>
       </c>
       <c r="H135" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="I135" t="n">
-        <v>119.8</v>
+        <v>108.375</v>
       </c>
       <c r="J135" t="n">
-        <v>19.92999999999999</v>
+        <v>4.564999999999998</v>
       </c>
       <c r="K135" t="n">
-        <v>17.438</v>
+        <v>3.994</v>
       </c>
       <c r="L135" t="n">
-        <v>1.85</v>
+        <v>0.96</v>
       </c>
       <c r="M135" t="n">
-        <v>1.618</v>
+        <v>0.84</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>IT0005594483 -Btp Valore Sc Mg30 EurUltimo: 103,67Cedola: 0,8375Scadenza: 14/05/2030IT0005594483</t>
+          <t>IT0005595803 -Btp Fx 3.45% Jul31 EurUltimo: 103,22Cedola: 1,725Scadenza: 15/07/2031IT0005595803</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Btp Valore Sc Mg30 Eur</t>
+          <t>Btp Fx 3.45% Jul31 Eur</t>
         </is>
       </c>
       <c r="C136" t="n">
-        <v>103.67</v>
+        <v>103.22</v>
       </c>
       <c r="D136" t="n">
-        <v>0.8375</v>
+        <v>1.725</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>14-05-30</t>
+          <t>15-07-31</t>
         </is>
       </c>
       <c r="F136" t="n">
-        <v>1.675</v>
+        <v>3.45</v>
       </c>
       <c r="G136" t="n">
-        <v>1.615</v>
+        <v>3.342</v>
       </c>
       <c r="H136" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I136" t="n">
-        <v>108.375</v>
+        <v>120.7</v>
       </c>
       <c r="J136" t="n">
-        <v>4.704999999999998</v>
+        <v>17.48</v>
       </c>
       <c r="K136" t="n">
-        <v>4.116</v>
+        <v>15.295</v>
       </c>
       <c r="L136" t="n">
-        <v>0.988</v>
+        <v>2.951</v>
       </c>
       <c r="M136" t="n">
-        <v>0.864</v>
+        <v>2.582</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>IT0005595803 -Btp Fx 3.45% Jul31 EurUltimo: 103,02Cedola: 1,725Scadenza: 15/07/2031IT0005595803</t>
+          <t>IT0005596470 -Btp Green Fx 4.05% Oct37 EurUltimo: 104,35Cedola: 2,025Scadenza: 30/10/2037IT0005596470</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Btp Fx 3.45% Jul31 Eur</t>
+          <t>Btp Green Fx 4.05% Oct37 Eur</t>
         </is>
       </c>
       <c r="C137" t="n">
-        <v>103.02</v>
+        <v>104.35</v>
       </c>
       <c r="D137" t="n">
-        <v>1.725</v>
+        <v>2.025</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>15-07-31</t>
+          <t>30-10-37</t>
         </is>
       </c>
       <c r="F137" t="n">
-        <v>3.45</v>
+        <v>4.05</v>
       </c>
       <c r="G137" t="n">
-        <v>3.348</v>
+        <v>3.881</v>
       </c>
       <c r="H137" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="I137" t="n">
-        <v>120.7</v>
+        <v>150.625</v>
       </c>
       <c r="J137" t="n">
-        <v>17.68000000000001</v>
+        <v>46.27500000000001</v>
       </c>
       <c r="K137" t="n">
-        <v>15.47</v>
+        <v>40.49</v>
       </c>
       <c r="L137" t="n">
-        <v>2.98</v>
+        <v>3.786</v>
       </c>
       <c r="M137" t="n">
-        <v>2.607</v>
+        <v>3.312</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>IT0005596470 -Btp Green Fx 4.05% Oct37 EurUltimo: 104,12Cedola: 2,025Scadenza: 30/10/2037IT0005596470</t>
+          <t>IT0005599904 -Btp Fx 3.45% Jul27 EurUltimo: 102,49Cedola: 1,725Scadenza: 15/07/2027IT0005599904</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Btp Green Fx 4.05% Oct37 Eur</t>
+          <t>Btp Fx 3.45% Jul27 Eur</t>
         </is>
       </c>
       <c r="C138" t="n">
-        <v>104.12</v>
+        <v>102.49</v>
       </c>
       <c r="D138" t="n">
-        <v>2.025</v>
+        <v>1.725</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>30-10-37</t>
+          <t>15-07-27</t>
         </is>
       </c>
       <c r="F138" t="n">
-        <v>4.05</v>
+        <v>3.45</v>
       </c>
       <c r="G138" t="n">
-        <v>3.889</v>
+        <v>3.366</v>
       </c>
       <c r="H138" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="I138" t="n">
-        <v>150.625</v>
+        <v>106.9</v>
       </c>
       <c r="J138" t="n">
-        <v>46.505</v>
+        <v>4.410000000000011</v>
       </c>
       <c r="K138" t="n">
-        <v>40.691</v>
+        <v>3.858</v>
       </c>
       <c r="L138" t="n">
-        <v>3.802</v>
+        <v>2.296</v>
       </c>
       <c r="M138" t="n">
-        <v>3.326</v>
+        <v>2.009</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>IT0005599904 -Btp Fx 3.45% Jul27 EurUltimo: 102,45Cedola: 1,725Scadenza: 15/07/2027IT0005599904</t>
+          <t>IT0005607269 -Btp Fx 3.1% Aug26 EurUltimo: 101,07Cedola: 1,55Scadenza: 28/08/2026IT0005607269</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Btp Fx 3.45% Jul27 Eur</t>
+          <t>Btp Fx 3.1% Aug26 Eur</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>102.45</v>
+        <v>101.07</v>
       </c>
       <c r="D139" t="n">
-        <v>1.725</v>
+        <v>1.55</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>15-07-27</t>
+          <t>28-08-26</t>
         </is>
       </c>
       <c r="F139" t="n">
-        <v>3.45</v>
+        <v>3.1</v>
       </c>
       <c r="G139" t="n">
-        <v>3.367</v>
+        <v>3.067</v>
       </c>
       <c r="H139" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I139" t="n">
-        <v>106.9</v>
+        <v>104.65</v>
       </c>
       <c r="J139" t="n">
-        <v>4.450000000000003</v>
+        <v>3.580000000000013</v>
       </c>
       <c r="K139" t="n">
-        <v>3.893</v>
+        <v>3.132</v>
       </c>
       <c r="L139" t="n">
-        <v>2.307</v>
+        <v>3.438</v>
       </c>
       <c r="M139" t="n">
-        <v>2.018</v>
+        <v>3.008</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>IT0005607269 -Btp Fx 3.1% Aug26 EurUltimo: 101,06Cedola: 1,55Scadenza: 28/08/2026IT0005607269</t>
+          <t>IT0005607970 -Btp Fx 3.85% Feb35 EurUltimo: 103,96Cedola: 1,925Scadenza: 01/02/2035IT0005607970</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Btp Fx 3.1% Aug26 Eur</t>
+          <t>Btp Fx 3.85% Feb35 Eur</t>
         </is>
       </c>
       <c r="C140" t="n">
-        <v>101.06</v>
+        <v>103.96</v>
       </c>
       <c r="D140" t="n">
-        <v>1.55</v>
+        <v>1.925</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>28-08-26</t>
+          <t>01-02-35</t>
         </is>
       </c>
       <c r="F140" t="n">
-        <v>3.1</v>
+        <v>3.85</v>
       </c>
       <c r="G140" t="n">
-        <v>3.067</v>
+        <v>3.703</v>
       </c>
       <c r="H140" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="I140" t="n">
-        <v>104.65</v>
+        <v>136.575</v>
       </c>
       <c r="J140" t="n">
-        <v>3.590000000000003</v>
+        <v>32.61499999999999</v>
       </c>
       <c r="K140" t="n">
-        <v>3.141</v>
+        <v>28.538</v>
       </c>
       <c r="L140" t="n">
-        <v>3.421</v>
+        <v>3.441</v>
       </c>
       <c r="M140" t="n">
-        <v>2.993</v>
+        <v>3.01</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>IT0005607970 -Btp Fx 3.85% Feb35 EurUltimo: 103,78Cedola: 1,925Scadenza: 01/02/2035IT0005607970</t>
+          <t>IT0005611055 -Btp Fx 3% Oct29 EurUltimo: 101,86Cedola: 1,50Scadenza: 01/10/2029IT0005611055</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Btp Fx 3.85% Feb35 Eur</t>
+          <t>Btp Fx 3% Oct29 Eur</t>
         </is>
       </c>
       <c r="C141" t="n">
-        <v>103.78</v>
+        <v>101.86</v>
       </c>
       <c r="D141" t="n">
-        <v>1.925</v>
+        <v>1.5</v>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>01-02-35</t>
+          <t>01-10-29</t>
         </is>
       </c>
       <c r="F141" t="n">
-        <v>3.85</v>
+        <v>3</v>
       </c>
       <c r="G141" t="n">
-        <v>3.709</v>
+        <v>2.945</v>
       </c>
       <c r="H141" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="I141" t="n">
-        <v>136.575</v>
+        <v>113.5</v>
       </c>
       <c r="J141" t="n">
-        <v>32.79499999999999</v>
+        <v>11.64</v>
       </c>
       <c r="K141" t="n">
-        <v>28.695</v>
+        <v>10.185</v>
       </c>
       <c r="L141" t="n">
-        <v>3.457</v>
+        <v>2.813</v>
       </c>
       <c r="M141" t="n">
-        <v>3.024</v>
+        <v>2.461</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>IT0005611055 -Btp Fx 3% Oct29 EurUltimo: 102,20Cedola: 1,50Scadenza: 01/10/2029IT0005611055</t>
+          <t>IT0005611741 -Btp Fx 4.3% Oct54 EurUltimo: 99,21Cedola: 2,15Scadenza: 01/10/2054IT0005611741</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Btp Fx 3% Oct29 Eur</t>
+          <t>Btp Fx 4.3% Oct54 Eur</t>
         </is>
       </c>
       <c r="C142" t="n">
-        <v>102.2</v>
+        <v>99.20999999999999</v>
       </c>
       <c r="D142" t="n">
-        <v>1.5</v>
+        <v>2.15</v>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>01-10-29</t>
+          <t>01-10-54</t>
         </is>
       </c>
       <c r="F142" t="n">
-        <v>3</v>
+        <v>4.3</v>
       </c>
       <c r="G142" t="n">
-        <v>2.935</v>
+        <v>4.334</v>
       </c>
       <c r="H142" t="n">
-        <v>9</v>
+        <v>59</v>
       </c>
       <c r="I142" t="n">
-        <v>113.5</v>
+        <v>226.85</v>
       </c>
       <c r="J142" t="n">
-        <v>11.3</v>
+        <v>127.64</v>
       </c>
       <c r="K142" t="n">
-        <v>9.887</v>
+        <v>111.685</v>
       </c>
       <c r="L142" t="n">
-        <v>2.726</v>
+        <v>4.378</v>
       </c>
       <c r="M142" t="n">
-        <v>2.385</v>
+        <v>3.83</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>IT0005611741 -Btp Fx 4.3% Oct54 EurUltimo: 99,23Cedola: 2,15Scadenza: 01/10/2054IT0005611741</t>
+          <t>IT0005619546 -Btp Fx 3.15% Nov31 EurUltimo: 101,37Cedola: 1,575Scadenza: 15/11/2031IT0005619546</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Btp Fx 4.3% Oct54 Eur</t>
+          <t>Btp Fx 3.15% Nov31 Eur</t>
         </is>
       </c>
       <c r="C143" t="n">
-        <v>99.23</v>
+        <v>101.37</v>
       </c>
       <c r="D143" t="n">
-        <v>2.15</v>
+        <v>1.575</v>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>01-10-54</t>
+          <t>15-11-31</t>
         </is>
       </c>
       <c r="F143" t="n">
-        <v>4.3</v>
+        <v>3.15</v>
       </c>
       <c r="G143" t="n">
-        <v>4.333</v>
+        <v>3.107</v>
       </c>
       <c r="H143" t="n">
-        <v>59</v>
+        <v>13</v>
       </c>
       <c r="I143" t="n">
-        <v>226.85</v>
+        <v>120.475</v>
       </c>
       <c r="J143" t="n">
-        <v>127.62</v>
+        <v>19.10499999999999</v>
       </c>
       <c r="K143" t="n">
-        <v>111.667</v>
+        <v>16.716</v>
       </c>
       <c r="L143" t="n">
-        <v>4.376</v>
+        <v>3.051</v>
       </c>
       <c r="M143" t="n">
-        <v>3.829</v>
+        <v>2.669</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>IT0005619546 -Btp Fx 3.15% Nov31 EurUltimo: 101,17Cedola: 1,575Scadenza: 15/11/2031IT0005619546</t>
+          <t>IT0005622128 -Btp Fx 2.7% Oct27 EurUltimo: 101,12Cedola: 1,35Scadenza: 15/10/2027IT0005622128</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Btp Fx 3.15% Nov31 Eur</t>
+          <t>Btp Fx 2.7% Oct27 Eur</t>
         </is>
       </c>
       <c r="C144" t="n">
-        <v>101.17</v>
+        <v>101.12</v>
       </c>
       <c r="D144" t="n">
-        <v>1.575</v>
+        <v>1.35</v>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>15-11-31</t>
+          <t>15-10-27</t>
         </is>
       </c>
       <c r="F144" t="n">
-        <v>3.15</v>
+        <v>2.7</v>
       </c>
       <c r="G144" t="n">
-        <v>3.113</v>
+        <v>2.67</v>
       </c>
       <c r="H144" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="I144" t="n">
-        <v>120.475</v>
+        <v>106.75</v>
       </c>
       <c r="J144" t="n">
-        <v>19.30499999999999</v>
+        <v>5.629999999999995</v>
       </c>
       <c r="K144" t="n">
-        <v>16.891</v>
+        <v>4.926</v>
       </c>
       <c r="L144" t="n">
-        <v>3.079</v>
+        <v>2.591</v>
       </c>
       <c r="M144" t="n">
-        <v>2.694</v>
+        <v>2.267</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>IT0005622128 -Btp Fx 2.7% Oct27 EurUltimo: 101,07Cedola: 1,35Scadenza: 15/10/2027IT0005622128</t>
+          <t>IT0005631590 -Btp Fx 3.65% Aug35 EurUltimo: 101,90Cedola: 1,825Scadenza: 01/08/2035IT0005631590</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Btp Fx 2.7% Oct27 Eur</t>
+          <t>Btp Fx 3.65% Aug35 Eur</t>
         </is>
       </c>
       <c r="C145" t="n">
-        <v>101.07</v>
+        <v>101.9</v>
       </c>
       <c r="D145" t="n">
-        <v>1.35</v>
+        <v>1.825</v>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>15-10-27</t>
+          <t>01-08-35</t>
         </is>
       </c>
       <c r="F145" t="n">
-        <v>2.7</v>
+        <v>3.65</v>
       </c>
       <c r="G145" t="n">
-        <v>2.671</v>
+        <v>3.581</v>
       </c>
       <c r="H145" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="I145" t="n">
-        <v>106.75</v>
+        <v>136.5</v>
       </c>
       <c r="J145" t="n">
-        <v>5.680000000000007</v>
+        <v>34.59999999999999</v>
       </c>
       <c r="K145" t="n">
-        <v>4.97</v>
+        <v>30.274</v>
       </c>
       <c r="L145" t="n">
-        <v>2.604</v>
+        <v>3.469</v>
       </c>
       <c r="M145" t="n">
-        <v>2.278</v>
+        <v>3.035</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>IT0005631590 -Btp Fx 3.65% Aug35 EurUltimo: 101,69Cedola: 1,825Scadenza: 01/08/2035IT0005631590</t>
+          <t>IT0005631608 -Btp Green Fx 4.1% Apr46 EurUltimo: 100,73Cedola: 2,05Scadenza: 30/04/2046IT0005631608</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Btp Fx 3.65% Aug35 Eur</t>
+          <t>Btp Green Fx 4.1% Apr46 Eur</t>
         </is>
       </c>
       <c r="C146" t="n">
-        <v>101.69</v>
+        <v>100.73</v>
       </c>
       <c r="D146" t="n">
-        <v>1.825</v>
+        <v>2.05</v>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>01-08-35</t>
+          <t>30-04-46</t>
         </is>
       </c>
       <c r="F146" t="n">
-        <v>3.65</v>
+        <v>4.1</v>
       </c>
       <c r="G146" t="n">
-        <v>3.589</v>
+        <v>4.07</v>
       </c>
       <c r="H146" t="n">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="I146" t="n">
-        <v>136.5</v>
+        <v>186.1</v>
       </c>
       <c r="J146" t="n">
-        <v>34.81</v>
+        <v>85.36999999999999</v>
       </c>
       <c r="K146" t="n">
-        <v>30.458</v>
+        <v>74.69799999999999</v>
       </c>
       <c r="L146" t="n">
-        <v>3.487</v>
+        <v>4.118</v>
       </c>
       <c r="M146" t="n">
-        <v>3.051</v>
+        <v>3.603</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>IT0005631608 -Btp Green Fx 4.1% Apr46 EurUltimo: 100,66Cedola: 2,05Scadenza: 30/04/2046IT0005631608</t>
+          <t>IT0005633794 -Btp Fx 2.55% Feb27 EurUltimo: 100,69Cedola: 1,275Scadenza: 25/02/2027IT0005633794</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Btp Green Fx 4.1% Apr46 Eur</t>
+          <t>Btp Fx 2.55% Feb27 Eur</t>
         </is>
       </c>
       <c r="C147" t="n">
-        <v>100.66</v>
+        <v>100.69</v>
       </c>
       <c r="D147" t="n">
-        <v>2.05</v>
+        <v>1.275</v>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>30-04-46</t>
+          <t>25-02-27</t>
         </is>
       </c>
       <c r="F147" t="n">
-        <v>4.1</v>
+        <v>2.55</v>
       </c>
       <c r="G147" t="n">
-        <v>4.073</v>
+        <v>2.532</v>
       </c>
       <c r="H147" t="n">
-        <v>42</v>
+        <v>4</v>
       </c>
       <c r="I147" t="n">
-        <v>186.1</v>
+        <v>105.1</v>
       </c>
       <c r="J147" t="n">
-        <v>85.44</v>
+        <v>4.409999999999997</v>
       </c>
       <c r="K147" t="n">
-        <v>74.759</v>
+        <v>3.858</v>
       </c>
       <c r="L147" t="n">
-        <v>4.12</v>
+        <v>2.869</v>
       </c>
       <c r="M147" t="n">
-        <v>3.605</v>
+        <v>2.51</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>IT0005633794 -Btp Fx 2.55% Feb27 EurUltimo: 100,68Cedola: 1,275Scadenza: 25/02/2027IT0005633794</t>
+          <t>IT0005634800 -Btp Piu' Sc Fb33 EurUltimo: 100,96Cedola: 0,7125Scadenza: 25/02/2033IT0005634800</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Btp Fx 2.55% Feb27 Eur</t>
+          <t>Btp Piu' Sc Fb33 Eur</t>
         </is>
       </c>
       <c r="C148" t="n">
-        <v>100.68</v>
+        <v>100.96</v>
       </c>
       <c r="D148" t="n">
-        <v>1.275</v>
+        <v>0.7125</v>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>25-02-27</t>
+          <t>25-02-33</t>
         </is>
       </c>
       <c r="F148" t="n">
-        <v>2.55</v>
+        <v>1.425</v>
       </c>
       <c r="G148" t="n">
-        <v>2.532</v>
+        <v>1.411</v>
       </c>
       <c r="H148" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="I148" t="n">
-        <v>105.1</v>
+        <v>111.4</v>
       </c>
       <c r="J148" t="n">
-        <v>4.419999999999987</v>
+        <v>10.44000000000001</v>
       </c>
       <c r="K148" t="n">
-        <v>3.867</v>
+        <v>9.135</v>
       </c>
       <c r="L148" t="n">
-        <v>2.86</v>
+        <v>1.384</v>
       </c>
       <c r="M148" t="n">
-        <v>2.502</v>
+        <v>1.21</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>IT0005634800 -Btp Piu' Sc Fb33 EurUltimo: 100,74Cedola: 0,7125Scadenza: 25/02/2033IT0005634800</t>
+          <t>IT0005635583 -Btp Fx 3.85% Oct40 EurUltimo: 99,72Cedola: 1,925Scadenza: 01/10/2040IT0005635583</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Btp Piu' Sc Fb33 Eur</t>
+          <t>Btp Fx 3.85% Oct40 Eur</t>
         </is>
       </c>
       <c r="C149" t="n">
-        <v>100.74</v>
+        <v>99.72</v>
       </c>
       <c r="D149" t="n">
-        <v>0.7125</v>
+        <v>1.925</v>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>25-02-33</t>
+          <t>01-10-40</t>
         </is>
       </c>
       <c r="F149" t="n">
-        <v>1.425</v>
+        <v>3.85</v>
       </c>
       <c r="G149" t="n">
-        <v>1.414</v>
+        <v>3.86</v>
       </c>
       <c r="H149" t="n">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="I149" t="n">
-        <v>111.4</v>
+        <v>159.675</v>
       </c>
       <c r="J149" t="n">
-        <v>10.66000000000001</v>
+        <v>59.95500000000001</v>
       </c>
       <c r="K149" t="n">
-        <v>9.327</v>
+        <v>52.46</v>
       </c>
       <c r="L149" t="n">
-        <v>1.411</v>
+        <v>3.958</v>
       </c>
       <c r="M149" t="n">
-        <v>1.234</v>
+        <v>3.463</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>IT0005635583 -Btp Fx 3.85% Oct40 EurUltimo: 99,50Cedola: 1,925Scadenza: 01/10/2040IT0005635583</t>
+          <t>IT0005637399 -Btp Fx 2.95% Jul30 EurUltimo: 101,21Cedola: 1,475Scadenza: 01/07/2030IT0005637399</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Btp Fx 3.85% Oct40 Eur</t>
+          <t>Btp Fx 2.95% Jul30 Eur</t>
         </is>
       </c>
       <c r="C150" t="n">
-        <v>99.5</v>
+        <v>101.21</v>
       </c>
       <c r="D150" t="n">
-        <v>1.925</v>
+        <v>1.475</v>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>01-10-40</t>
+          <t>01-07-30</t>
         </is>
       </c>
       <c r="F150" t="n">
-        <v>3.85</v>
+        <v>2.95</v>
       </c>
       <c r="G150" t="n">
-        <v>3.869</v>
+        <v>2.914</v>
       </c>
       <c r="H150" t="n">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="I150" t="n">
-        <v>159.675</v>
+        <v>114.75</v>
       </c>
       <c r="J150" t="n">
-        <v>60.17500000000001</v>
+        <v>13.54000000000001</v>
       </c>
       <c r="K150" t="n">
-        <v>52.653</v>
+        <v>11.847</v>
       </c>
       <c r="L150" t="n">
-        <v>3.971</v>
+        <v>2.771</v>
       </c>
       <c r="M150" t="n">
-        <v>3.474</v>
+        <v>2.424</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>IT0005637399 -Btp Fx 2.95% Jul30 EurUltimo: 101,14Cedola: 1,475Scadenza: 01/07/2030IT0005637399</t>
+          <t>IT0005641029 -Btp Fx 2.65% Jun28 EurUltimo: 101,02Cedola: 1,325Scadenza: 15/06/2028IT0005641029</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Btp Fx 2.95% Jul30 Eur</t>
+          <t>Btp Fx 2.65% Jun28 Eur</t>
         </is>
       </c>
       <c r="C151" t="n">
-        <v>101.14</v>
+        <v>101.02</v>
       </c>
       <c r="D151" t="n">
-        <v>1.475</v>
+        <v>1.325</v>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>01-07-30</t>
+          <t>15-06-28</t>
         </is>
       </c>
       <c r="F151" t="n">
-        <v>2.95</v>
+        <v>2.65</v>
       </c>
       <c r="G151" t="n">
-        <v>2.916</v>
+        <v>2.623</v>
       </c>
       <c r="H151" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="I151" t="n">
-        <v>114.75</v>
+        <v>107.95</v>
       </c>
       <c r="J151" t="n">
-        <v>13.61</v>
+        <v>6.930000000000007</v>
       </c>
       <c r="K151" t="n">
-        <v>11.908</v>
+        <v>6.063</v>
       </c>
       <c r="L151" t="n">
-        <v>2.781</v>
+        <v>2.439</v>
       </c>
       <c r="M151" t="n">
-        <v>2.433</v>
+        <v>2.134</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>IT0005641029 -Btp Fx 2.65% Jun28 EurUltimo: 100,93Cedola: 1,325Scadenza: 15/06/2028IT0005641029</t>
+          <t>IT0005647265 -Btp Fx 3.25% Jul32 EurUltimo: 101,35Cedola: 1,625Scadenza: 15/07/2032IT0005647265</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Btp Fx 2.65% Jun28 Eur</t>
+          <t>Btp Fx 3.25% Jul32 Eur</t>
         </is>
       </c>
       <c r="C152" t="n">
-        <v>100.93</v>
+        <v>101.35</v>
       </c>
       <c r="D152" t="n">
-        <v>1.325</v>
+        <v>1.625</v>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>15-06-28</t>
+          <t>15-07-32</t>
         </is>
       </c>
       <c r="F152" t="n">
-        <v>2.65</v>
+        <v>3.25</v>
       </c>
       <c r="G152" t="n">
-        <v>2.625</v>
+        <v>3.206</v>
       </c>
       <c r="H152" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="I152" t="n">
-        <v>107.95</v>
+        <v>122.75</v>
       </c>
       <c r="J152" t="n">
-        <v>7.019999999999996</v>
+        <v>21.40000000000001</v>
       </c>
       <c r="K152" t="n">
-        <v>6.142</v>
+        <v>18.725</v>
       </c>
       <c r="L152" t="n">
-        <v>2.463</v>
+        <v>3.089</v>
       </c>
       <c r="M152" t="n">
-        <v>2.155</v>
+        <v>2.702</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>IT0005647265 -Btp Fx 3.25% Jul32 EurUltimo: 101,23Cedola: 1,625Scadenza: 15/07/2032IT0005647265</t>
+          <t>IT0005647273 -Btpi Fx May56 EurUltimo: 100,88Cedola: 1,275Scadenza: 15/05/2056IT0005647273</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Btp Fx 3.25% Jul32 Eur</t>
+          <t>Btpi Fx May56 Eur</t>
         </is>
       </c>
       <c r="C153" t="n">
-        <v>101.23</v>
+        <v>100.88</v>
       </c>
       <c r="D153" t="n">
-        <v>1.625</v>
+        <v>1.275</v>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>15-07-32</t>
+          <t>15-05-56</t>
         </is>
       </c>
       <c r="F153" t="n">
-        <v>3.25</v>
+        <v>2.55</v>
       </c>
       <c r="G153" t="n">
-        <v>3.21</v>
+        <v>2.527</v>
       </c>
       <c r="H153" t="n">
-        <v>14</v>
+        <v>62</v>
       </c>
       <c r="I153" t="n">
-        <v>122.75</v>
+        <v>179.05</v>
       </c>
       <c r="J153" t="n">
-        <v>21.52</v>
+        <v>78.17000000000002</v>
       </c>
       <c r="K153" t="n">
-        <v>18.83</v>
+        <v>68.398</v>
       </c>
       <c r="L153" t="n">
-        <v>3.103</v>
+        <v>2.54</v>
       </c>
       <c r="M153" t="n">
-        <v>2.715</v>
+        <v>2.222</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>IT0005647273 -Btpi Fx May56 EurUltimo: 101,38Cedola: 1,275Scadenza: 15/05/2056IT0005647273</t>
+          <t>IT0005648149 -Btp Fx 3.6% Oct35 EurUltimo: 101,26Cedola: 1,49508Scadenza: 01/10/2035IT0005648149</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Btpi Fx May56 Eur</t>
+          <t>Btp Fx 3.6% Oct35 Eur</t>
         </is>
       </c>
       <c r="C154" t="n">
-        <v>101.38</v>
+        <v>101.26</v>
       </c>
       <c r="D154" t="n">
-        <v>1.275</v>
+        <v>1.49508</v>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>15-05-56</t>
+          <t>01-10-35</t>
         </is>
       </c>
       <c r="F154" t="n">
-        <v>2.55</v>
+        <v>2.99016</v>
       </c>
       <c r="G154" t="n">
-        <v>2.515</v>
+        <v>2.952</v>
       </c>
       <c r="H154" t="n">
-        <v>62</v>
+        <v>21</v>
       </c>
       <c r="I154" t="n">
-        <v>179.05</v>
+        <v>131.39668</v>
       </c>
       <c r="J154" t="n">
-        <v>77.67000000000002</v>
+        <v>30.13668</v>
       </c>
       <c r="K154" t="n">
-        <v>67.961</v>
+        <v>26.369</v>
       </c>
       <c r="L154" t="n">
-        <v>2.523</v>
+        <v>2.972</v>
       </c>
       <c r="M154" t="n">
-        <v>2.207</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>IT0005648149 -Btp Fx 3.6% Oct35 EurUltimo: 101,10Cedola: 1,49508Scadenza: 01/10/2035IT0005648149</t>
+          <t>IT0005648255 -Btp Italia Jun32 EurUltimo: 100,80Cedola: 0,925Scadenza: 04/06/2032IT0005648255</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Btp Fx 3.6% Oct35 Eur</t>
+          <t>Btp Italia Jun32 Eur</t>
         </is>
       </c>
       <c r="C155" t="n">
-        <v>101.1</v>
+        <v>100.8</v>
       </c>
       <c r="D155" t="n">
-        <v>1.49508</v>
+        <v>0.925</v>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>01-10-35</t>
+          <t>04-06-32</t>
         </is>
       </c>
       <c r="F155" t="n">
-        <v>2.99016</v>
+        <v>1.85</v>
       </c>
       <c r="G155" t="n">
-        <v>2.957</v>
+        <v>1.835</v>
       </c>
       <c r="H155" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="I155" t="n">
-        <v>131.39668</v>
+        <v>112.95</v>
       </c>
       <c r="J155" t="n">
-        <v>30.29668000000001</v>
+        <v>12.15000000000001</v>
       </c>
       <c r="K155" t="n">
-        <v>26.509</v>
+        <v>10.631</v>
       </c>
       <c r="L155" t="n">
-        <v>2.985</v>
+        <v>1.783</v>
       </c>
       <c r="M155" t="n">
-        <v>2.611</v>
+        <v>1.56</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>IT0005648255 -Btp Italia Jun32 EurUltimo: 100,73Cedola: 0,925Scadenza: 04/06/2032IT0005648255</t>
+          <t>IT0005654642 -Btp Fx 2.7% Oct30 EurUltimo: 99,93Cedola: 0,82623Scadenza: 01/10/2030IT0005654642</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Btp Italia Jun32 Eur</t>
+          <t>Btp Fx 2.7% Oct30 Eur</t>
         </is>
       </c>
       <c r="C156" t="n">
-        <v>100.73</v>
+        <v>99.93000000000001</v>
       </c>
       <c r="D156" t="n">
-        <v>0.925</v>
+        <v>0.82623</v>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>04-06-32</t>
+          <t>01-10-30</t>
         </is>
       </c>
       <c r="F156" t="n">
-        <v>1.85</v>
+        <v>1.65246</v>
       </c>
       <c r="G156" t="n">
-        <v>1.836</v>
+        <v>1.653</v>
       </c>
       <c r="H156" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="I156" t="n">
-        <v>112.95</v>
+        <v>109.08853</v>
       </c>
       <c r="J156" t="n">
-        <v>12.22</v>
+        <v>9.158529999999999</v>
       </c>
       <c r="K156" t="n">
-        <v>10.692</v>
+        <v>8.013</v>
       </c>
       <c r="L156" t="n">
-        <v>1.791</v>
+        <v>1.782</v>
       </c>
       <c r="M156" t="n">
-        <v>1.567</v>
+        <v>1.559</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>IT0005654642 -Btp Fx 2.7% Oct30 EurUltimo: 99,71Cedola: 0,82623Scadenza: 01/10/2030IT0005654642</t>
+          <t>IT0005657330 -Btp Fx 2.1% Aug27 EurUltimo: 99,93Cedola: 0,34807Scadenza: 26/08/2027IT0005657330</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Btp Fx 2.7% Oct30 Eur</t>
+          <t>Btp Fx 2.1% Aug27 Eur</t>
         </is>
       </c>
       <c r="C157" t="n">
-        <v>99.70999999999999</v>
+        <v>99.93000000000001</v>
       </c>
       <c r="D157" t="n">
-        <v>0.82623</v>
+        <v>0.34807</v>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>01-10-30</t>
+          <t>26-08-27</t>
         </is>
       </c>
       <c r="F157" t="n">
-        <v>1.65246</v>
+        <v>0.69614</v>
       </c>
       <c r="G157" t="n">
-        <v>1.657</v>
+        <v>0.696</v>
       </c>
       <c r="H157" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="I157" t="n">
-        <v>109.08853</v>
+        <v>101.74035</v>
       </c>
       <c r="J157" t="n">
-        <v>9.378530000000012</v>
+        <v>1.81035</v>
       </c>
       <c r="K157" t="n">
-        <v>8.206</v>
+        <v>1.584</v>
       </c>
       <c r="L157" t="n">
-        <v>1.822</v>
+        <v>0.889</v>
       </c>
       <c r="M157" t="n">
-        <v>1.594</v>
+        <v>0.777</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>IT0005657330 -Btp Fx 2.1% Aug27 EurUltimo: 99,85Cedola: 0,34807Scadenza: 26/08/2027IT0005657330</t>
+          <t>IT0005657348 -Btpi Fx Aug31 EurUltimo: 99,80Cedola: 0,1489Scadenza: 15/08/2031IT0005657348</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Btp Fx 2.1% Aug27 Eur</t>
+          <t>Btpi Fx Aug31 Eur</t>
         </is>
       </c>
       <c r="C158" t="n">
-        <v>99.84999999999999</v>
+        <v>99.8</v>
       </c>
       <c r="D158" t="n">
-        <v>0.34807</v>
+        <v>0.1489</v>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>26-08-27</t>
+          <t>15-08-31</t>
         </is>
       </c>
       <c r="F158" t="n">
-        <v>0.69614</v>
+        <v>0.2978</v>
       </c>
       <c r="G158" t="n">
-        <v>0.697</v>
+        <v>0.298</v>
       </c>
       <c r="H158" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="I158" t="n">
-        <v>101.74035</v>
+        <v>101.9357</v>
       </c>
       <c r="J158" t="n">
-        <v>1.890350000000012</v>
+        <v>2.1357</v>
       </c>
       <c r="K158" t="n">
-        <v>1.654</v>
+        <v>1.868</v>
       </c>
       <c r="L158" t="n">
-        <v>0.924</v>
+        <v>0.355</v>
       </c>
       <c r="M158" t="n">
-        <v>0.8080000000000001</v>
+        <v>0.31</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>IT0005657348 -Btpi Fx Aug31 EurUltimo: 99,70Cedola: 0,1489Scadenza: 15/08/2031IT0005657348</t>
+          <t>IT0005660052 -Btp Fx 2.35% Jan29 EurUltimo: 99,86Cedola: 1,175Scadenza: 15/01/2029IT0005660052</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Btpi Fx Aug31 Eur</t>
+          <t>Btp Fx 2.35% Jan29 Eur</t>
         </is>
       </c>
       <c r="C159" t="n">
-        <v>99.7</v>
+        <v>99.86</v>
       </c>
       <c r="D159" t="n">
-        <v>0.1489</v>
+        <v>1.175</v>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>15-08-31</t>
+          <t>15-01-29</t>
         </is>
       </c>
       <c r="F159" t="n">
-        <v>0.2978</v>
+        <v>2.35</v>
       </c>
       <c r="G159" t="n">
-        <v>0.298</v>
+        <v>2.353</v>
       </c>
       <c r="H159" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="I159" t="n">
-        <v>101.9357</v>
+        <v>108.225</v>
       </c>
       <c r="J159" t="n">
-        <v>2.235699999999994</v>
+        <v>8.364999999999995</v>
       </c>
       <c r="K159" t="n">
-        <v>1.956</v>
+        <v>7.319</v>
       </c>
       <c r="L159" t="n">
-        <v>0.371</v>
+        <v>2.44</v>
       </c>
       <c r="M159" t="n">
-        <v>0.324</v>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="inlineStr">
-        <is>
-          <t>IT0005660052 -Btp Fx 2.35% Jan29 EurUltimo: 99,70Cedola: 1,175Scadenza: 15/01/2029IT0005660052</t>
-        </is>
-      </c>
-      <c r="B160" t="inlineStr">
-        <is>
-          <t>Btp Fx 2.35% Jan29 Eur</t>
-        </is>
-      </c>
-      <c r="C160" t="n">
-        <v>99.7</v>
-      </c>
-      <c r="D160" t="n">
-        <v>1.175</v>
-      </c>
-      <c r="E160" t="inlineStr">
-        <is>
-          <t>15-01-29</t>
-        </is>
-      </c>
-      <c r="F160" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="G160" t="n">
-        <v>2.357</v>
-      </c>
-      <c r="H160" t="n">
-        <v>7</v>
-      </c>
-      <c r="I160" t="n">
-        <v>108.225</v>
-      </c>
-      <c r="J160" t="n">
-        <v>8.524999999999991</v>
-      </c>
-      <c r="K160" t="n">
-        <v>7.459</v>
-      </c>
-      <c r="L160" t="n">
-        <v>2.481</v>
-      </c>
-      <c r="M160" t="n">
-        <v>2.17</v>
+        <v>2.135</v>
       </c>
     </row>
   </sheetData>

--- a/btp_dati.xlsx
+++ b/btp_dati.xlsx
@@ -473,9 +473,6 @@
           <t>Btp-1nv26      7,25%</t>
         </is>
       </c>
-      <c r="C2" t="n">
-        <v>106.23</v>
-      </c>
       <c r="D2" t="n">
         <v>3.625</v>
       </c>
@@ -496,9 +493,6 @@
           <t>Btp-1nv27       6,5%</t>
         </is>
       </c>
-      <c r="C3" t="n">
-        <v>109.25</v>
-      </c>
       <c r="D3" t="n">
         <v>3.25</v>
       </c>
@@ -519,9 +513,6 @@
           <t>Btp-1nv29      5,25%</t>
         </is>
       </c>
-      <c r="C4" t="n">
-        <v>110.91</v>
-      </c>
       <c r="D4" t="n">
         <v>2.625</v>
       </c>
@@ -542,9 +533,6 @@
           <t>Btp-1mg31         6%</t>
         </is>
       </c>
-      <c r="C5" t="n">
-        <v>116.77</v>
-      </c>
       <c r="D5" t="n">
         <v>3</v>
       </c>
@@ -565,9 +553,6 @@
           <t>Btp-1fb33      5,75%</t>
         </is>
       </c>
-      <c r="C6" t="n">
-        <v>117.02</v>
-      </c>
       <c r="D6" t="n">
         <v>2.875</v>
       </c>
@@ -588,9 +573,6 @@
           <t>Btp-1ag34         5%</t>
         </is>
       </c>
-      <c r="C7" t="n">
-        <v>112.55</v>
-      </c>
       <c r="D7" t="n">
         <v>2.5</v>
       </c>
@@ -611,9 +593,6 @@
           <t>Btpi-15st35    2,35%</t>
         </is>
       </c>
-      <c r="C8" t="n">
-        <v>107.07</v>
-      </c>
       <c r="D8" t="n">
         <v>1.175</v>
       </c>
@@ -634,9 +613,6 @@
           <t>Btp-1fb37         4%</t>
         </is>
       </c>
-      <c r="C9" t="n">
-        <v>103.57</v>
-      </c>
       <c r="D9" t="n">
         <v>2</v>
       </c>
@@ -657,9 +633,6 @@
           <t>Btp-1ag39         5%</t>
         </is>
       </c>
-      <c r="C10" t="n">
-        <v>112.44</v>
-      </c>
       <c r="D10" t="n">
         <v>2.5</v>
       </c>
@@ -680,9 +653,6 @@
           <t>Btp-1st40 5%</t>
         </is>
       </c>
-      <c r="C11" t="n">
-        <v>112.25</v>
-      </c>
       <c r="D11" t="n">
         <v>2.5</v>
       </c>
@@ -703,9 +673,6 @@
           <t>Btpi-15st41 2,55%</t>
         </is>
       </c>
-      <c r="C12" t="n">
-        <v>106.05</v>
-      </c>
       <c r="D12" t="n">
         <v>1.275</v>
       </c>
@@ -726,9 +693,6 @@
           <t>Btp-1mz26 4,5%</t>
         </is>
       </c>
-      <c r="C13" t="n">
-        <v>101.307</v>
-      </c>
       <c r="D13" t="n">
         <v>2.25</v>
       </c>
@@ -749,9 +713,6 @@
           <t>Btpi-15st26 3,1%</t>
         </is>
       </c>
-      <c r="C14" t="n">
-        <v>102.86</v>
-      </c>
       <c r="D14" t="n">
         <v>1.55</v>
       </c>
@@ -772,9 +733,6 @@
           <t>Btp Coupon Strip Zc Nv26 Eur</t>
         </is>
       </c>
-      <c r="C15" t="n">
-        <v>97.79000000000001</v>
-      </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>01-11-26</t>
@@ -792,9 +750,6 @@
           <t>Btp Coupon Strip Zc Nv27 Eur</t>
         </is>
       </c>
-      <c r="C16" t="n">
-        <v>95.34999999999999</v>
-      </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>01-11-27</t>
@@ -812,9 +767,6 @@
           <t>Btp Coupon Strip Zc Nv29 Eur</t>
         </is>
       </c>
-      <c r="C17" t="n">
-        <v>89.98</v>
-      </c>
       <c r="E17" t="inlineStr">
         <is>
           <t>01-11-29</t>
@@ -832,9 +784,6 @@
           <t>Btp Coupon Strip Zc Mg31 Eur</t>
         </is>
       </c>
-      <c r="C18" t="n">
-        <v>84.97</v>
-      </c>
       <c r="E18" t="inlineStr">
         <is>
           <t>01-05-31</t>
@@ -903,9 +852,6 @@
           <t>Btp Tf 4,75% St28 Eur</t>
         </is>
       </c>
-      <c r="C22" t="n">
-        <v>107.03</v>
-      </c>
       <c r="D22" t="n">
         <v>2.375</v>
       </c>
@@ -926,9 +872,6 @@
           <t>Btp Tf 4,75% St44 Eur</t>
         </is>
       </c>
-      <c r="C23" t="n">
-        <v>108.46</v>
-      </c>
       <c r="D23" t="n">
         <v>2.375</v>
       </c>
@@ -949,9 +892,6 @@
           <t>Btp Coupon Strip Zc St28 Eur</t>
         </is>
       </c>
-      <c r="C24" t="n">
-        <v>93.19</v>
-      </c>
       <c r="E24" t="inlineStr">
         <is>
           <t>01-09-28</t>
@@ -969,9 +909,6 @@
           <t>Btp Coupon Strip Zc Mz30 Eur</t>
         </is>
       </c>
-      <c r="C25" t="n">
-        <v>89.15000000000001</v>
-      </c>
       <c r="E25" t="inlineStr">
         <is>
           <t>01-03-30</t>
@@ -1074,9 +1011,6 @@
           <t>Btp Tf 3,50% Mz30 Eur</t>
         </is>
       </c>
-      <c r="C31" t="n">
-        <v>103.94</v>
-      </c>
       <c r="D31" t="n">
         <v>1.75</v>
       </c>
@@ -1097,9 +1031,6 @@
           <t>Btp Tf 3,25% St46 Eur</t>
         </is>
       </c>
-      <c r="C32" t="n">
-        <v>86.95999999999999</v>
-      </c>
       <c r="D32" t="n">
         <v>1.625</v>
       </c>
@@ -1120,9 +1051,6 @@
           <t>Btp Tf 1,65% Mz32 Eur</t>
         </is>
       </c>
-      <c r="C33" t="n">
-        <v>92.09999999999999</v>
-      </c>
       <c r="D33" t="n">
         <v>0.825</v>
       </c>
@@ -1143,9 +1071,6 @@
           <t>Btp Tf 2,00% Dc25 Eur</t>
         </is>
       </c>
-      <c r="C34" t="n">
-        <v>100.004</v>
-      </c>
       <c r="D34" t="n">
         <v>1</v>
       </c>
@@ -1166,9 +1091,6 @@
           <t>Btpi Tf 1,25% St32 Eur</t>
         </is>
       </c>
-      <c r="C35" t="n">
-        <v>99.81999999999999</v>
-      </c>
       <c r="D35" t="n">
         <v>0.625</v>
       </c>
@@ -1189,9 +1111,6 @@
           <t>Btp Tf 2,7% Mz47 Eur</t>
         </is>
       </c>
-      <c r="C36" t="n">
-        <v>79.05</v>
-      </c>
       <c r="D36" t="n">
         <v>1.35</v>
       </c>
@@ -1212,9 +1131,6 @@
           <t>Btp Tf 1,60% Gn26 Eur</t>
         </is>
       </c>
-      <c r="C37" t="n">
-        <v>99.76000000000001</v>
-      </c>
       <c r="D37" t="n">
         <v>0.8</v>
       </c>
@@ -1235,9 +1151,6 @@
           <t>Btp Tf 2,25% St36 Eur</t>
         </is>
       </c>
-      <c r="C38" t="n">
-        <v>87.88</v>
-      </c>
       <c r="D38" t="n">
         <v>1.125</v>
       </c>
@@ -1258,9 +1171,6 @@
           <t>Btp Tf 1.25% Dc26 Eur</t>
         </is>
       </c>
-      <c r="C39" t="n">
-        <v>99.06</v>
-      </c>
       <c r="D39" t="n">
         <v>0.625</v>
       </c>
@@ -1281,9 +1191,6 @@
           <t>Btp Tf 2,8% Mz67 Eur</t>
         </is>
       </c>
-      <c r="C40" t="n">
-        <v>69.73999999999999</v>
-      </c>
       <c r="D40" t="n">
         <v>1.4</v>
       </c>
@@ -1304,9 +1211,6 @@
           <t>Btp Tf 2,45% St33 Eur</t>
         </is>
       </c>
-      <c r="C41" t="n">
-        <v>94.61</v>
-      </c>
       <c r="D41" t="n">
         <v>1.225</v>
       </c>
@@ -1327,9 +1231,6 @@
           <t>Btp Tf 2,20% Gn27 Eur</t>
         </is>
       </c>
-      <c r="C42" t="n">
-        <v>100.29</v>
-      </c>
       <c r="D42" t="n">
         <v>1.1</v>
       </c>
@@ -1350,9 +1251,6 @@
           <t>Btpi Tf 1,30% Mg28 Eur</t>
         </is>
       </c>
-      <c r="C43" t="n">
-        <v>101.36</v>
-      </c>
       <c r="D43" t="n">
         <v>0.65</v>
       </c>
@@ -1373,9 +1271,6 @@
           <t>Btp Tf 3,45% Mz48 Eur</t>
         </is>
       </c>
-      <c r="C44" t="n">
-        <v>88.90000000000001</v>
-      </c>
       <c r="D44" t="n">
         <v>1.725</v>
       </c>
@@ -1396,9 +1291,6 @@
           <t>Btp Tf 2,05% Ag27 Eur</t>
         </is>
       </c>
-      <c r="C45" t="n">
-        <v>99.94</v>
-      </c>
       <c r="D45" t="n">
         <v>1.025</v>
       </c>
@@ -1419,9 +1311,6 @@
           <t>Btp Tf 2,95% St38 Eur</t>
         </is>
       </c>
-      <c r="C46" t="n">
-        <v>91.55</v>
-      </c>
       <c r="D46" t="n">
         <v>1.475</v>
       </c>
@@ -1442,9 +1331,6 @@
           <t>Btp Tf 2,00% Fb28 Eur</t>
         </is>
       </c>
-      <c r="C47" t="n">
-        <v>99.66</v>
-      </c>
       <c r="D47" t="n">
         <v>1</v>
       </c>
@@ -1465,9 +1351,6 @@
           <t>Btp Italia Mg26 Eur</t>
         </is>
       </c>
-      <c r="C48" t="n">
-        <v>99.879</v>
-      </c>
       <c r="D48" t="n">
         <v>0.275</v>
       </c>
@@ -1488,9 +1371,6 @@
           <t>Btp Tf 2,80% Dc28 Eur</t>
         </is>
       </c>
-      <c r="C49" t="n">
-        <v>101.55</v>
-      </c>
       <c r="D49" t="n">
         <v>1.4</v>
       </c>
@@ -1511,9 +1391,6 @@
           <t>Btp Tf 2.50% Nv25 Eur</t>
         </is>
       </c>
-      <c r="C50" t="n">
-        <v>100.107</v>
-      </c>
       <c r="D50" t="n">
         <v>1.25</v>
       </c>
@@ -1534,9 +1411,6 @@
           <t>Btp Tf 3,35% Mz35 Eur</t>
         </is>
       </c>
-      <c r="C51" t="n">
-        <v>99.45999999999999</v>
-      </c>
       <c r="D51" t="n">
         <v>1.675</v>
       </c>
@@ -1557,9 +1431,6 @@
           <t>Btp Tf 3,85% St49 Eur</t>
         </is>
       </c>
-      <c r="C52" t="n">
-        <v>94.02</v>
-      </c>
       <c r="D52" t="n">
         <v>1.925</v>
       </c>
@@ -1580,9 +1451,6 @@
           <t>Btp Tf 3,00% Ag29 Eur</t>
         </is>
       </c>
-      <c r="C53" t="n">
-        <v>101.95</v>
-      </c>
       <c r="D53" t="n">
         <v>1.5</v>
       </c>
@@ -1603,9 +1471,6 @@
           <t>Btp Tf 2,10% Lg26 Eur</t>
         </is>
       </c>
-      <c r="C54" t="n">
-        <v>100.095</v>
-      </c>
       <c r="D54" t="n">
         <v>1.05</v>
       </c>
@@ -1626,9 +1491,6 @@
           <t>Btp Tf 3,1% Mz40 Eur</t>
         </is>
       </c>
-      <c r="C55" t="n">
-        <v>91.09999999999999</v>
-      </c>
       <c r="D55" t="n">
         <v>1.55</v>
       </c>
@@ -1649,9 +1511,6 @@
           <t>Btp Tf 1,35% Ap30 Eur</t>
         </is>
       </c>
-      <c r="C56" t="n">
-        <v>94.5</v>
-      </c>
       <c r="D56" t="n">
         <v>0.675</v>
       </c>
@@ -1672,9 +1531,6 @@
           <t>Btpi Tf 0,4% Mg30 Eur</t>
         </is>
       </c>
-      <c r="C57" t="n">
-        <v>97.02</v>
-      </c>
       <c r="D57" t="n">
         <v>0.2</v>
       </c>
@@ -1695,9 +1551,6 @@
           <t>Btp Italia Ot27 Eur</t>
         </is>
       </c>
-      <c r="C58" t="n">
-        <v>99.8</v>
-      </c>
       <c r="D58" t="n">
         <v>0.325</v>
       </c>
@@ -1718,9 +1571,6 @@
           <t>Btp Tf 0,85% Ge27 Eur</t>
         </is>
       </c>
-      <c r="C59" t="n">
-        <v>98.45999999999999</v>
-      </c>
       <c r="D59" t="n">
         <v>0.425</v>
       </c>
@@ -1741,9 +1591,6 @@
           <t>Btp Tf 2,45% St50 Eur</t>
         </is>
       </c>
-      <c r="C60" t="n">
-        <v>72.03</v>
-      </c>
       <c r="D60" t="n">
         <v>1.225</v>
       </c>
@@ -1764,9 +1611,6 @@
           <t>Btp Tf 1,45% Mz36 Eur</t>
         </is>
       </c>
-      <c r="C61" t="n">
-        <v>81.5</v>
-      </c>
       <c r="D61" t="n">
         <v>0.725</v>
       </c>
@@ -1787,9 +1631,6 @@
           <t>Btp Tf 0,95% Ag30 Eur</t>
         </is>
       </c>
-      <c r="C62" t="n">
-        <v>91.97</v>
-      </c>
       <c r="D62" t="n">
         <v>0.475</v>
       </c>
@@ -1810,9 +1651,6 @@
           <t>Btp Tf 1,65% Dc30 Eur</t>
         </is>
       </c>
-      <c r="C63" t="n">
-        <v>94.53</v>
-      </c>
       <c r="D63" t="n">
         <v>0.825</v>
       </c>
@@ -1833,9 +1671,6 @@
           <t>Btp Futura Lg30 Eur</t>
         </is>
       </c>
-      <c r="C64" t="n">
-        <v>93.92</v>
-      </c>
       <c r="D64" t="n">
         <v>0.65</v>
       </c>
@@ -1856,9 +1691,6 @@
           <t>Btpi Tf 0,65% Mg26 Eur</t>
         </is>
       </c>
-      <c r="C65" t="n">
-        <v>99.476</v>
-      </c>
       <c r="D65" t="n">
         <v>0.325</v>
       </c>
@@ -1879,9 +1711,6 @@
           <t>Btp Tf 0,95% St27 Eur</t>
         </is>
       </c>
-      <c r="C66" t="n">
-        <v>97.69</v>
-      </c>
       <c r="D66" t="n">
         <v>0.475</v>
       </c>
@@ -1902,9 +1731,6 @@
           <t>Btp Tf 0,50% Fb26 Eur</t>
         </is>
       </c>
-      <c r="C67" t="n">
-        <v>99.355</v>
-      </c>
       <c r="D67" t="n">
         <v>0.25</v>
       </c>
@@ -1925,9 +1751,6 @@
           <t>Btp Tf 1,8% Mz41 Eur</t>
         </is>
       </c>
-      <c r="C68" t="n">
-        <v>74.87</v>
-      </c>
       <c r="D68" t="n">
         <v>0.9</v>
       </c>
@@ -1948,9 +1771,6 @@
           <t>Btp Tf 0,90% Ap31 Eur</t>
         </is>
       </c>
-      <c r="C69" t="n">
-        <v>90</v>
-      </c>
       <c r="D69" t="n">
         <v>0.45</v>
       </c>
@@ -1971,9 +1791,6 @@
           <t>Btp Tf 1,7% St51 Eur</t>
         </is>
       </c>
-      <c r="C70" t="n">
-        <v>60.18</v>
-      </c>
       <c r="D70" t="n">
         <v>0.85</v>
       </c>
@@ -1994,9 +1811,6 @@
           <t>Btp Futura Nv28 Eur</t>
         </is>
       </c>
-      <c r="C71" t="n">
-        <v>95.18000000000001</v>
-      </c>
       <c r="D71" t="n">
         <v>0.3</v>
       </c>
@@ -2017,9 +1831,6 @@
           <t>Btp Tf 0,95% Mz37 Eur</t>
         </is>
       </c>
-      <c r="C72" t="n">
-        <v>74.63</v>
-      </c>
       <c r="D72" t="n">
         <v>0.475</v>
       </c>
@@ -2040,9 +1851,6 @@
           <t>Btp Tf 0,25% Mz28 Eur</t>
         </is>
       </c>
-      <c r="C73" t="n">
-        <v>95.16</v>
-      </c>
       <c r="D73" t="n">
         <v>0.125</v>
       </c>
@@ -2063,9 +1871,6 @@
           <t>Btp Tf 0,6% Ag31 Eur</t>
         </is>
       </c>
-      <c r="C74" t="n">
-        <v>87.58</v>
-      </c>
       <c r="D74" t="n">
         <v>0.3</v>
       </c>
@@ -2086,9 +1891,6 @@
           <t>Btpi Tf 0,15% Mg51 Eur</t>
         </is>
       </c>
-      <c r="C75" t="n">
-        <v>58.98</v>
-      </c>
       <c r="D75" t="n">
         <v>0.075</v>
       </c>
@@ -2109,9 +1911,6 @@
           <t>Btp Tf 0% Ap26 Eur</t>
         </is>
       </c>
-      <c r="C76" t="n">
-        <v>98.833</v>
-      </c>
       <c r="E76" t="inlineStr">
         <is>
           <t>01-04-26</t>
@@ -2129,9 +1928,6 @@
           <t>Btpgreen 1,5%Ap45eur</t>
         </is>
       </c>
-      <c r="C77" t="n">
-        <v>65.12</v>
-      </c>
       <c r="D77" t="n">
         <v>0.75</v>
       </c>
@@ -2152,9 +1948,6 @@
           <t>Btp Tf 2,15% Mz72 Eur</t>
         </is>
       </c>
-      <c r="C78" t="n">
-        <v>57.52</v>
-      </c>
       <c r="D78" t="n">
         <v>1.075</v>
       </c>
@@ -2175,9 +1968,6 @@
           <t>Btp Futura Ap37 Eur</t>
         </is>
       </c>
-      <c r="C79" t="n">
-        <v>78.84999999999999</v>
-      </c>
       <c r="D79" t="n">
         <v>0.6</v>
       </c>
@@ -2198,9 +1988,6 @@
           <t>Btp Tf 0,5% Lg28 Eur</t>
         </is>
       </c>
-      <c r="C80" t="n">
-        <v>95.09999999999999</v>
-      </c>
       <c r="D80" t="n">
         <v>0.25</v>
       </c>
@@ -2221,9 +2008,6 @@
           <t>Btp Tf 0,95% Dc31 Eur</t>
         </is>
       </c>
-      <c r="C81" t="n">
-        <v>88.64</v>
-      </c>
       <c r="D81" t="n">
         <v>0.475</v>
       </c>
@@ -2244,9 +2028,6 @@
           <t>Btp Tf 0% Ag26 Eur</t>
         </is>
       </c>
-      <c r="C82" t="n">
-        <v>98.28</v>
-      </c>
       <c r="E82" t="inlineStr">
         <is>
           <t>01-08-26</t>
@@ -2264,9 +2045,6 @@
           <t>Btp Tf 0,95% Gn32 Eur</t>
         </is>
       </c>
-      <c r="C83" t="n">
-        <v>87.38</v>
-      </c>
       <c r="D83" t="n">
         <v>0.475</v>
       </c>
@@ -2287,9 +2065,6 @@
           <t>Btp Futura Nv33 Eur</t>
         </is>
       </c>
-      <c r="C84" t="n">
-        <v>87.20999999999999</v>
-      </c>
       <c r="D84" t="n">
         <v>0.375</v>
       </c>
@@ -2310,9 +2085,6 @@
           <t>Btp Tf 0,45% Fb29 Eur</t>
         </is>
       </c>
-      <c r="C85" t="n">
-        <v>93.53</v>
-      </c>
       <c r="D85" t="n">
         <v>0.225</v>
       </c>
@@ -2333,9 +2105,6 @@
           <t>Btp Tf 2,15% St52 Eur</t>
         </is>
       </c>
-      <c r="C86" t="n">
-        <v>65.84999999999999</v>
-      </c>
       <c r="D86" t="n">
         <v>1.075</v>
       </c>
@@ -2356,9 +2125,6 @@
           <t>Btpi Tf 0,1% Mg33 Eur</t>
         </is>
       </c>
-      <c r="C87" t="n">
-        <v>89.94</v>
-      </c>
       <c r="D87" t="n">
         <v>0.05</v>
       </c>
@@ -2379,9 +2145,6 @@
           <t>Btp Tf 1,1% Ap27 Eur</t>
         </is>
       </c>
-      <c r="C88" t="n">
-        <v>98.47</v>
-      </c>
       <c r="D88" t="n">
         <v>0.55</v>
       </c>
@@ -2402,9 +2165,6 @@
           <t>Btp Tf 2,5% Dc32 Eur</t>
         </is>
       </c>
-      <c r="C89" t="n">
-        <v>95.98999999999999</v>
-      </c>
       <c r="D89" t="n">
         <v>1.25</v>
       </c>
@@ -2425,9 +2185,6 @@
           <t>Btp Tf 2,80% Gn29 Eur</t>
         </is>
       </c>
-      <c r="C90" t="n">
-        <v>101.07</v>
-      </c>
       <c r="D90" t="n">
         <v>1.4</v>
       </c>
@@ -2448,9 +2205,6 @@
           <t>Btp Tf 3,25% Mz38 Eur</t>
         </is>
       </c>
-      <c r="C91" t="n">
-        <v>94.97</v>
-      </c>
       <c r="D91" t="n">
         <v>1.625</v>
       </c>
@@ -2471,9 +2225,6 @@
           <t>Btp Italia Gn30 Eur</t>
         </is>
       </c>
-      <c r="C92" t="n">
-        <v>100.87</v>
-      </c>
       <c r="D92" t="n">
         <v>0.8</v>
       </c>
@@ -2630,9 +2381,6 @@
           <t>Btp Tf 2,65% Dc27 Eur</t>
         </is>
       </c>
-      <c r="C101" t="n">
-        <v>101.02</v>
-      </c>
       <c r="D101" t="n">
         <v>1.325</v>
       </c>
@@ -2653,9 +2401,6 @@
           <t>Btpgreen 4%Ap35eur</t>
         </is>
       </c>
-      <c r="C102" t="n">
-        <v>105.06</v>
-      </c>
       <c r="D102" t="n">
         <v>2</v>
       </c>
@@ -2676,9 +2421,6 @@
           <t>Btp Tf 3,5% Ge26 Eur</t>
         </is>
       </c>
-      <c r="C103" t="n">
-        <v>100.592</v>
-      </c>
       <c r="D103" t="n">
         <v>1.75</v>
       </c>
@@ -2699,9 +2441,6 @@
           <t>Btp Italia Nv28 Eur</t>
         </is>
       </c>
-      <c r="C104" t="n">
-        <v>101.43</v>
-      </c>
       <c r="D104" t="n">
         <v>0.8</v>
       </c>
@@ -2722,9 +2461,6 @@
           <t>Btp Tf 4,40% Mg33 Eur</t>
         </is>
       </c>
-      <c r="C105" t="n">
-        <v>108.13</v>
-      </c>
       <c r="D105" t="n">
         <v>2.2</v>
       </c>
@@ -2745,9 +2481,6 @@
           <t>Btp Tf 3,85% Dc29 Eur</t>
         </is>
       </c>
-      <c r="C106" t="n">
-        <v>105.12</v>
-      </c>
       <c r="D106" t="n">
         <v>1.925</v>
       </c>
@@ -2768,9 +2501,6 @@
           <t>Btp Tf 3,4% Ap28 Eur</t>
         </is>
       </c>
-      <c r="C107" t="n">
-        <v>102.9</v>
-      </c>
       <c r="D107" t="n">
         <v>1.7</v>
       </c>
@@ -2808,9 +2538,6 @@
           <t>Btp Tf 4,45% St43 Eur</t>
         </is>
       </c>
-      <c r="C109" t="n">
-        <v>104.29</v>
-      </c>
       <c r="D109" t="n">
         <v>2.225</v>
       </c>
@@ -2831,9 +2558,6 @@
           <t>Btp Italia Mz28 Eur</t>
         </is>
       </c>
-      <c r="C110" t="n">
-        <v>102.38</v>
-      </c>
       <c r="D110" t="n">
         <v>1</v>
       </c>
@@ -2854,9 +2578,6 @@
           <t>Btp Tf 4,5% Ot53 Eur</t>
         </is>
       </c>
-      <c r="C111" t="n">
-        <v>101.25</v>
-      </c>
       <c r="D111" t="n">
         <v>2.25</v>
       </c>
@@ -2877,9 +2598,6 @@
           <t>Btp Tf 3,80% Ap26 Eur</t>
         </is>
       </c>
-      <c r="C112" t="n">
-        <v>101.16</v>
-      </c>
       <c r="D112" t="n">
         <v>1.9</v>
       </c>
@@ -2900,9 +2618,6 @@
           <t>Btpgreen 4%Ot31eur</t>
         </is>
       </c>
-      <c r="C113" t="n">
-        <v>106.19</v>
-      </c>
       <c r="D113" t="n">
         <v>2</v>
       </c>
@@ -2923,9 +2638,6 @@
           <t>Btp Tf 3,7% Gn30 Eur</t>
         </is>
       </c>
-      <c r="C114" t="n">
-        <v>104.38</v>
-      </c>
       <c r="D114" t="n">
         <v>1.85</v>
       </c>
@@ -2966,9 +2678,6 @@
           <t>Btp Tf 4,35% Nv33 Eur</t>
         </is>
       </c>
-      <c r="C116" t="n">
-        <v>107.66</v>
-      </c>
       <c r="D116" t="n">
         <v>2.175</v>
       </c>
@@ -2989,9 +2698,6 @@
           <t>Btp Valore Gn27 Eur</t>
         </is>
       </c>
-      <c r="C117" t="n">
-        <v>102.92</v>
-      </c>
       <c r="D117" t="n">
         <v>2</v>
       </c>
@@ -3012,9 +2718,6 @@
           <t>Btpi Tf 2,4% Mg39 Eur</t>
         </is>
       </c>
-      <c r="C118" t="n">
-        <v>102.98</v>
-      </c>
       <c r="D118" t="n">
         <v>1.2</v>
       </c>
@@ -3035,9 +2738,6 @@
           <t>Btp Tf 3,8% Ag28 Eur</t>
         </is>
       </c>
-      <c r="C119" t="n">
-        <v>104.19</v>
-      </c>
       <c r="D119" t="n">
         <v>1.9</v>
       </c>
@@ -3075,9 +2775,6 @@
           <t>Btp Tf 3,85% St26 Eur</t>
         </is>
       </c>
-      <c r="C121" t="n">
-        <v>101.89</v>
-      </c>
       <c r="D121" t="n">
         <v>1.925</v>
       </c>
@@ -3098,9 +2795,6 @@
           <t>Btp Tf 3,6% St25 Eur</t>
         </is>
       </c>
-      <c r="C122" t="n">
-        <v>100.164</v>
-      </c>
       <c r="D122" t="n">
         <v>1.8</v>
       </c>
@@ -3121,9 +2815,6 @@
           <t>Btp Tf 4,2% Mz34 Eur</t>
         </is>
       </c>
-      <c r="C123" t="n">
-        <v>106.43</v>
-      </c>
       <c r="D123" t="n">
         <v>2.1</v>
       </c>
@@ -3144,9 +2835,6 @@
           <t>Btp Fx 4% Nov30 Eur</t>
         </is>
       </c>
-      <c r="C124" t="n">
-        <v>105.77</v>
-      </c>
       <c r="D124" t="n">
         <v>2</v>
       </c>
@@ -3167,9 +2855,6 @@
           <t>Btp Valore Sc Oct28 Eur</t>
         </is>
       </c>
-      <c r="C125" t="n">
-        <v>105.36</v>
-      </c>
       <c r="D125" t="n">
         <v>1.025</v>
       </c>
@@ -3190,9 +2875,6 @@
           <t>Btp Fx 4.1% Feb29 Eur</t>
         </is>
       </c>
-      <c r="C126" t="n">
-        <v>105.46</v>
-      </c>
       <c r="E126" t="inlineStr">
         <is>
           <t>01-02-29</t>
@@ -3210,9 +2892,6 @@
           <t>Btp Fx 2.95% Feb27 Eur</t>
         </is>
       </c>
-      <c r="C127" t="n">
-        <v>101.2</v>
-      </c>
       <c r="D127" t="n">
         <v>1.475</v>
       </c>
@@ -3233,9 +2912,6 @@
           <t>Btp Fx 3.5% Feb31 Eur</t>
         </is>
       </c>
-      <c r="C128" t="n">
-        <v>103.27</v>
-      </c>
       <c r="D128" t="n">
         <v>1.75</v>
       </c>
@@ -3256,9 +2932,6 @@
           <t>Btp Fx 4.15% Oct39 Eur</t>
         </is>
       </c>
-      <c r="C129" t="n">
-        <v>102.77</v>
-      </c>
       <c r="E129" t="inlineStr">
         <is>
           <t>01-10-39</t>
@@ -3276,9 +2949,6 @@
           <t>Btp Valore Sc Mz30 Eur</t>
         </is>
       </c>
-      <c r="C130" t="n">
-        <v>103.63</v>
-      </c>
       <c r="D130" t="n">
         <v>0.8125</v>
       </c>
@@ -3299,9 +2969,6 @@
           <t>Btp Fx 3.2% Jan26 Eur</t>
         </is>
       </c>
-      <c r="C131" t="n">
-        <v>100.519</v>
-      </c>
       <c r="D131" t="n">
         <v>1.6</v>
       </c>
@@ -3322,9 +2989,6 @@
           <t>Btp Fx 3.35% Jul29 Eur</t>
         </is>
       </c>
-      <c r="C132" t="n">
-        <v>102.94</v>
-      </c>
       <c r="D132" t="n">
         <v>1.675</v>
       </c>
@@ -3345,9 +3009,6 @@
           <t>Btp Fx 3.85% Jul34 Eur</t>
         </is>
       </c>
-      <c r="C133" t="n">
-        <v>103.58</v>
-      </c>
       <c r="D133" t="n">
         <v>1.925</v>
       </c>
@@ -3368,9 +3029,6 @@
           <t>Btpi Fx May36 Eur</t>
         </is>
       </c>
-      <c r="C134" t="n">
-        <v>99.12</v>
-      </c>
       <c r="D134" t="n">
         <v>0.9</v>
       </c>
@@ -3391,9 +3049,6 @@
           <t>Btp Valore Sc Mg30 Eur</t>
         </is>
       </c>
-      <c r="C135" t="n">
-        <v>103.49</v>
-      </c>
       <c r="D135" t="n">
         <v>0.8375</v>
       </c>
@@ -3414,9 +3069,6 @@
           <t>Btp Fx 3.45% Jul31 Eur</t>
         </is>
       </c>
-      <c r="C136" t="n">
-        <v>102.79</v>
-      </c>
       <c r="D136" t="n">
         <v>1.725</v>
       </c>
@@ -3437,9 +3089,6 @@
           <t>Btp Green Fx 4.05% Oct37 Eur</t>
         </is>
       </c>
-      <c r="C137" t="n">
-        <v>103.3</v>
-      </c>
       <c r="D137" t="n">
         <v>2.025</v>
       </c>
@@ -3460,9 +3109,6 @@
           <t>Btp Fx 3.45% Jul27 Eur</t>
         </is>
       </c>
-      <c r="C138" t="n">
-        <v>102.4</v>
-      </c>
       <c r="D138" t="n">
         <v>1.725</v>
       </c>
@@ -3483,9 +3129,6 @@
           <t>Btp Fx 3.1% Aug26 Eur</t>
         </is>
       </c>
-      <c r="C139" t="n">
-        <v>101.05</v>
-      </c>
       <c r="D139" t="n">
         <v>1.55</v>
       </c>
@@ -3506,9 +3149,6 @@
           <t>Btp Fx 3.85% Feb35 Eur</t>
         </is>
       </c>
-      <c r="C140" t="n">
-        <v>103.09</v>
-      </c>
       <c r="D140" t="n">
         <v>1.925</v>
       </c>
@@ -3529,9 +3169,6 @@
           <t>Btp Fx 3% Oct29 Eur</t>
         </is>
       </c>
-      <c r="C141" t="n">
-        <v>101.59</v>
-      </c>
       <c r="D141" t="n">
         <v>1.5</v>
       </c>
@@ -3552,9 +3189,6 @@
           <t>Btp Fx 4.3% Oct54 Eur</t>
         </is>
       </c>
-      <c r="C142" t="n">
-        <v>97.36</v>
-      </c>
       <c r="D142" t="n">
         <v>2.15</v>
       </c>
@@ -3575,9 +3209,6 @@
           <t>Btp Fx 3.15% Nov31 Eur</t>
         </is>
       </c>
-      <c r="C143" t="n">
-        <v>100.9</v>
-      </c>
       <c r="D143" t="n">
         <v>1.575</v>
       </c>
@@ -3598,9 +3229,6 @@
           <t>Btp Fx 2.7% Oct27 Eur</t>
         </is>
       </c>
-      <c r="C144" t="n">
-        <v>101.04</v>
-      </c>
       <c r="D144" t="n">
         <v>1.35</v>
       </c>
@@ -3621,9 +3249,6 @@
           <t>Btp Fx 3.65% Aug35 Eur</t>
         </is>
       </c>
-      <c r="C145" t="n">
-        <v>101.05</v>
-      </c>
       <c r="D145" t="n">
         <v>1.825</v>
       </c>
@@ -3644,9 +3269,6 @@
           <t>Btp Green Fx 4.1% Apr46 Eur</t>
         </is>
       </c>
-      <c r="C146" t="n">
-        <v>99.29000000000001</v>
-      </c>
       <c r="D146" t="n">
         <v>2.05</v>
       </c>
@@ -3667,9 +3289,6 @@
           <t>Btp Fx 2.55% Feb27 Eur</t>
         </is>
       </c>
-      <c r="C147" t="n">
-        <v>100.64</v>
-      </c>
       <c r="D147" t="n">
         <v>1.275</v>
       </c>
@@ -3690,9 +3309,6 @@
           <t>Btp Piu' Sc Fb33 Eur</t>
         </is>
       </c>
-      <c r="C148" t="n">
-        <v>100.6</v>
-      </c>
       <c r="D148" t="n">
         <v>0.7125</v>
       </c>
@@ -3713,9 +3329,6 @@
           <t>Btp Fx 3.85% Oct40 Eur</t>
         </is>
       </c>
-      <c r="C149" t="n">
-        <v>98.52</v>
-      </c>
       <c r="D149" t="n">
         <v>1.925</v>
       </c>
@@ -3736,9 +3349,6 @@
           <t>Btp Fx 2.95% Jul30 Eur</t>
         </is>
       </c>
-      <c r="C150" t="n">
-        <v>100.95</v>
-      </c>
       <c r="D150" t="n">
         <v>1.475</v>
       </c>
@@ -3759,9 +3369,6 @@
           <t>Btp Fx 2.65% Jun28 Eur</t>
         </is>
       </c>
-      <c r="C151" t="n">
-        <v>100.9</v>
-      </c>
       <c r="D151" t="n">
         <v>1.325</v>
       </c>
@@ -3782,9 +3389,6 @@
           <t>Btp Fx 3.25% Jul32 Eur</t>
         </is>
       </c>
-      <c r="C152" t="n">
-        <v>100.85</v>
-      </c>
       <c r="D152" t="n">
         <v>1.625</v>
       </c>
@@ -3805,9 +3409,6 @@
           <t>Btpi Fx May56 Eur</t>
         </is>
       </c>
-      <c r="C153" t="n">
-        <v>98.16</v>
-      </c>
       <c r="D153" t="n">
         <v>1.275</v>
       </c>
@@ -3828,9 +3429,6 @@
           <t>Btp Fx 3.6% Oct35 Eur</t>
         </is>
       </c>
-      <c r="C154" t="n">
-        <v>100.44</v>
-      </c>
       <c r="D154" t="n">
         <v>1.49508</v>
       </c>
@@ -3851,9 +3449,6 @@
           <t>Btp Italia Jun32 Eur</t>
         </is>
       </c>
-      <c r="C155" t="n">
-        <v>100.29</v>
-      </c>
       <c r="D155" t="n">
         <v>0.925</v>
       </c>
@@ -3874,9 +3469,6 @@
           <t>Btp Fx 2.7% Oct30 Eur</t>
         </is>
       </c>
-      <c r="C156" t="n">
-        <v>99.56</v>
-      </c>
       <c r="D156" t="n">
         <v>0.82623</v>
       </c>
@@ -3897,9 +3489,6 @@
           <t>Btp Fx 2.1% Aug27 Eur</t>
         </is>
       </c>
-      <c r="C157" t="n">
-        <v>99.84</v>
-      </c>
       <c r="D157" t="n">
         <v>0.34807</v>
       </c>
@@ -3920,9 +3509,6 @@
           <t>Btpi Fx Aug31 Eur</t>
         </is>
       </c>
-      <c r="C158" t="n">
-        <v>99.40000000000001</v>
-      </c>
       <c r="D158" t="n">
         <v>0.55</v>
       </c>
@@ -3942,9 +3528,6 @@
         <is>
           <t>Btp Fx 2.35% Jan29 Eur</t>
         </is>
-      </c>
-      <c r="C159" t="n">
-        <v>99.75</v>
       </c>
       <c r="D159" t="n">
         <v>1.175</v>

--- a/btp_dati.xlsx
+++ b/btp_dati.xlsx
@@ -473,6 +473,9 @@
           <t>Btp-1nv26      7,25%</t>
         </is>
       </c>
+      <c r="C2" t="n">
+        <v>106.19</v>
+      </c>
       <c r="D2" t="n">
         <v>3.625</v>
       </c>
@@ -493,6 +496,9 @@
           <t>Btp-1nv27       6,5%</t>
         </is>
       </c>
+      <c r="C3" t="n">
+        <v>109.25</v>
+      </c>
       <c r="D3" t="n">
         <v>3.25</v>
       </c>
@@ -513,6 +519,9 @@
           <t>Btp-1nv29      5,25%</t>
         </is>
       </c>
+      <c r="C4" t="n">
+        <v>111</v>
+      </c>
       <c r="D4" t="n">
         <v>2.625</v>
       </c>
@@ -533,6 +542,9 @@
           <t>Btp-1mg31         6%</t>
         </is>
       </c>
+      <c r="C5" t="n">
+        <v>116.87</v>
+      </c>
       <c r="D5" t="n">
         <v>3</v>
       </c>
@@ -553,6 +565,9 @@
           <t>Btp-1fb33      5,75%</t>
         </is>
       </c>
+      <c r="C6" t="n">
+        <v>117.2</v>
+      </c>
       <c r="D6" t="n">
         <v>2.875</v>
       </c>
@@ -573,6 +588,9 @@
           <t>Btp-1ag34         5%</t>
         </is>
       </c>
+      <c r="C7" t="n">
+        <v>112.81</v>
+      </c>
       <c r="D7" t="n">
         <v>2.5</v>
       </c>
@@ -593,6 +611,9 @@
           <t>Btpi-15st35    2,35%</t>
         </is>
       </c>
+      <c r="C8" t="n">
+        <v>107.17</v>
+      </c>
       <c r="D8" t="n">
         <v>1.175</v>
       </c>
@@ -613,6 +634,9 @@
           <t>Btp-1fb37         4%</t>
         </is>
       </c>
+      <c r="C9" t="n">
+        <v>103.72</v>
+      </c>
       <c r="D9" t="n">
         <v>2</v>
       </c>
@@ -633,6 +657,9 @@
           <t>Btp-1ag39         5%</t>
         </is>
       </c>
+      <c r="C10" t="n">
+        <v>112.55</v>
+      </c>
       <c r="D10" t="n">
         <v>2.5</v>
       </c>
@@ -653,6 +680,9 @@
           <t>Btp-1st40 5%</t>
         </is>
       </c>
+      <c r="C11" t="n">
+        <v>112.37</v>
+      </c>
       <c r="D11" t="n">
         <v>2.5</v>
       </c>
@@ -673,6 +703,9 @@
           <t>Btpi-15st41 2,55%</t>
         </is>
       </c>
+      <c r="C12" t="n">
+        <v>106.15</v>
+      </c>
       <c r="D12" t="n">
         <v>1.275</v>
       </c>
@@ -693,6 +726,9 @@
           <t>Btp-1mz26 4,5%</t>
         </is>
       </c>
+      <c r="C13" t="n">
+        <v>101.271</v>
+      </c>
       <c r="D13" t="n">
         <v>2.25</v>
       </c>
@@ -733,6 +769,9 @@
           <t>Btp Coupon Strip Zc Nv26 Eur</t>
         </is>
       </c>
+      <c r="C15" t="n">
+        <v>97.81</v>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>01-11-26</t>
@@ -750,6 +789,9 @@
           <t>Btp Coupon Strip Zc Nv27 Eur</t>
         </is>
       </c>
+      <c r="C16" t="n">
+        <v>95.56</v>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>01-11-27</t>
@@ -767,6 +809,9 @@
           <t>Btp Coupon Strip Zc Nv29 Eur</t>
         </is>
       </c>
+      <c r="C17" t="n">
+        <v>90.41</v>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
           <t>01-11-29</t>
@@ -784,6 +829,9 @@
           <t>Btp Coupon Strip Zc Mg31 Eur</t>
         </is>
       </c>
+      <c r="C18" t="n">
+        <v>85.2</v>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
           <t>01-05-31</t>
@@ -852,6 +900,9 @@
           <t>Btp Tf 4,75% St28 Eur</t>
         </is>
       </c>
+      <c r="C22" t="n">
+        <v>107.07</v>
+      </c>
       <c r="D22" t="n">
         <v>2.375</v>
       </c>
@@ -872,6 +923,9 @@
           <t>Btp Tf 4,75% St44 Eur</t>
         </is>
       </c>
+      <c r="C23" t="n">
+        <v>108.62</v>
+      </c>
       <c r="D23" t="n">
         <v>2.375</v>
       </c>
@@ -892,6 +946,9 @@
           <t>Btp Coupon Strip Zc St28 Eur</t>
         </is>
       </c>
+      <c r="C24" t="n">
+        <v>93.42</v>
+      </c>
       <c r="E24" t="inlineStr">
         <is>
           <t>01-09-28</t>
@@ -909,6 +966,9 @@
           <t>Btp Coupon Strip Zc Mz30 Eur</t>
         </is>
       </c>
+      <c r="C25" t="n">
+        <v>89.26000000000001</v>
+      </c>
       <c r="E25" t="inlineStr">
         <is>
           <t>01-03-30</t>
@@ -1011,6 +1071,9 @@
           <t>Btp Tf 3,50% Mz30 Eur</t>
         </is>
       </c>
+      <c r="C31" t="n">
+        <v>104.05</v>
+      </c>
       <c r="D31" t="n">
         <v>1.75</v>
       </c>
@@ -1031,6 +1094,9 @@
           <t>Btp Tf 3,25% St46 Eur</t>
         </is>
       </c>
+      <c r="C32" t="n">
+        <v>87.2</v>
+      </c>
       <c r="D32" t="n">
         <v>1.625</v>
       </c>
@@ -1051,6 +1117,9 @@
           <t>Btp Tf 1,65% Mz32 Eur</t>
         </is>
       </c>
+      <c r="C33" t="n">
+        <v>92.29000000000001</v>
+      </c>
       <c r="D33" t="n">
         <v>0.825</v>
       </c>
@@ -1071,6 +1140,9 @@
           <t>Btp Tf 2,00% Dc25 Eur</t>
         </is>
       </c>
+      <c r="C34" t="n">
+        <v>100.01</v>
+      </c>
       <c r="D34" t="n">
         <v>1</v>
       </c>
@@ -1091,6 +1163,9 @@
           <t>Btpi Tf 1,25% St32 Eur</t>
         </is>
       </c>
+      <c r="C35" t="n">
+        <v>100.03</v>
+      </c>
       <c r="D35" t="n">
         <v>0.625</v>
       </c>
@@ -1111,6 +1186,9 @@
           <t>Btp Tf 2,7% Mz47 Eur</t>
         </is>
       </c>
+      <c r="C36" t="n">
+        <v>79.23999999999999</v>
+      </c>
       <c r="D36" t="n">
         <v>1.35</v>
       </c>
@@ -1131,6 +1209,9 @@
           <t>Btp Tf 1,60% Gn26 Eur</t>
         </is>
       </c>
+      <c r="C37" t="n">
+        <v>99.736</v>
+      </c>
       <c r="D37" t="n">
         <v>0.8</v>
       </c>
@@ -1151,6 +1232,9 @@
           <t>Btp Tf 2,25% St36 Eur</t>
         </is>
       </c>
+      <c r="C38" t="n">
+        <v>88.06</v>
+      </c>
       <c r="D38" t="n">
         <v>1.125</v>
       </c>
@@ -1171,6 +1255,9 @@
           <t>Btp Tf 1.25% Dc26 Eur</t>
         </is>
       </c>
+      <c r="C39" t="n">
+        <v>99.14</v>
+      </c>
       <c r="D39" t="n">
         <v>0.625</v>
       </c>
@@ -1191,6 +1278,9 @@
           <t>Btp Tf 2,8% Mz67 Eur</t>
         </is>
       </c>
+      <c r="C40" t="n">
+        <v>69.83</v>
+      </c>
       <c r="D40" t="n">
         <v>1.4</v>
       </c>
@@ -1211,6 +1301,9 @@
           <t>Btp Tf 2,45% St33 Eur</t>
         </is>
       </c>
+      <c r="C41" t="n">
+        <v>94.81999999999999</v>
+      </c>
       <c r="D41" t="n">
         <v>1.225</v>
       </c>
@@ -1231,6 +1324,9 @@
           <t>Btp Tf 2,20% Gn27 Eur</t>
         </is>
       </c>
+      <c r="C42" t="n">
+        <v>100.27</v>
+      </c>
       <c r="D42" t="n">
         <v>1.1</v>
       </c>
@@ -1251,6 +1347,9 @@
           <t>Btpi Tf 1,30% Mg28 Eur</t>
         </is>
       </c>
+      <c r="C43" t="n">
+        <v>101.19</v>
+      </c>
       <c r="D43" t="n">
         <v>0.65</v>
       </c>
@@ -1271,6 +1370,9 @@
           <t>Btp Tf 3,45% Mz48 Eur</t>
         </is>
       </c>
+      <c r="C44" t="n">
+        <v>89.09999999999999</v>
+      </c>
       <c r="D44" t="n">
         <v>1.725</v>
       </c>
@@ -1291,6 +1393,9 @@
           <t>Btp Tf 2,05% Ag27 Eur</t>
         </is>
       </c>
+      <c r="C45" t="n">
+        <v>99.95</v>
+      </c>
       <c r="D45" t="n">
         <v>1.025</v>
       </c>
@@ -1311,6 +1416,9 @@
           <t>Btp Tf 2,95% St38 Eur</t>
         </is>
       </c>
+      <c r="C46" t="n">
+        <v>91.7</v>
+      </c>
       <c r="D46" t="n">
         <v>1.475</v>
       </c>
@@ -1331,6 +1439,9 @@
           <t>Btp Tf 2,00% Fb28 Eur</t>
         </is>
       </c>
+      <c r="C47" t="n">
+        <v>99.56</v>
+      </c>
       <c r="D47" t="n">
         <v>1</v>
       </c>
@@ -1351,6 +1462,9 @@
           <t>Btp Italia Mg26 Eur</t>
         </is>
       </c>
+      <c r="C48" t="n">
+        <v>99.836</v>
+      </c>
       <c r="D48" t="n">
         <v>0.275</v>
       </c>
@@ -1371,6 +1485,9 @@
           <t>Btp Tf 2,80% Dc28 Eur</t>
         </is>
       </c>
+      <c r="C49" t="n">
+        <v>101.55</v>
+      </c>
       <c r="D49" t="n">
         <v>1.4</v>
       </c>
@@ -1391,6 +1508,9 @@
           <t>Btp Tf 2.50% Nv25 Eur</t>
         </is>
       </c>
+      <c r="C50" t="n">
+        <v>100.099</v>
+      </c>
       <c r="D50" t="n">
         <v>1.25</v>
       </c>
@@ -1411,6 +1531,9 @@
           <t>Btp Tf 3,35% Mz35 Eur</t>
         </is>
       </c>
+      <c r="C51" t="n">
+        <v>99.7</v>
+      </c>
       <c r="D51" t="n">
         <v>1.675</v>
       </c>
@@ -1431,6 +1554,9 @@
           <t>Btp Tf 3,85% St49 Eur</t>
         </is>
       </c>
+      <c r="C52" t="n">
+        <v>94.25</v>
+      </c>
       <c r="D52" t="n">
         <v>1.925</v>
       </c>
@@ -1451,6 +1577,9 @@
           <t>Btp Tf 3,00% Ag29 Eur</t>
         </is>
       </c>
+      <c r="C53" t="n">
+        <v>102.06</v>
+      </c>
       <c r="D53" t="n">
         <v>1.5</v>
       </c>
@@ -1471,6 +1600,9 @@
           <t>Btp Tf 2,10% Lg26 Eur</t>
         </is>
       </c>
+      <c r="C54" t="n">
+        <v>100.1</v>
+      </c>
       <c r="D54" t="n">
         <v>1.05</v>
       </c>
@@ -1491,6 +1623,9 @@
           <t>Btp Tf 3,1% Mz40 Eur</t>
         </is>
       </c>
+      <c r="C55" t="n">
+        <v>91.33</v>
+      </c>
       <c r="D55" t="n">
         <v>1.55</v>
       </c>
@@ -1511,6 +1646,9 @@
           <t>Btp Tf 1,35% Ap30 Eur</t>
         </is>
       </c>
+      <c r="C56" t="n">
+        <v>94.66</v>
+      </c>
       <c r="D56" t="n">
         <v>0.675</v>
       </c>
@@ -1531,6 +1669,9 @@
           <t>Btpi Tf 0,4% Mg30 Eur</t>
         </is>
       </c>
+      <c r="C57" t="n">
+        <v>97.23</v>
+      </c>
       <c r="D57" t="n">
         <v>0.2</v>
       </c>
@@ -1551,6 +1692,9 @@
           <t>Btp Italia Ot27 Eur</t>
         </is>
       </c>
+      <c r="C58" t="n">
+        <v>99.81</v>
+      </c>
       <c r="D58" t="n">
         <v>0.325</v>
       </c>
@@ -1571,6 +1715,9 @@
           <t>Btp Tf 0,85% Ge27 Eur</t>
         </is>
       </c>
+      <c r="C59" t="n">
+        <v>98.45</v>
+      </c>
       <c r="D59" t="n">
         <v>0.425</v>
       </c>
@@ -1591,6 +1738,9 @@
           <t>Btp Tf 2,45% St50 Eur</t>
         </is>
       </c>
+      <c r="C60" t="n">
+        <v>72.22</v>
+      </c>
       <c r="D60" t="n">
         <v>1.225</v>
       </c>
@@ -1611,6 +1761,9 @@
           <t>Btp Tf 1,45% Mz36 Eur</t>
         </is>
       </c>
+      <c r="C61" t="n">
+        <v>81.69</v>
+      </c>
       <c r="D61" t="n">
         <v>0.725</v>
       </c>
@@ -1631,6 +1784,9 @@
           <t>Btp Tf 0,95% Ag30 Eur</t>
         </is>
       </c>
+      <c r="C62" t="n">
+        <v>92.09</v>
+      </c>
       <c r="D62" t="n">
         <v>0.475</v>
       </c>
@@ -1651,6 +1807,9 @@
           <t>Btp Tf 1,65% Dc30 Eur</t>
         </is>
       </c>
+      <c r="C63" t="n">
+        <v>94.66</v>
+      </c>
       <c r="D63" t="n">
         <v>0.825</v>
       </c>
@@ -1671,6 +1830,9 @@
           <t>Btp Futura Lg30 Eur</t>
         </is>
       </c>
+      <c r="C64" t="n">
+        <v>93.94</v>
+      </c>
       <c r="D64" t="n">
         <v>0.65</v>
       </c>
@@ -1691,6 +1853,9 @@
           <t>Btpi Tf 0,65% Mg26 Eur</t>
         </is>
       </c>
+      <c r="C65" t="n">
+        <v>99.59399999999999</v>
+      </c>
       <c r="D65" t="n">
         <v>0.325</v>
       </c>
@@ -1711,6 +1876,9 @@
           <t>Btp Tf 0,95% St27 Eur</t>
         </is>
       </c>
+      <c r="C66" t="n">
+        <v>97.72</v>
+      </c>
       <c r="D66" t="n">
         <v>0.475</v>
       </c>
@@ -1731,6 +1899,9 @@
           <t>Btp Tf 0,50% Fb26 Eur</t>
         </is>
       </c>
+      <c r="C67" t="n">
+        <v>99.364</v>
+      </c>
       <c r="D67" t="n">
         <v>0.25</v>
       </c>
@@ -1751,6 +1922,9 @@
           <t>Btp Tf 1,8% Mz41 Eur</t>
         </is>
       </c>
+      <c r="C68" t="n">
+        <v>74.98</v>
+      </c>
       <c r="D68" t="n">
         <v>0.9</v>
       </c>
@@ -1771,6 +1945,9 @@
           <t>Btp Tf 0,90% Ap31 Eur</t>
         </is>
       </c>
+      <c r="C69" t="n">
+        <v>90.17</v>
+      </c>
       <c r="D69" t="n">
         <v>0.45</v>
       </c>
@@ -1791,6 +1968,9 @@
           <t>Btp Tf 1,7% St51 Eur</t>
         </is>
       </c>
+      <c r="C70" t="n">
+        <v>60.43</v>
+      </c>
       <c r="D70" t="n">
         <v>0.85</v>
       </c>
@@ -1811,6 +1991,9 @@
           <t>Btp Futura Nv28 Eur</t>
         </is>
       </c>
+      <c r="C71" t="n">
+        <v>95.23</v>
+      </c>
       <c r="D71" t="n">
         <v>0.3</v>
       </c>
@@ -1831,6 +2014,9 @@
           <t>Btp Tf 0,95% Mz37 Eur</t>
         </is>
       </c>
+      <c r="C72" t="n">
+        <v>74.78</v>
+      </c>
       <c r="D72" t="n">
         <v>0.475</v>
       </c>
@@ -1851,6 +2037,9 @@
           <t>Btp Tf 0,25% Mz28 Eur</t>
         </is>
       </c>
+      <c r="C73" t="n">
+        <v>95.20999999999999</v>
+      </c>
       <c r="D73" t="n">
         <v>0.125</v>
       </c>
@@ -1871,6 +2060,9 @@
           <t>Btp Tf 0,6% Ag31 Eur</t>
         </is>
       </c>
+      <c r="C74" t="n">
+        <v>87.73999999999999</v>
+      </c>
       <c r="D74" t="n">
         <v>0.3</v>
       </c>
@@ -1891,6 +2083,9 @@
           <t>Btpi Tf 0,15% Mg51 Eur</t>
         </is>
       </c>
+      <c r="C75" t="n">
+        <v>58.73</v>
+      </c>
       <c r="D75" t="n">
         <v>0.075</v>
       </c>
@@ -1911,6 +2106,9 @@
           <t>Btp Tf 0% Ap26 Eur</t>
         </is>
       </c>
+      <c r="C76" t="n">
+        <v>98.84099999999999</v>
+      </c>
       <c r="E76" t="inlineStr">
         <is>
           <t>01-04-26</t>
@@ -1928,6 +2126,9 @@
           <t>Btpgreen 1,5%Ap45eur</t>
         </is>
       </c>
+      <c r="C77" t="n">
+        <v>65.26000000000001</v>
+      </c>
       <c r="D77" t="n">
         <v>0.75</v>
       </c>
@@ -1948,6 +2149,9 @@
           <t>Btp Tf 2,15% Mz72 Eur</t>
         </is>
       </c>
+      <c r="C78" t="n">
+        <v>57.49</v>
+      </c>
       <c r="D78" t="n">
         <v>1.075</v>
       </c>
@@ -1968,6 +2172,9 @@
           <t>Btp Futura Ap37 Eur</t>
         </is>
       </c>
+      <c r="C79" t="n">
+        <v>79.09999999999999</v>
+      </c>
       <c r="D79" t="n">
         <v>0.6</v>
       </c>
@@ -1988,6 +2195,9 @@
           <t>Btp Tf 0,5% Lg28 Eur</t>
         </is>
       </c>
+      <c r="C80" t="n">
+        <v>95.13</v>
+      </c>
       <c r="D80" t="n">
         <v>0.25</v>
       </c>
@@ -2008,6 +2218,9 @@
           <t>Btp Tf 0,95% Dc31 Eur</t>
         </is>
       </c>
+      <c r="C81" t="n">
+        <v>88.78</v>
+      </c>
       <c r="D81" t="n">
         <v>0.475</v>
       </c>
@@ -2028,6 +2241,9 @@
           <t>Btp Tf 0% Ag26 Eur</t>
         </is>
       </c>
+      <c r="C82" t="n">
+        <v>98.29900000000001</v>
+      </c>
       <c r="E82" t="inlineStr">
         <is>
           <t>01-08-26</t>
@@ -2045,6 +2261,9 @@
           <t>Btp Tf 0,95% Gn32 Eur</t>
         </is>
       </c>
+      <c r="C83" t="n">
+        <v>87.54000000000001</v>
+      </c>
       <c r="D83" t="n">
         <v>0.475</v>
       </c>
@@ -2065,6 +2284,9 @@
           <t>Btp Futura Nv33 Eur</t>
         </is>
       </c>
+      <c r="C84" t="n">
+        <v>87.3</v>
+      </c>
       <c r="D84" t="n">
         <v>0.375</v>
       </c>
@@ -2085,6 +2307,9 @@
           <t>Btp Tf 0,45% Fb29 Eur</t>
         </is>
       </c>
+      <c r="C85" t="n">
+        <v>93.62</v>
+      </c>
       <c r="D85" t="n">
         <v>0.225</v>
       </c>
@@ -2105,6 +2330,9 @@
           <t>Btp Tf 2,15% St52 Eur</t>
         </is>
       </c>
+      <c r="C86" t="n">
+        <v>66.05</v>
+      </c>
       <c r="D86" t="n">
         <v>1.075</v>
       </c>
@@ -2125,6 +2353,9 @@
           <t>Btpi Tf 0,1% Mg33 Eur</t>
         </is>
       </c>
+      <c r="C87" t="n">
+        <v>90.02</v>
+      </c>
       <c r="D87" t="n">
         <v>0.05</v>
       </c>
@@ -2145,6 +2376,9 @@
           <t>Btp Tf 1,1% Ap27 Eur</t>
         </is>
       </c>
+      <c r="C88" t="n">
+        <v>98.53</v>
+      </c>
       <c r="D88" t="n">
         <v>0.55</v>
       </c>
@@ -2165,6 +2399,9 @@
           <t>Btp Tf 2,5% Dc32 Eur</t>
         </is>
       </c>
+      <c r="C89" t="n">
+        <v>96.19</v>
+      </c>
       <c r="D89" t="n">
         <v>1.25</v>
       </c>
@@ -2185,6 +2422,9 @@
           <t>Btp Tf 2,80% Gn29 Eur</t>
         </is>
       </c>
+      <c r="C90" t="n">
+        <v>101.19</v>
+      </c>
       <c r="D90" t="n">
         <v>1.4</v>
       </c>
@@ -2205,6 +2445,9 @@
           <t>Btp Tf 3,25% Mz38 Eur</t>
         </is>
       </c>
+      <c r="C91" t="n">
+        <v>95.06999999999999</v>
+      </c>
       <c r="D91" t="n">
         <v>1.625</v>
       </c>
@@ -2225,6 +2468,9 @@
           <t>Btp Italia Gn30 Eur</t>
         </is>
       </c>
+      <c r="C92" t="n">
+        <v>100.86</v>
+      </c>
       <c r="D92" t="n">
         <v>0.8</v>
       </c>
@@ -2381,6 +2627,9 @@
           <t>Btp Tf 2,65% Dc27 Eur</t>
         </is>
       </c>
+      <c r="C101" t="n">
+        <v>101.05</v>
+      </c>
       <c r="D101" t="n">
         <v>1.325</v>
       </c>
@@ -2401,6 +2650,9 @@
           <t>Btpgreen 4%Ap35eur</t>
         </is>
       </c>
+      <c r="C102" t="n">
+        <v>105.27</v>
+      </c>
       <c r="D102" t="n">
         <v>2</v>
       </c>
@@ -2421,6 +2673,9 @@
           <t>Btp Tf 3,5% Ge26 Eur</t>
         </is>
       </c>
+      <c r="C103" t="n">
+        <v>100.549</v>
+      </c>
       <c r="D103" t="n">
         <v>1.75</v>
       </c>
@@ -2441,6 +2696,9 @@
           <t>Btp Italia Nv28 Eur</t>
         </is>
       </c>
+      <c r="C104" t="n">
+        <v>101.51</v>
+      </c>
       <c r="D104" t="n">
         <v>0.8</v>
       </c>
@@ -2461,6 +2719,9 @@
           <t>Btp Tf 4,40% Mg33 Eur</t>
         </is>
       </c>
+      <c r="C105" t="n">
+        <v>108.37</v>
+      </c>
       <c r="D105" t="n">
         <v>2.2</v>
       </c>
@@ -2481,6 +2742,9 @@
           <t>Btp Tf 3,85% Dc29 Eur</t>
         </is>
       </c>
+      <c r="C106" t="n">
+        <v>105.11</v>
+      </c>
       <c r="D106" t="n">
         <v>1.925</v>
       </c>
@@ -2501,6 +2765,9 @@
           <t>Btp Tf 3,4% Ap28 Eur</t>
         </is>
       </c>
+      <c r="C107" t="n">
+        <v>102.89</v>
+      </c>
       <c r="D107" t="n">
         <v>1.7</v>
       </c>
@@ -2538,6 +2805,9 @@
           <t>Btp Tf 4,45% St43 Eur</t>
         </is>
       </c>
+      <c r="C109" t="n">
+        <v>104.33</v>
+      </c>
       <c r="D109" t="n">
         <v>2.225</v>
       </c>
@@ -2558,6 +2828,9 @@
           <t>Btp Italia Mz28 Eur</t>
         </is>
       </c>
+      <c r="C110" t="n">
+        <v>102.43</v>
+      </c>
       <c r="D110" t="n">
         <v>1</v>
       </c>
@@ -2578,6 +2851,9 @@
           <t>Btp Tf 4,5% Ot53 Eur</t>
         </is>
       </c>
+      <c r="C111" t="n">
+        <v>101.48</v>
+      </c>
       <c r="D111" t="n">
         <v>2.25</v>
       </c>
@@ -2598,6 +2874,9 @@
           <t>Btp Tf 3,80% Ap26 Eur</t>
         </is>
       </c>
+      <c r="C112" t="n">
+        <v>101.126</v>
+      </c>
       <c r="D112" t="n">
         <v>1.9</v>
       </c>
@@ -2618,6 +2897,9 @@
           <t>Btpgreen 4%Ot31eur</t>
         </is>
       </c>
+      <c r="C113" t="n">
+        <v>106.27</v>
+      </c>
       <c r="D113" t="n">
         <v>2</v>
       </c>
@@ -2638,6 +2920,9 @@
           <t>Btp Tf 3,7% Gn30 Eur</t>
         </is>
       </c>
+      <c r="C114" t="n">
+        <v>104.53</v>
+      </c>
       <c r="D114" t="n">
         <v>1.85</v>
       </c>
@@ -2658,6 +2943,9 @@
           <t>Btpi Tf 1.5% Mg29 Eur</t>
         </is>
       </c>
+      <c r="C115" t="n">
+        <v>101.9</v>
+      </c>
       <c r="D115" t="n">
         <v>0.75</v>
       </c>
@@ -2678,6 +2966,9 @@
           <t>Btp Tf 4,35% Nv33 Eur</t>
         </is>
       </c>
+      <c r="C116" t="n">
+        <v>107.84</v>
+      </c>
       <c r="D116" t="n">
         <v>2.175</v>
       </c>
@@ -2698,6 +2989,9 @@
           <t>Btp Valore Gn27 Eur</t>
         </is>
       </c>
+      <c r="C117" t="n">
+        <v>102.95</v>
+      </c>
       <c r="D117" t="n">
         <v>2</v>
       </c>
@@ -2718,6 +3012,9 @@
           <t>Btpi Tf 2,4% Mg39 Eur</t>
         </is>
       </c>
+      <c r="C118" t="n">
+        <v>103.1</v>
+      </c>
       <c r="D118" t="n">
         <v>1.2</v>
       </c>
@@ -2738,6 +3035,9 @@
           <t>Btp Tf 3,8% Ag28 Eur</t>
         </is>
       </c>
+      <c r="C119" t="n">
+        <v>104.19</v>
+      </c>
       <c r="D119" t="n">
         <v>1.9</v>
       </c>
@@ -2775,6 +3075,9 @@
           <t>Btp Tf 3,85% St26 Eur</t>
         </is>
       </c>
+      <c r="C121" t="n">
+        <v>101.86</v>
+      </c>
       <c r="D121" t="n">
         <v>1.925</v>
       </c>
@@ -2795,6 +3098,9 @@
           <t>Btp Tf 3,6% St25 Eur</t>
         </is>
       </c>
+      <c r="C122" t="n">
+        <v>100.144</v>
+      </c>
       <c r="D122" t="n">
         <v>1.8</v>
       </c>
@@ -2815,6 +3121,9 @@
           <t>Btp Tf 4,2% Mz34 Eur</t>
         </is>
       </c>
+      <c r="C123" t="n">
+        <v>106.64</v>
+      </c>
       <c r="D123" t="n">
         <v>2.1</v>
       </c>
@@ -2835,6 +3144,9 @@
           <t>Btp Fx 4% Nov30 Eur</t>
         </is>
       </c>
+      <c r="C124" t="n">
+        <v>105.92</v>
+      </c>
       <c r="D124" t="n">
         <v>2</v>
       </c>
@@ -2855,6 +3167,9 @@
           <t>Btp Valore Sc Oct28 Eur</t>
         </is>
       </c>
+      <c r="C125" t="n">
+        <v>105.45</v>
+      </c>
       <c r="D125" t="n">
         <v>1.025</v>
       </c>
@@ -2875,6 +3190,9 @@
           <t>Btp Fx 4.1% Feb29 Eur</t>
         </is>
       </c>
+      <c r="C126" t="n">
+        <v>105.47</v>
+      </c>
       <c r="E126" t="inlineStr">
         <is>
           <t>01-02-29</t>
@@ -2892,6 +3210,9 @@
           <t>Btp Fx 2.95% Feb27 Eur</t>
         </is>
       </c>
+      <c r="C127" t="n">
+        <v>101.17</v>
+      </c>
       <c r="D127" t="n">
         <v>1.475</v>
       </c>
@@ -2912,6 +3233,9 @@
           <t>Btp Fx 3.5% Feb31 Eur</t>
         </is>
       </c>
+      <c r="C128" t="n">
+        <v>103.34</v>
+      </c>
       <c r="D128" t="n">
         <v>1.75</v>
       </c>
@@ -2932,6 +3256,9 @@
           <t>Btp Fx 4.15% Oct39 Eur</t>
         </is>
       </c>
+      <c r="C129" t="n">
+        <v>102.95</v>
+      </c>
       <c r="E129" t="inlineStr">
         <is>
           <t>01-10-39</t>
@@ -2949,6 +3276,9 @@
           <t>Btp Valore Sc Mz30 Eur</t>
         </is>
       </c>
+      <c r="C130" t="n">
+        <v>103.78</v>
+      </c>
       <c r="D130" t="n">
         <v>0.8125</v>
       </c>
@@ -2969,6 +3299,9 @@
           <t>Btp Fx 3.2% Jan26 Eur</t>
         </is>
       </c>
+      <c r="C131" t="n">
+        <v>100.491</v>
+      </c>
       <c r="D131" t="n">
         <v>1.6</v>
       </c>
@@ -2989,6 +3322,9 @@
           <t>Btp Fx 3.35% Jul29 Eur</t>
         </is>
       </c>
+      <c r="C132" t="n">
+        <v>103.01</v>
+      </c>
       <c r="D132" t="n">
         <v>1.675</v>
       </c>
@@ -3009,6 +3345,9 @@
           <t>Btp Fx 3.85% Jul34 Eur</t>
         </is>
       </c>
+      <c r="C133" t="n">
+        <v>103.81</v>
+      </c>
       <c r="D133" t="n">
         <v>1.925</v>
       </c>
@@ -3029,6 +3368,9 @@
           <t>Btpi Fx May36 Eur</t>
         </is>
       </c>
+      <c r="C134" t="n">
+        <v>98.98</v>
+      </c>
       <c r="D134" t="n">
         <v>0.9</v>
       </c>
@@ -3049,6 +3391,9 @@
           <t>Btp Valore Sc Mg30 Eur</t>
         </is>
       </c>
+      <c r="C135" t="n">
+        <v>103.7</v>
+      </c>
       <c r="D135" t="n">
         <v>0.8375</v>
       </c>
@@ -3069,6 +3414,9 @@
           <t>Btp Fx 3.45% Jul31 Eur</t>
         </is>
       </c>
+      <c r="C136" t="n">
+        <v>102.91</v>
+      </c>
       <c r="D136" t="n">
         <v>1.725</v>
       </c>
@@ -3089,6 +3437,9 @@
           <t>Btp Green Fx 4.05% Oct37 Eur</t>
         </is>
       </c>
+      <c r="C137" t="n">
+        <v>103.44</v>
+      </c>
       <c r="D137" t="n">
         <v>2.025</v>
       </c>
@@ -3109,6 +3460,9 @@
           <t>Btp Fx 3.45% Jul27 Eur</t>
         </is>
       </c>
+      <c r="C138" t="n">
+        <v>102.31</v>
+      </c>
       <c r="D138" t="n">
         <v>1.725</v>
       </c>
@@ -3129,6 +3483,9 @@
           <t>Btp Fx 3.1% Aug26 Eur</t>
         </is>
       </c>
+      <c r="C139" t="n">
+        <v>101.06</v>
+      </c>
       <c r="D139" t="n">
         <v>1.55</v>
       </c>
@@ -3149,6 +3506,9 @@
           <t>Btp Fx 3.85% Feb35 Eur</t>
         </is>
       </c>
+      <c r="C140" t="n">
+        <v>103.36</v>
+      </c>
       <c r="D140" t="n">
         <v>1.925</v>
       </c>
@@ -3169,6 +3529,9 @@
           <t>Btp Fx 3% Oct29 Eur</t>
         </is>
       </c>
+      <c r="C141" t="n">
+        <v>101.68</v>
+      </c>
       <c r="D141" t="n">
         <v>1.5</v>
       </c>
@@ -3189,6 +3552,9 @@
           <t>Btp Fx 4.3% Oct54 Eur</t>
         </is>
       </c>
+      <c r="C142" t="n">
+        <v>97.62</v>
+      </c>
       <c r="D142" t="n">
         <v>2.15</v>
       </c>
@@ -3209,6 +3575,9 @@
           <t>Btp Fx 3.15% Nov31 Eur</t>
         </is>
       </c>
+      <c r="C143" t="n">
+        <v>101.04</v>
+      </c>
       <c r="D143" t="n">
         <v>1.575</v>
       </c>
@@ -3229,6 +3598,9 @@
           <t>Btp Fx 2.7% Oct27 Eur</t>
         </is>
       </c>
+      <c r="C144" t="n">
+        <v>100.11</v>
+      </c>
       <c r="D144" t="n">
         <v>1.35</v>
       </c>
@@ -3249,6 +3621,9 @@
           <t>Btp Fx 3.65% Aug35 Eur</t>
         </is>
       </c>
+      <c r="C145" t="n">
+        <v>101.29</v>
+      </c>
       <c r="D145" t="n">
         <v>1.825</v>
       </c>
@@ -3269,6 +3644,9 @@
           <t>Btp Green Fx 4.1% Apr46 Eur</t>
         </is>
       </c>
+      <c r="C146" t="n">
+        <v>99.39</v>
+      </c>
       <c r="D146" t="n">
         <v>2.05</v>
       </c>
@@ -3289,6 +3667,9 @@
           <t>Btp Fx 2.55% Feb27 Eur</t>
         </is>
       </c>
+      <c r="C147" t="n">
+        <v>100.59</v>
+      </c>
       <c r="D147" t="n">
         <v>1.275</v>
       </c>
@@ -3309,6 +3690,9 @@
           <t>Btp Piu' Sc Fb33 Eur</t>
         </is>
       </c>
+      <c r="C148" t="n">
+        <v>100.77</v>
+      </c>
       <c r="D148" t="n">
         <v>0.7125</v>
       </c>
@@ -3329,6 +3713,9 @@
           <t>Btp Fx 3.85% Oct40 Eur</t>
         </is>
       </c>
+      <c r="C149" t="n">
+        <v>98.66</v>
+      </c>
       <c r="D149" t="n">
         <v>1.925</v>
       </c>
@@ -3349,6 +3736,9 @@
           <t>Btp Fx 2.95% Jul30 Eur</t>
         </is>
       </c>
+      <c r="C150" t="n">
+        <v>100.91</v>
+      </c>
       <c r="D150" t="n">
         <v>1.475</v>
       </c>
@@ -3369,6 +3759,9 @@
           <t>Btp Fx 2.65% Jun28 Eur</t>
         </is>
       </c>
+      <c r="C151" t="n">
+        <v>100.83</v>
+      </c>
       <c r="D151" t="n">
         <v>1.325</v>
       </c>
@@ -3389,6 +3782,9 @@
           <t>Btp Fx 3.25% Jul32 Eur</t>
         </is>
       </c>
+      <c r="C152" t="n">
+        <v>100.94</v>
+      </c>
       <c r="D152" t="n">
         <v>1.625</v>
       </c>
@@ -3409,6 +3805,9 @@
           <t>Btpi Fx May56 Eur</t>
         </is>
       </c>
+      <c r="C153" t="n">
+        <v>98.38</v>
+      </c>
       <c r="D153" t="n">
         <v>1.275</v>
       </c>
@@ -3429,6 +3828,9 @@
           <t>Btp Fx 3.6% Oct35 Eur</t>
         </is>
       </c>
+      <c r="C154" t="n">
+        <v>100.64</v>
+      </c>
       <c r="D154" t="n">
         <v>1.49508</v>
       </c>
@@ -3449,6 +3851,9 @@
           <t>Btp Italia Jun32 Eur</t>
         </is>
       </c>
+      <c r="C155" t="n">
+        <v>100.47</v>
+      </c>
       <c r="D155" t="n">
         <v>0.925</v>
       </c>
@@ -3469,6 +3874,9 @@
           <t>Btp Fx 2.7% Oct30 Eur</t>
         </is>
       </c>
+      <c r="C156" t="n">
+        <v>99.69</v>
+      </c>
       <c r="D156" t="n">
         <v>0.82623</v>
       </c>
@@ -3489,6 +3897,9 @@
           <t>Btp Fx 2.1% Aug27 Eur</t>
         </is>
       </c>
+      <c r="C157" t="n">
+        <v>99.94</v>
+      </c>
       <c r="D157" t="n">
         <v>0.34807</v>
       </c>
@@ -3509,6 +3920,9 @@
           <t>Btpi Fx Aug31 Eur</t>
         </is>
       </c>
+      <c r="C158" t="n">
+        <v>99.38</v>
+      </c>
       <c r="D158" t="n">
         <v>0.55</v>
       </c>
@@ -3528,6 +3942,9 @@
         <is>
           <t>Btp Fx 2.35% Jan29 Eur</t>
         </is>
+      </c>
+      <c r="C159" t="n">
+        <v>99.75</v>
       </c>
       <c r="D159" t="n">
         <v>1.175</v>

--- a/btp_dati.xlsx
+++ b/btp_dati.xlsx
@@ -474,7 +474,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>106.19</v>
+        <v>106.1</v>
       </c>
       <c r="D2" t="n">
         <v>3.625</v>
@@ -497,7 +497,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>109.25</v>
+        <v>109.11</v>
       </c>
       <c r="D3" t="n">
         <v>3.25</v>
@@ -520,7 +520,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>111</v>
+        <v>110.61</v>
       </c>
       <c r="D4" t="n">
         <v>2.625</v>
@@ -543,7 +543,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>116.87</v>
+        <v>116.49</v>
       </c>
       <c r="D5" t="n">
         <v>3</v>
@@ -566,7 +566,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>117.2</v>
+        <v>116.8</v>
       </c>
       <c r="D6" t="n">
         <v>2.875</v>
@@ -589,7 +589,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>112.81</v>
+        <v>112.38</v>
       </c>
       <c r="D7" t="n">
         <v>2.5</v>
@@ -612,7 +612,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>107.17</v>
+        <v>106.79</v>
       </c>
       <c r="D8" t="n">
         <v>1.175</v>
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>103.72</v>
+        <v>103.19</v>
       </c>
       <c r="D9" t="n">
         <v>2</v>
@@ -658,7 +658,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>112.55</v>
+        <v>111.95</v>
       </c>
       <c r="D10" t="n">
         <v>2.5</v>
@@ -681,7 +681,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>112.37</v>
+        <v>111.73</v>
       </c>
       <c r="D11" t="n">
         <v>2.5</v>
@@ -704,7 +704,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>106.15</v>
+        <v>105.4</v>
       </c>
       <c r="D12" t="n">
         <v>1.275</v>
@@ -727,7 +727,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>101.271</v>
+        <v>101.253</v>
       </c>
       <c r="D13" t="n">
         <v>2.25</v>
@@ -749,6 +749,9 @@
           <t>Btpi-15st26 3,1%</t>
         </is>
       </c>
+      <c r="C14" t="n">
+        <v>102.86</v>
+      </c>
       <c r="D14" t="n">
         <v>1.55</v>
       </c>
@@ -790,7 +793,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>95.56</v>
+        <v>95.47</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -810,7 +813,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>90.41</v>
+        <v>90.22</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -830,7 +833,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>85.2</v>
+        <v>85.25</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -901,7 +904,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>107.07</v>
+        <v>106.87</v>
       </c>
       <c r="D22" t="n">
         <v>2.375</v>
@@ -924,7 +927,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>108.62</v>
+        <v>107.85</v>
       </c>
       <c r="D23" t="n">
         <v>2.375</v>
@@ -947,7 +950,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>93.42</v>
+        <v>93.37</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -967,7 +970,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>89.26000000000001</v>
+        <v>89.06999999999999</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -1072,7 +1075,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>104.05</v>
+        <v>103.78</v>
       </c>
       <c r="D31" t="n">
         <v>1.75</v>
@@ -1095,7 +1098,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>87.2</v>
+        <v>86.51000000000001</v>
       </c>
       <c r="D32" t="n">
         <v>1.625</v>
@@ -1118,7 +1121,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>92.29000000000001</v>
+        <v>91.97</v>
       </c>
       <c r="D33" t="n">
         <v>0.825</v>
@@ -1141,7 +1144,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>100.01</v>
+        <v>100</v>
       </c>
       <c r="D34" t="n">
         <v>1</v>
@@ -1164,7 +1167,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>100.03</v>
+        <v>99.70999999999999</v>
       </c>
       <c r="D35" t="n">
         <v>0.625</v>
@@ -1187,7 +1190,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>79.23999999999999</v>
+        <v>78.51000000000001</v>
       </c>
       <c r="D36" t="n">
         <v>1.35</v>
@@ -1210,7 +1213,7 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>99.736</v>
+        <v>99.729</v>
       </c>
       <c r="D37" t="n">
         <v>0.8</v>
@@ -1233,7 +1236,7 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>88.06</v>
+        <v>87.58</v>
       </c>
       <c r="D38" t="n">
         <v>1.125</v>
@@ -1256,7 +1259,7 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>99.14</v>
+        <v>99.06</v>
       </c>
       <c r="D39" t="n">
         <v>0.625</v>
@@ -1279,7 +1282,7 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>69.83</v>
+        <v>69.11</v>
       </c>
       <c r="D40" t="n">
         <v>1.4</v>
@@ -1302,7 +1305,7 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>94.81999999999999</v>
+        <v>94.31999999999999</v>
       </c>
       <c r="D41" t="n">
         <v>1.225</v>
@@ -1325,7 +1328,7 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>100.27</v>
+        <v>100.2</v>
       </c>
       <c r="D42" t="n">
         <v>1.1</v>
@@ -1348,7 +1351,7 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>101.19</v>
+        <v>101.25</v>
       </c>
       <c r="D43" t="n">
         <v>0.65</v>
@@ -1371,7 +1374,7 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>89.09999999999999</v>
+        <v>88.43000000000001</v>
       </c>
       <c r="D44" t="n">
         <v>1.725</v>
@@ -1394,7 +1397,7 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>99.95</v>
+        <v>99.87</v>
       </c>
       <c r="D45" t="n">
         <v>1.025</v>
@@ -1417,7 +1420,7 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>91.7</v>
+        <v>91.18000000000001</v>
       </c>
       <c r="D46" t="n">
         <v>1.475</v>
@@ -1440,7 +1443,7 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>99.56</v>
+        <v>99.54000000000001</v>
       </c>
       <c r="D47" t="n">
         <v>1</v>
@@ -1463,7 +1466,7 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>99.836</v>
+        <v>99.84999999999999</v>
       </c>
       <c r="D48" t="n">
         <v>0.275</v>
@@ -1486,7 +1489,7 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>101.55</v>
+        <v>101.43</v>
       </c>
       <c r="D49" t="n">
         <v>1.4</v>
@@ -1509,7 +1512,7 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>100.099</v>
+        <v>100.078</v>
       </c>
       <c r="D50" t="n">
         <v>1.25</v>
@@ -1532,7 +1535,7 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>99.7</v>
+        <v>99.19</v>
       </c>
       <c r="D51" t="n">
         <v>1.675</v>
@@ -1555,7 +1558,7 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>94.25</v>
+        <v>93.5</v>
       </c>
       <c r="D52" t="n">
         <v>1.925</v>
@@ -1578,7 +1581,7 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>102.06</v>
+        <v>101.85</v>
       </c>
       <c r="D53" t="n">
         <v>1.5</v>
@@ -1601,7 +1604,7 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>100.1</v>
+        <v>100.071</v>
       </c>
       <c r="D54" t="n">
         <v>1.05</v>
@@ -1624,7 +1627,7 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>91.33</v>
+        <v>90.73</v>
       </c>
       <c r="D55" t="n">
         <v>1.55</v>
@@ -1647,7 +1650,7 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>94.66</v>
+        <v>94.45999999999999</v>
       </c>
       <c r="D56" t="n">
         <v>0.675</v>
@@ -1670,7 +1673,7 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>97.23</v>
+        <v>97.12</v>
       </c>
       <c r="D57" t="n">
         <v>0.2</v>
@@ -1693,7 +1696,7 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>99.81</v>
+        <v>99.79000000000001</v>
       </c>
       <c r="D58" t="n">
         <v>0.325</v>
@@ -1716,7 +1719,7 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>98.45</v>
+        <v>98.5</v>
       </c>
       <c r="D59" t="n">
         <v>0.425</v>
@@ -1739,7 +1742,7 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>72.22</v>
+        <v>71.67</v>
       </c>
       <c r="D60" t="n">
         <v>1.225</v>
@@ -1762,7 +1765,7 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>81.69</v>
+        <v>81.27</v>
       </c>
       <c r="D61" t="n">
         <v>0.725</v>
@@ -1785,7 +1788,7 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>92.09</v>
+        <v>91.86</v>
       </c>
       <c r="D62" t="n">
         <v>0.475</v>
@@ -1808,7 +1811,7 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>94.66</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="D63" t="n">
         <v>0.825</v>
@@ -1831,7 +1834,7 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>93.94</v>
+        <v>93.7</v>
       </c>
       <c r="D64" t="n">
         <v>0.65</v>
@@ -1854,7 +1857,7 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>99.59399999999999</v>
+        <v>99.521</v>
       </c>
       <c r="D65" t="n">
         <v>0.325</v>
@@ -1877,7 +1880,7 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>97.72</v>
+        <v>97.65000000000001</v>
       </c>
       <c r="D66" t="n">
         <v>0.475</v>
@@ -1900,7 +1903,7 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>99.364</v>
+        <v>99.348</v>
       </c>
       <c r="D67" t="n">
         <v>0.25</v>
@@ -1923,7 +1926,7 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>74.98</v>
+        <v>74.48999999999999</v>
       </c>
       <c r="D68" t="n">
         <v>0.9</v>
@@ -1946,7 +1949,7 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>90.17</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="D69" t="n">
         <v>0.45</v>
@@ -1969,7 +1972,7 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>60.43</v>
+        <v>59.88</v>
       </c>
       <c r="D70" t="n">
         <v>0.85</v>
@@ -1992,7 +1995,7 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>95.23</v>
+        <v>95.26000000000001</v>
       </c>
       <c r="D71" t="n">
         <v>0.3</v>
@@ -2015,7 +2018,7 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>74.78</v>
+        <v>74.34</v>
       </c>
       <c r="D72" t="n">
         <v>0.475</v>
@@ -2038,7 +2041,7 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>95.20999999999999</v>
+        <v>95.08</v>
       </c>
       <c r="D73" t="n">
         <v>0.125</v>
@@ -2061,7 +2064,7 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>87.73999999999999</v>
+        <v>87.47</v>
       </c>
       <c r="D74" t="n">
         <v>0.3</v>
@@ -2084,7 +2087,7 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>58.73</v>
+        <v>58.13</v>
       </c>
       <c r="D75" t="n">
         <v>0.075</v>
@@ -2107,7 +2110,7 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>98.84099999999999</v>
+        <v>98.821</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
@@ -2127,7 +2130,7 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>65.26000000000001</v>
+        <v>64.72</v>
       </c>
       <c r="D77" t="n">
         <v>0.75</v>
@@ -2150,7 +2153,7 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>57.49</v>
+        <v>56.85</v>
       </c>
       <c r="D78" t="n">
         <v>1.075</v>
@@ -2173,7 +2176,7 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>79.09999999999999</v>
+        <v>78.77</v>
       </c>
       <c r="D79" t="n">
         <v>0.6</v>
@@ -2196,7 +2199,7 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>95.13</v>
+        <v>94.98999999999999</v>
       </c>
       <c r="D80" t="n">
         <v>0.25</v>
@@ -2219,7 +2222,7 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>88.78</v>
+        <v>88.48999999999999</v>
       </c>
       <c r="D81" t="n">
         <v>0.475</v>
@@ -2242,7 +2245,7 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>98.29900000000001</v>
+        <v>98.268</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
@@ -2262,7 +2265,7 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>87.54000000000001</v>
+        <v>87.19</v>
       </c>
       <c r="D83" t="n">
         <v>0.475</v>
@@ -2285,7 +2288,7 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>87.3</v>
+        <v>86.91</v>
       </c>
       <c r="D84" t="n">
         <v>0.375</v>
@@ -2308,7 +2311,7 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>93.62</v>
+        <v>93.5</v>
       </c>
       <c r="D85" t="n">
         <v>0.225</v>
@@ -2331,7 +2334,7 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>66.05</v>
+        <v>65.47</v>
       </c>
       <c r="D86" t="n">
         <v>1.075</v>
@@ -2354,7 +2357,7 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>90.02</v>
+        <v>89.70999999999999</v>
       </c>
       <c r="D87" t="n">
         <v>0.05</v>
@@ -2377,7 +2380,7 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>98.53</v>
+        <v>98.45</v>
       </c>
       <c r="D88" t="n">
         <v>0.55</v>
@@ -2400,7 +2403,7 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>96.19</v>
+        <v>95.81</v>
       </c>
       <c r="D89" t="n">
         <v>1.25</v>
@@ -2423,7 +2426,7 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>101.19</v>
+        <v>101.01</v>
       </c>
       <c r="D90" t="n">
         <v>1.4</v>
@@ -2446,7 +2449,7 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>95.06999999999999</v>
+        <v>94.5</v>
       </c>
       <c r="D91" t="n">
         <v>1.625</v>
@@ -2469,7 +2472,7 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>100.86</v>
+        <v>100.8</v>
       </c>
       <c r="D92" t="n">
         <v>0.8</v>
@@ -2628,7 +2631,7 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>101.05</v>
+        <v>100.91</v>
       </c>
       <c r="D101" t="n">
         <v>1.325</v>
@@ -2651,7 +2654,7 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>105.27</v>
+        <v>104.77</v>
       </c>
       <c r="D102" t="n">
         <v>2</v>
@@ -2674,7 +2677,7 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>100.549</v>
+        <v>100.544</v>
       </c>
       <c r="D103" t="n">
         <v>1.75</v>
@@ -2697,7 +2700,7 @@
         </is>
       </c>
       <c r="C104" t="n">
-        <v>101.51</v>
+        <v>101.42</v>
       </c>
       <c r="D104" t="n">
         <v>0.8</v>
@@ -2720,7 +2723,7 @@
         </is>
       </c>
       <c r="C105" t="n">
-        <v>108.37</v>
+        <v>107.99</v>
       </c>
       <c r="D105" t="n">
         <v>2.2</v>
@@ -2743,7 +2746,7 @@
         </is>
       </c>
       <c r="C106" t="n">
-        <v>105.11</v>
+        <v>104.88</v>
       </c>
       <c r="D106" t="n">
         <v>1.925</v>
@@ -2766,7 +2769,7 @@
         </is>
       </c>
       <c r="C107" t="n">
-        <v>102.89</v>
+        <v>102.78</v>
       </c>
       <c r="D107" t="n">
         <v>1.7</v>
@@ -2806,7 +2809,7 @@
         </is>
       </c>
       <c r="C109" t="n">
-        <v>104.33</v>
+        <v>103.69</v>
       </c>
       <c r="D109" t="n">
         <v>2.225</v>
@@ -2829,7 +2832,7 @@
         </is>
       </c>
       <c r="C110" t="n">
-        <v>102.43</v>
+        <v>102.34</v>
       </c>
       <c r="D110" t="n">
         <v>1</v>
@@ -2852,7 +2855,7 @@
         </is>
       </c>
       <c r="C111" t="n">
-        <v>101.48</v>
+        <v>100.63</v>
       </c>
       <c r="D111" t="n">
         <v>2.25</v>
@@ -2875,7 +2878,7 @@
         </is>
       </c>
       <c r="C112" t="n">
-        <v>101.126</v>
+        <v>101.11</v>
       </c>
       <c r="D112" t="n">
         <v>1.9</v>
@@ -2898,7 +2901,7 @@
         </is>
       </c>
       <c r="C113" t="n">
-        <v>106.27</v>
+        <v>106.02</v>
       </c>
       <c r="D113" t="n">
         <v>2</v>
@@ -2921,7 +2924,7 @@
         </is>
       </c>
       <c r="C114" t="n">
-        <v>104.53</v>
+        <v>104.28</v>
       </c>
       <c r="D114" t="n">
         <v>1.85</v>
@@ -2943,9 +2946,6 @@
           <t>Btpi Tf 1.5% Mg29 Eur</t>
         </is>
       </c>
-      <c r="C115" t="n">
-        <v>101.9</v>
-      </c>
       <c r="D115" t="n">
         <v>0.75</v>
       </c>
@@ -2967,7 +2967,7 @@
         </is>
       </c>
       <c r="C116" t="n">
-        <v>107.84</v>
+        <v>107.39</v>
       </c>
       <c r="D116" t="n">
         <v>2.175</v>
@@ -2990,7 +2990,7 @@
         </is>
       </c>
       <c r="C117" t="n">
-        <v>102.95</v>
+        <v>102.81</v>
       </c>
       <c r="D117" t="n">
         <v>2</v>
@@ -3013,7 +3013,7 @@
         </is>
       </c>
       <c r="C118" t="n">
-        <v>103.1</v>
+        <v>102.68</v>
       </c>
       <c r="D118" t="n">
         <v>1.2</v>
@@ -3036,7 +3036,7 @@
         </is>
       </c>
       <c r="C119" t="n">
-        <v>104.19</v>
+        <v>104.04</v>
       </c>
       <c r="D119" t="n">
         <v>1.9</v>
@@ -3076,7 +3076,7 @@
         </is>
       </c>
       <c r="C121" t="n">
-        <v>101.86</v>
+        <v>101.79</v>
       </c>
       <c r="D121" t="n">
         <v>1.925</v>
@@ -3099,7 +3099,7 @@
         </is>
       </c>
       <c r="C122" t="n">
-        <v>100.144</v>
+        <v>100.15</v>
       </c>
       <c r="D122" t="n">
         <v>1.8</v>
@@ -3122,7 +3122,7 @@
         </is>
       </c>
       <c r="C123" t="n">
-        <v>106.64</v>
+        <v>106.17</v>
       </c>
       <c r="D123" t="n">
         <v>2.1</v>
@@ -3145,7 +3145,7 @@
         </is>
       </c>
       <c r="C124" t="n">
-        <v>105.92</v>
+        <v>105.61</v>
       </c>
       <c r="D124" t="n">
         <v>2</v>
@@ -3168,7 +3168,7 @@
         </is>
       </c>
       <c r="C125" t="n">
-        <v>105.45</v>
+        <v>105.17</v>
       </c>
       <c r="D125" t="n">
         <v>1.025</v>
@@ -3191,7 +3191,7 @@
         </is>
       </c>
       <c r="C126" t="n">
-        <v>105.47</v>
+        <v>105.28</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="C127" t="n">
-        <v>101.17</v>
+        <v>101.14</v>
       </c>
       <c r="D127" t="n">
         <v>1.475</v>
@@ -3234,7 +3234,7 @@
         </is>
       </c>
       <c r="C128" t="n">
-        <v>103.34</v>
+        <v>103.06</v>
       </c>
       <c r="D128" t="n">
         <v>1.75</v>
@@ -3257,7 +3257,7 @@
         </is>
       </c>
       <c r="C129" t="n">
-        <v>102.95</v>
+        <v>102.28</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
@@ -3277,7 +3277,7 @@
         </is>
       </c>
       <c r="C130" t="n">
-        <v>103.78</v>
+        <v>103.55</v>
       </c>
       <c r="D130" t="n">
         <v>0.8125</v>
@@ -3300,7 +3300,7 @@
         </is>
       </c>
       <c r="C131" t="n">
-        <v>100.491</v>
+        <v>100.467</v>
       </c>
       <c r="D131" t="n">
         <v>1.6</v>
@@ -3323,7 +3323,7 @@
         </is>
       </c>
       <c r="C132" t="n">
-        <v>103.01</v>
+        <v>102.81</v>
       </c>
       <c r="D132" t="n">
         <v>1.675</v>
@@ -3346,7 +3346,7 @@
         </is>
       </c>
       <c r="C133" t="n">
-        <v>103.81</v>
+        <v>103.38</v>
       </c>
       <c r="D133" t="n">
         <v>1.925</v>
@@ -3369,7 +3369,7 @@
         </is>
       </c>
       <c r="C134" t="n">
-        <v>98.98</v>
+        <v>98.7</v>
       </c>
       <c r="D134" t="n">
         <v>0.9</v>
@@ -3392,7 +3392,7 @@
         </is>
       </c>
       <c r="C135" t="n">
-        <v>103.7</v>
+        <v>103.36</v>
       </c>
       <c r="D135" t="n">
         <v>0.8375</v>
@@ -3415,7 +3415,7 @@
         </is>
       </c>
       <c r="C136" t="n">
-        <v>102.91</v>
+        <v>102.64</v>
       </c>
       <c r="D136" t="n">
         <v>1.725</v>
@@ -3438,7 +3438,7 @@
         </is>
       </c>
       <c r="C137" t="n">
-        <v>103.44</v>
+        <v>102.86</v>
       </c>
       <c r="D137" t="n">
         <v>2.025</v>
@@ -3461,7 +3461,7 @@
         </is>
       </c>
       <c r="C138" t="n">
-        <v>102.31</v>
+        <v>102.28</v>
       </c>
       <c r="D138" t="n">
         <v>1.725</v>
@@ -3484,7 +3484,7 @@
         </is>
       </c>
       <c r="C139" t="n">
-        <v>101.06</v>
+        <v>101</v>
       </c>
       <c r="D139" t="n">
         <v>1.55</v>
@@ -3507,7 +3507,7 @@
         </is>
       </c>
       <c r="C140" t="n">
-        <v>103.36</v>
+        <v>102.9</v>
       </c>
       <c r="D140" t="n">
         <v>1.925</v>
@@ -3530,7 +3530,7 @@
         </is>
       </c>
       <c r="C141" t="n">
-        <v>101.68</v>
+        <v>101.48</v>
       </c>
       <c r="D141" t="n">
         <v>1.5</v>
@@ -3553,7 +3553,7 @@
         </is>
       </c>
       <c r="C142" t="n">
-        <v>97.62</v>
+        <v>96.84999999999999</v>
       </c>
       <c r="D142" t="n">
         <v>2.15</v>
@@ -3576,7 +3576,7 @@
         </is>
       </c>
       <c r="C143" t="n">
-        <v>101.04</v>
+        <v>100.71</v>
       </c>
       <c r="D143" t="n">
         <v>1.575</v>
@@ -3599,7 +3599,7 @@
         </is>
       </c>
       <c r="C144" t="n">
-        <v>100.11</v>
+        <v>100.97</v>
       </c>
       <c r="D144" t="n">
         <v>1.35</v>
@@ -3622,7 +3622,7 @@
         </is>
       </c>
       <c r="C145" t="n">
-        <v>101.29</v>
+        <v>100.78</v>
       </c>
       <c r="D145" t="n">
         <v>1.825</v>
@@ -3645,7 +3645,7 @@
         </is>
       </c>
       <c r="C146" t="n">
-        <v>99.39</v>
+        <v>98.7</v>
       </c>
       <c r="D146" t="n">
         <v>2.05</v>
@@ -3668,7 +3668,7 @@
         </is>
       </c>
       <c r="C147" t="n">
-        <v>100.59</v>
+        <v>100.58</v>
       </c>
       <c r="D147" t="n">
         <v>1.275</v>
@@ -3691,7 +3691,7 @@
         </is>
       </c>
       <c r="C148" t="n">
-        <v>100.77</v>
+        <v>100.44</v>
       </c>
       <c r="D148" t="n">
         <v>0.7125</v>
@@ -3714,7 +3714,7 @@
         </is>
       </c>
       <c r="C149" t="n">
-        <v>98.66</v>
+        <v>98.08</v>
       </c>
       <c r="D149" t="n">
         <v>1.925</v>
@@ -3737,7 +3737,7 @@
         </is>
       </c>
       <c r="C150" t="n">
-        <v>100.91</v>
+        <v>100.82</v>
       </c>
       <c r="D150" t="n">
         <v>1.475</v>
@@ -3760,7 +3760,7 @@
         </is>
       </c>
       <c r="C151" t="n">
-        <v>100.83</v>
+        <v>100.81</v>
       </c>
       <c r="D151" t="n">
         <v>1.325</v>
@@ -3783,7 +3783,7 @@
         </is>
       </c>
       <c r="C152" t="n">
-        <v>100.94</v>
+        <v>100.69</v>
       </c>
       <c r="D152" t="n">
         <v>1.625</v>
@@ -3806,7 +3806,7 @@
         </is>
       </c>
       <c r="C153" t="n">
-        <v>98.38</v>
+        <v>97.3</v>
       </c>
       <c r="D153" t="n">
         <v>1.275</v>
@@ -3829,7 +3829,7 @@
         </is>
       </c>
       <c r="C154" t="n">
-        <v>100.64</v>
+        <v>100.18</v>
       </c>
       <c r="D154" t="n">
         <v>1.49508</v>
@@ -3852,7 +3852,7 @@
         </is>
       </c>
       <c r="C155" t="n">
-        <v>100.47</v>
+        <v>100.29</v>
       </c>
       <c r="D155" t="n">
         <v>0.925</v>
@@ -3875,7 +3875,7 @@
         </is>
       </c>
       <c r="C156" t="n">
-        <v>99.69</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="D156" t="n">
         <v>0.82623</v>
@@ -3898,7 +3898,7 @@
         </is>
       </c>
       <c r="C157" t="n">
-        <v>99.94</v>
+        <v>99.93000000000001</v>
       </c>
       <c r="D157" t="n">
         <v>0.34807</v>
@@ -3921,7 +3921,7 @@
         </is>
       </c>
       <c r="C158" t="n">
-        <v>99.38</v>
+        <v>99.36</v>
       </c>
       <c r="D158" t="n">
         <v>0.55</v>
@@ -3944,7 +3944,7 @@
         </is>
       </c>
       <c r="C159" t="n">
-        <v>99.75</v>
+        <v>99.56</v>
       </c>
       <c r="D159" t="n">
         <v>1.175</v>

--- a/btp_dati.xlsx
+++ b/btp_dati.xlsx
@@ -474,7 +474,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>106.1</v>
+        <v>106.08</v>
       </c>
       <c r="D2" t="n">
         <v>3.625</v>
@@ -497,7 +497,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>109.11</v>
+        <v>109.26</v>
       </c>
       <c r="D3" t="n">
         <v>3.25</v>
@@ -520,7 +520,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>110.61</v>
+        <v>110.87</v>
       </c>
       <c r="D4" t="n">
         <v>2.625</v>
@@ -543,7 +543,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>116.49</v>
+        <v>116.72</v>
       </c>
       <c r="D5" t="n">
         <v>3</v>
@@ -566,7 +566,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>116.8</v>
+        <v>116.92</v>
       </c>
       <c r="D6" t="n">
         <v>2.875</v>
@@ -589,7 +589,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>112.38</v>
+        <v>112.51</v>
       </c>
       <c r="D7" t="n">
         <v>2.5</v>
@@ -612,7 +612,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>106.79</v>
+        <v>107</v>
       </c>
       <c r="D8" t="n">
         <v>1.175</v>
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>103.19</v>
+        <v>103.16</v>
       </c>
       <c r="D9" t="n">
         <v>2</v>
@@ -658,7 +658,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>111.95</v>
+        <v>111.86</v>
       </c>
       <c r="D10" t="n">
         <v>2.5</v>
@@ -681,7 +681,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>111.73</v>
+        <v>111.63</v>
       </c>
       <c r="D11" t="n">
         <v>2.5</v>
@@ -704,7 +704,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>105.4</v>
+        <v>104.99</v>
       </c>
       <c r="D12" t="n">
         <v>1.275</v>
@@ -727,7 +727,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>101.253</v>
+        <v>101.233</v>
       </c>
       <c r="D13" t="n">
         <v>2.25</v>
@@ -773,7 +773,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>97.81</v>
+        <v>97.78</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>95.47</v>
+        <v>95.56999999999999</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>90.22</v>
+        <v>90.17</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -833,7 +833,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>85.25</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -904,7 +904,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>106.87</v>
+        <v>107.05</v>
       </c>
       <c r="D22" t="n">
         <v>2.375</v>
@@ -927,7 +927,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>107.85</v>
+        <v>107.7</v>
       </c>
       <c r="D23" t="n">
         <v>2.375</v>
@@ -949,9 +949,6 @@
           <t>Btp Coupon Strip Zc St28 Eur</t>
         </is>
       </c>
-      <c r="C24" t="n">
-        <v>93.37</v>
-      </c>
       <c r="E24" t="inlineStr">
         <is>
           <t>01-09-28</t>
@@ -970,7 +967,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>89.06999999999999</v>
+        <v>89.23999999999999</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -1075,7 +1072,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>103.78</v>
+        <v>103.98</v>
       </c>
       <c r="D31" t="n">
         <v>1.75</v>
@@ -1098,7 +1095,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>86.51000000000001</v>
+        <v>86.27</v>
       </c>
       <c r="D32" t="n">
         <v>1.625</v>
@@ -1121,7 +1118,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>91.97</v>
+        <v>92.19</v>
       </c>
       <c r="D33" t="n">
         <v>0.825</v>
@@ -1144,7 +1141,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>100</v>
+        <v>99.999</v>
       </c>
       <c r="D34" t="n">
         <v>1</v>
@@ -1167,7 +1164,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>99.70999999999999</v>
+        <v>99.8</v>
       </c>
       <c r="D35" t="n">
         <v>0.625</v>
@@ -1190,7 +1187,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>78.51000000000001</v>
+        <v>78.31999999999999</v>
       </c>
       <c r="D36" t="n">
         <v>1.35</v>
@@ -1213,7 +1210,7 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>99.729</v>
+        <v>99.72</v>
       </c>
       <c r="D37" t="n">
         <v>0.8</v>
@@ -1236,7 +1233,7 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>87.58</v>
+        <v>87.62</v>
       </c>
       <c r="D38" t="n">
         <v>1.125</v>
@@ -1259,7 +1256,7 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>99.06</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="D39" t="n">
         <v>0.625</v>
@@ -1282,7 +1279,7 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>69.11</v>
+        <v>68.87</v>
       </c>
       <c r="D40" t="n">
         <v>1.4</v>
@@ -1305,7 +1302,7 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>94.31999999999999</v>
+        <v>94.56</v>
       </c>
       <c r="D41" t="n">
         <v>1.225</v>
@@ -1328,7 +1325,7 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>100.2</v>
+        <v>100.25</v>
       </c>
       <c r="D42" t="n">
         <v>1.1</v>
@@ -1351,7 +1348,7 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>101.25</v>
+        <v>101.37</v>
       </c>
       <c r="D43" t="n">
         <v>0.65</v>
@@ -1374,7 +1371,7 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>88.43000000000001</v>
+        <v>88.17</v>
       </c>
       <c r="D44" t="n">
         <v>1.725</v>
@@ -1397,7 +1394,7 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>99.87</v>
+        <v>99.94</v>
       </c>
       <c r="D45" t="n">
         <v>1.025</v>
@@ -1420,7 +1417,7 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>91.18000000000001</v>
+        <v>91.17</v>
       </c>
       <c r="D46" t="n">
         <v>1.475</v>
@@ -1443,7 +1440,7 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>99.54000000000001</v>
+        <v>99.64</v>
       </c>
       <c r="D47" t="n">
         <v>1</v>
@@ -1466,7 +1463,7 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>99.84999999999999</v>
+        <v>99.849</v>
       </c>
       <c r="D48" t="n">
         <v>0.275</v>
@@ -1489,7 +1486,7 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>101.43</v>
+        <v>101.57</v>
       </c>
       <c r="D49" t="n">
         <v>1.4</v>
@@ -1512,7 +1509,7 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>100.078</v>
+        <v>100.097</v>
       </c>
       <c r="D50" t="n">
         <v>1.25</v>
@@ -1535,7 +1532,7 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>99.19</v>
+        <v>99.34</v>
       </c>
       <c r="D51" t="n">
         <v>1.675</v>
@@ -1558,7 +1555,7 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>93.5</v>
+        <v>93.29000000000001</v>
       </c>
       <c r="D52" t="n">
         <v>1.925</v>
@@ -1581,7 +1578,7 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>101.85</v>
+        <v>101.96</v>
       </c>
       <c r="D53" t="n">
         <v>1.5</v>
@@ -1604,7 +1601,7 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>100.071</v>
+        <v>100.095</v>
       </c>
       <c r="D54" t="n">
         <v>1.05</v>
@@ -1627,7 +1624,7 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>90.73</v>
+        <v>90.81999999999999</v>
       </c>
       <c r="D55" t="n">
         <v>1.55</v>
@@ -1650,7 +1647,7 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>94.45999999999999</v>
+        <v>94.59</v>
       </c>
       <c r="D56" t="n">
         <v>0.675</v>
@@ -1673,7 +1670,7 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>97.12</v>
+        <v>97.15000000000001</v>
       </c>
       <c r="D57" t="n">
         <v>0.2</v>
@@ -1696,7 +1693,7 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>99.79000000000001</v>
+        <v>99.83</v>
       </c>
       <c r="D58" t="n">
         <v>0.325</v>
@@ -1719,7 +1716,7 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>98.5</v>
+        <v>98.47</v>
       </c>
       <c r="D59" t="n">
         <v>0.425</v>
@@ -1742,7 +1739,7 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>71.67</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="D60" t="n">
         <v>1.225</v>
@@ -1765,7 +1762,7 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>81.27</v>
+        <v>81.41</v>
       </c>
       <c r="D61" t="n">
         <v>0.725</v>
@@ -1788,7 +1785,7 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>91.86</v>
+        <v>92.02</v>
       </c>
       <c r="D62" t="n">
         <v>0.475</v>
@@ -1811,7 +1808,7 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>94.40000000000001</v>
+        <v>94.55</v>
       </c>
       <c r="D63" t="n">
         <v>0.825</v>
@@ -1834,7 +1831,7 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>93.7</v>
+        <v>93.93000000000001</v>
       </c>
       <c r="D64" t="n">
         <v>0.65</v>
@@ -1857,7 +1854,7 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>99.521</v>
+        <v>99.599</v>
       </c>
       <c r="D65" t="n">
         <v>0.325</v>
@@ -1880,7 +1877,7 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>97.65000000000001</v>
+        <v>98.01000000000001</v>
       </c>
       <c r="D66" t="n">
         <v>0.475</v>
@@ -1903,7 +1900,7 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>99.348</v>
+        <v>99.36199999999999</v>
       </c>
       <c r="D67" t="n">
         <v>0.25</v>
@@ -1926,7 +1923,7 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>74.48999999999999</v>
+        <v>74.34</v>
       </c>
       <c r="D68" t="n">
         <v>0.9</v>
@@ -1949,7 +1946,7 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>89.90000000000001</v>
+        <v>90.06</v>
       </c>
       <c r="D69" t="n">
         <v>0.45</v>
@@ -1972,7 +1969,7 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>59.88</v>
+        <v>59.63</v>
       </c>
       <c r="D70" t="n">
         <v>0.85</v>
@@ -1995,7 +1992,7 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>95.26000000000001</v>
+        <v>95.36</v>
       </c>
       <c r="D71" t="n">
         <v>0.3</v>
@@ -2018,7 +2015,7 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>74.34</v>
+        <v>74.41</v>
       </c>
       <c r="D72" t="n">
         <v>0.475</v>
@@ -2041,7 +2038,7 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>95.08</v>
+        <v>95.23</v>
       </c>
       <c r="D73" t="n">
         <v>0.125</v>
@@ -2064,7 +2061,7 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>87.47</v>
+        <v>87.63</v>
       </c>
       <c r="D74" t="n">
         <v>0.3</v>
@@ -2087,7 +2084,7 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>58.13</v>
+        <v>58.11</v>
       </c>
       <c r="D75" t="n">
         <v>0.075</v>
@@ -2110,7 +2107,7 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>98.821</v>
+        <v>98.84999999999999</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
@@ -2130,7 +2127,7 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>64.72</v>
+        <v>64.54000000000001</v>
       </c>
       <c r="D77" t="n">
         <v>0.75</v>
@@ -2153,7 +2150,7 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>56.85</v>
+        <v>56.79</v>
       </c>
       <c r="D78" t="n">
         <v>1.075</v>
@@ -2176,7 +2173,7 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>78.77</v>
+        <v>78.43000000000001</v>
       </c>
       <c r="D79" t="n">
         <v>0.6</v>
@@ -2199,7 +2196,7 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>94.98999999999999</v>
+        <v>95.13</v>
       </c>
       <c r="D80" t="n">
         <v>0.25</v>
@@ -2222,7 +2219,7 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>88.48999999999999</v>
+        <v>88.59</v>
       </c>
       <c r="D81" t="n">
         <v>0.475</v>
@@ -2245,7 +2242,7 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>98.268</v>
+        <v>98.3</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
@@ -2265,7 +2262,7 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>87.19</v>
+        <v>87.3</v>
       </c>
       <c r="D83" t="n">
         <v>0.475</v>
@@ -2288,7 +2285,7 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>86.91</v>
+        <v>87.06999999999999</v>
       </c>
       <c r="D84" t="n">
         <v>0.375</v>
@@ -2311,7 +2308,7 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>93.5</v>
+        <v>93.58</v>
       </c>
       <c r="D85" t="n">
         <v>0.225</v>
@@ -2334,7 +2331,7 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>65.47</v>
+        <v>65.29000000000001</v>
       </c>
       <c r="D86" t="n">
         <v>1.075</v>
@@ -2357,7 +2354,7 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>89.70999999999999</v>
+        <v>89.89</v>
       </c>
       <c r="D87" t="n">
         <v>0.05</v>
@@ -2380,7 +2377,7 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>98.45</v>
+        <v>98.51000000000001</v>
       </c>
       <c r="D88" t="n">
         <v>0.55</v>
@@ -2403,7 +2400,7 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>95.81</v>
+        <v>95.98</v>
       </c>
       <c r="D89" t="n">
         <v>1.25</v>
@@ -2426,7 +2423,7 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>101.01</v>
+        <v>101.13</v>
       </c>
       <c r="D90" t="n">
         <v>1.4</v>
@@ -2449,7 +2446,7 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>94.5</v>
+        <v>94.48999999999999</v>
       </c>
       <c r="D91" t="n">
         <v>1.625</v>
@@ -2472,7 +2469,7 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>100.8</v>
+        <v>100.89</v>
       </c>
       <c r="D92" t="n">
         <v>0.8</v>
@@ -2631,7 +2628,7 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>100.91</v>
+        <v>101.02</v>
       </c>
       <c r="D101" t="n">
         <v>1.325</v>
@@ -2654,7 +2651,7 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>104.77</v>
+        <v>104.8</v>
       </c>
       <c r="D102" t="n">
         <v>2</v>
@@ -2677,7 +2674,7 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>100.544</v>
+        <v>100.535</v>
       </c>
       <c r="D103" t="n">
         <v>1.75</v>
@@ -2700,7 +2697,7 @@
         </is>
       </c>
       <c r="C104" t="n">
-        <v>101.42</v>
+        <v>101.51</v>
       </c>
       <c r="D104" t="n">
         <v>0.8</v>
@@ -2723,7 +2720,7 @@
         </is>
       </c>
       <c r="C105" t="n">
-        <v>107.99</v>
+        <v>108.14</v>
       </c>
       <c r="D105" t="n">
         <v>2.2</v>
@@ -2746,7 +2743,7 @@
         </is>
       </c>
       <c r="C106" t="n">
-        <v>104.88</v>
+        <v>105.08</v>
       </c>
       <c r="D106" t="n">
         <v>1.925</v>
@@ -2769,7 +2766,7 @@
         </is>
       </c>
       <c r="C107" t="n">
-        <v>102.78</v>
+        <v>101.89</v>
       </c>
       <c r="D107" t="n">
         <v>1.7</v>
@@ -2809,7 +2806,7 @@
         </is>
       </c>
       <c r="C109" t="n">
-        <v>103.69</v>
+        <v>103.5</v>
       </c>
       <c r="D109" t="n">
         <v>2.225</v>
@@ -2832,7 +2829,7 @@
         </is>
       </c>
       <c r="C110" t="n">
-        <v>102.34</v>
+        <v>102.36</v>
       </c>
       <c r="D110" t="n">
         <v>1</v>
@@ -2855,7 +2852,7 @@
         </is>
       </c>
       <c r="C111" t="n">
-        <v>100.63</v>
+        <v>100.32</v>
       </c>
       <c r="D111" t="n">
         <v>2.25</v>
@@ -2878,7 +2875,7 @@
         </is>
       </c>
       <c r="C112" t="n">
-        <v>101.11</v>
+        <v>101.09</v>
       </c>
       <c r="D112" t="n">
         <v>1.9</v>
@@ -2901,7 +2898,7 @@
         </is>
       </c>
       <c r="C113" t="n">
-        <v>106.02</v>
+        <v>106.13</v>
       </c>
       <c r="D113" t="n">
         <v>2</v>
@@ -2924,7 +2921,7 @@
         </is>
       </c>
       <c r="C114" t="n">
-        <v>104.28</v>
+        <v>104.37</v>
       </c>
       <c r="D114" t="n">
         <v>1.85</v>
@@ -2946,6 +2943,9 @@
           <t>Btpi Tf 1.5% Mg29 Eur</t>
         </is>
       </c>
+      <c r="C115" t="n">
+        <v>101.98</v>
+      </c>
       <c r="D115" t="n">
         <v>0.75</v>
       </c>
@@ -2967,7 +2967,7 @@
         </is>
       </c>
       <c r="C116" t="n">
-        <v>107.39</v>
+        <v>107.46</v>
       </c>
       <c r="D116" t="n">
         <v>2.175</v>
@@ -2990,7 +2990,7 @@
         </is>
       </c>
       <c r="C117" t="n">
-        <v>102.81</v>
+        <v>102.86</v>
       </c>
       <c r="D117" t="n">
         <v>2</v>
@@ -3013,7 +3013,7 @@
         </is>
       </c>
       <c r="C118" t="n">
-        <v>102.68</v>
+        <v>102.6</v>
       </c>
       <c r="D118" t="n">
         <v>1.2</v>
@@ -3036,7 +3036,7 @@
         </is>
       </c>
       <c r="C119" t="n">
-        <v>104.04</v>
+        <v>104.16</v>
       </c>
       <c r="D119" t="n">
         <v>1.9</v>
@@ -3058,6 +3058,9 @@
           <t>Btpstripital Zc Ott39</t>
         </is>
       </c>
+      <c r="C120" t="n">
+        <v>56.72</v>
+      </c>
       <c r="E120" t="inlineStr">
         <is>
           <t>01-10-39</t>
@@ -3076,7 +3079,7 @@
         </is>
       </c>
       <c r="C121" t="n">
-        <v>101.79</v>
+        <v>101.83</v>
       </c>
       <c r="D121" t="n">
         <v>1.925</v>
@@ -3099,7 +3102,7 @@
         </is>
       </c>
       <c r="C122" t="n">
-        <v>100.15</v>
+        <v>100.122</v>
       </c>
       <c r="D122" t="n">
         <v>1.8</v>
@@ -3122,7 +3125,7 @@
         </is>
       </c>
       <c r="C123" t="n">
-        <v>106.17</v>
+        <v>106.18</v>
       </c>
       <c r="D123" t="n">
         <v>2.1</v>
@@ -3145,7 +3148,7 @@
         </is>
       </c>
       <c r="C124" t="n">
-        <v>105.61</v>
+        <v>105.8</v>
       </c>
       <c r="D124" t="n">
         <v>2</v>
@@ -3168,7 +3171,7 @@
         </is>
       </c>
       <c r="C125" t="n">
-        <v>105.17</v>
+        <v>105.23</v>
       </c>
       <c r="D125" t="n">
         <v>1.025</v>
@@ -3191,7 +3194,7 @@
         </is>
       </c>
       <c r="C126" t="n">
-        <v>105.28</v>
+        <v>105.45</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
@@ -3211,7 +3214,7 @@
         </is>
       </c>
       <c r="C127" t="n">
-        <v>101.14</v>
+        <v>101.19</v>
       </c>
       <c r="D127" t="n">
         <v>1.475</v>
@@ -3234,7 +3237,7 @@
         </is>
       </c>
       <c r="C128" t="n">
-        <v>103.06</v>
+        <v>103.21</v>
       </c>
       <c r="D128" t="n">
         <v>1.75</v>
@@ -3257,7 +3260,7 @@
         </is>
       </c>
       <c r="C129" t="n">
-        <v>102.28</v>
+        <v>102.25</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
@@ -3277,7 +3280,7 @@
         </is>
       </c>
       <c r="C130" t="n">
-        <v>103.55</v>
+        <v>103.99</v>
       </c>
       <c r="D130" t="n">
         <v>0.8125</v>
@@ -3300,7 +3303,7 @@
         </is>
       </c>
       <c r="C131" t="n">
-        <v>100.467</v>
+        <v>100.463</v>
       </c>
       <c r="D131" t="n">
         <v>1.6</v>
@@ -3323,7 +3326,7 @@
         </is>
       </c>
       <c r="C132" t="n">
-        <v>102.81</v>
+        <v>102.99</v>
       </c>
       <c r="D132" t="n">
         <v>1.675</v>
@@ -3346,7 +3349,7 @@
         </is>
       </c>
       <c r="C133" t="n">
-        <v>103.38</v>
+        <v>103.44</v>
       </c>
       <c r="D133" t="n">
         <v>1.925</v>
@@ -3369,7 +3372,7 @@
         </is>
       </c>
       <c r="C134" t="n">
-        <v>98.7</v>
+        <v>98.81999999999999</v>
       </c>
       <c r="D134" t="n">
         <v>0.9</v>
@@ -3392,7 +3395,7 @@
         </is>
       </c>
       <c r="C135" t="n">
-        <v>103.36</v>
+        <v>103.57</v>
       </c>
       <c r="D135" t="n">
         <v>0.8375</v>
@@ -3415,7 +3418,7 @@
         </is>
       </c>
       <c r="C136" t="n">
-        <v>102.64</v>
+        <v>102.72</v>
       </c>
       <c r="D136" t="n">
         <v>1.725</v>
@@ -3438,7 +3441,7 @@
         </is>
       </c>
       <c r="C137" t="n">
-        <v>102.86</v>
+        <v>103.03</v>
       </c>
       <c r="D137" t="n">
         <v>2.025</v>
@@ -3461,7 +3464,7 @@
         </is>
       </c>
       <c r="C138" t="n">
-        <v>102.28</v>
+        <v>102.35</v>
       </c>
       <c r="D138" t="n">
         <v>1.725</v>
@@ -3484,7 +3487,7 @@
         </is>
       </c>
       <c r="C139" t="n">
-        <v>101</v>
+        <v>101.006</v>
       </c>
       <c r="D139" t="n">
         <v>1.55</v>
@@ -3507,7 +3510,7 @@
         </is>
       </c>
       <c r="C140" t="n">
-        <v>102.9</v>
+        <v>103.08</v>
       </c>
       <c r="D140" t="n">
         <v>1.925</v>
@@ -3530,7 +3533,7 @@
         </is>
       </c>
       <c r="C141" t="n">
-        <v>101.48</v>
+        <v>101.59</v>
       </c>
       <c r="D141" t="n">
         <v>1.5</v>
@@ -3553,7 +3556,7 @@
         </is>
       </c>
       <c r="C142" t="n">
-        <v>96.84999999999999</v>
+        <v>96.48999999999999</v>
       </c>
       <c r="D142" t="n">
         <v>2.15</v>
@@ -3576,7 +3579,7 @@
         </is>
       </c>
       <c r="C143" t="n">
-        <v>100.71</v>
+        <v>100.94</v>
       </c>
       <c r="D143" t="n">
         <v>1.575</v>
@@ -3599,7 +3602,7 @@
         </is>
       </c>
       <c r="C144" t="n">
-        <v>100.97</v>
+        <v>101.05</v>
       </c>
       <c r="D144" t="n">
         <v>1.35</v>
@@ -3622,7 +3625,7 @@
         </is>
       </c>
       <c r="C145" t="n">
-        <v>100.78</v>
+        <v>100.98</v>
       </c>
       <c r="D145" t="n">
         <v>1.825</v>
@@ -3645,7 +3648,7 @@
         </is>
       </c>
       <c r="C146" t="n">
-        <v>98.7</v>
+        <v>98.45999999999999</v>
       </c>
       <c r="D146" t="n">
         <v>2.05</v>
@@ -3691,7 +3694,7 @@
         </is>
       </c>
       <c r="C148" t="n">
-        <v>100.44</v>
+        <v>100.54</v>
       </c>
       <c r="D148" t="n">
         <v>0.7125</v>
@@ -3714,7 +3717,7 @@
         </is>
       </c>
       <c r="C149" t="n">
-        <v>98.08</v>
+        <v>98.04000000000001</v>
       </c>
       <c r="D149" t="n">
         <v>1.925</v>
@@ -3737,7 +3740,7 @@
         </is>
       </c>
       <c r="C150" t="n">
-        <v>100.82</v>
+        <v>101.01</v>
       </c>
       <c r="D150" t="n">
         <v>1.475</v>
@@ -3760,7 +3763,7 @@
         </is>
       </c>
       <c r="C151" t="n">
-        <v>100.81</v>
+        <v>100.87</v>
       </c>
       <c r="D151" t="n">
         <v>1.325</v>
@@ -3783,7 +3786,7 @@
         </is>
       </c>
       <c r="C152" t="n">
-        <v>100.69</v>
+        <v>100.86</v>
       </c>
       <c r="D152" t="n">
         <v>1.625</v>
@@ -3806,7 +3809,7 @@
         </is>
       </c>
       <c r="C153" t="n">
-        <v>97.3</v>
+        <v>97.12</v>
       </c>
       <c r="D153" t="n">
         <v>1.275</v>
@@ -3829,7 +3832,7 @@
         </is>
       </c>
       <c r="C154" t="n">
-        <v>100.18</v>
+        <v>100.27</v>
       </c>
       <c r="D154" t="n">
         <v>1.49508</v>
@@ -3852,7 +3855,7 @@
         </is>
       </c>
       <c r="C155" t="n">
-        <v>100.29</v>
+        <v>100.45</v>
       </c>
       <c r="D155" t="n">
         <v>0.925</v>
@@ -3875,7 +3878,7 @@
         </is>
       </c>
       <c r="C156" t="n">
-        <v>99.40000000000001</v>
+        <v>99.56999999999999</v>
       </c>
       <c r="D156" t="n">
         <v>0.82623</v>
@@ -3898,10 +3901,10 @@
         </is>
       </c>
       <c r="C157" t="n">
-        <v>99.93000000000001</v>
+        <v>99.83</v>
       </c>
       <c r="D157" t="n">
-        <v>0.34807</v>
+        <v>1.05</v>
       </c>
       <c r="E157" t="inlineStr">
         <is>
@@ -3921,7 +3924,7 @@
         </is>
       </c>
       <c r="C158" t="n">
-        <v>99.36</v>
+        <v>99.47</v>
       </c>
       <c r="D158" t="n">
         <v>0.55</v>
@@ -3944,7 +3947,7 @@
         </is>
       </c>
       <c r="C159" t="n">
-        <v>99.56</v>
+        <v>99.73</v>
       </c>
       <c r="D159" t="n">
         <v>1.175</v>
